--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1172,8 +1172,206 @@
       </c>
       <c r="H15" s="3" t="inlineStr"/>
     </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>License stamp clobbers the §6 lab-identity header/footer and can name the wrong lab</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Parked by operator decision 2026-07-16 ("log it, finish PR 4 first"). Not started. No code touched.
+---</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>S-M (one shared helper plus a verify script; 8 callsites to re-check)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Medium-High. Every customer-facing workbook currently prints a header and foo...</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>licenseCtxFromReq (server/routes.ts:57-61) resolves the licensee lab from resolveActiveLabForRequest, which reads the X-Active-Lab-Id header and silently falls back to the user's default lab inside a bare catch {}. The export body meanwhile resolves the lab from req.scope.labId (the URL path param, set by labScopeMiddleware). Two sources of truth for one document. Separately and unconditionally, applyLicenseToExcelJSWorkbook (shared/licenseExceljs.ts:93-96) *assigns* rather than merges oddHeader/oddFooter on every sheet, so the six lines in the VeritaMap export that carefully set ${labName} CLIA: ${cliaNumber} (routes.ts:13932-13933, 14215-14216, 14224-14225) are dead code, overwritten at routes.ts:14237. §6 rule 3 exists so identity survives cell-level copy-paste; layers (b) and (c) do not currently exist in any shipped workbook.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 session, PR 4 (#1046) Gate 3 render. Related: feedback_pdf_lab_identity_resolution memory (same resolveActiveLabForRequest swallowed-throw shape).</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Long Excel column headers are clipped, truncating CFR citations mid-string</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Parked by operator decision 2026-07-16. Not started. No code touched.
+---</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>S (compute the header row height from the longest wrapped header, or raise th...</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Medium. The VeritaMap workbook currently prints "Reference Range Attestation...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>CLAUDE.md §6 specifies both "row height 20" for the header row and "wrap text" for cells. Those two rules conflict for any header longer than its column width. Row height 20 renders roughly one line of Calibri 11, so a header that wraps to two or three lines has its tail clipped in print and in PDF export. Confirmed on the live VeritaMap Compliance Map export: header row height is 20.0 with wrapText: true, and the three longest headers are "AMR Attestation (42 CFR 493.1253, per instrument)" (49 chars), "Reference Range Attestation (42 CFR 493.1253)" (45), and "Last Correlation / Method Comparison Date" (41). "Last SOP Review Date" and "AMR High (per instrument)" clip too.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-16 session, PR 4 (#1046) Gate 3 render. Sibling of [[#43]]; both were found by looking at the rendered workbook, and neither was catchable by the verify scripts.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>VeritaTrack calendar month cells are not expandable, so hidden tasks are unreachable</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Open. Not started.
+---</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>S (1-3 days) — make each month cell open a detail view or expand in place, an...</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>High — a compliance calendar that hides tasks with no way to see them undercu...</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Effort: S (1-3 days) — make each month cell open a detail view or expand in place, and wire the "+N more" affordance to reveal the full task list. The data is already loaded, this is a UI interaction gap, not a data one.
+Importance: High — a compliance calendar that hides tasks with no way to see them undercuts the module's core promise of showing what a lab owes and when.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>VeritaScan line items cannot attach or link evidence (policy or uploaded document)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Open. Not started.
+---</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>M (1-2 weeks) — add a per-item evidence link that reuses the VeritaScan URL-p...</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>High — showing evidence per line item is the whole point of a self-inspection...</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Effort: M (1-2 weeks) — add a per-item evidence link that reuses the VeritaScan URL-pointer model rather than storing files: let a line item reference an existing VeritaDC controlled document or an external URL, then surface it as completion evidence.
+Importance: High — showing evidence per line item is the whole point of a self-inspection; without it the scan records a status but cannot show the policy or document that satisfies it.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael. Recurring request.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Open. Not started. Needs a one-line scope confirmation (which master list).
+---</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Effort: S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility toggle that hides not-applicable or unused sections from a master-list view. Smaller if it is a "hide N/A" filter on the existing VeritaDC master list, larger if it also spans VeritaScan domains.
+Importance: Medium-High — came straight from a live prospect today as an onboarding-friction point; a lab that does not run a service line should not have to wade past its requirements.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael relaying a prospect ask from a demo today.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <autoFilter ref="A1:H20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1253,12 +1253,12 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells are not expandable, so hidden tasks are unreachable</t>
+          <t>VeritaScan line items cannot attach or link evidence (policy or uploaded document)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1269,23 +1269,23 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>S (1-3 days) — make each month cell open a detail view or expand in place, an...</t>
+          <t>M (1-2 weeks) — add a per-item evidence link that reuses the VeritaScan URL-p...</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>High — a compliance calendar that hides tasks with no way to see them undercu...</t>
+          <t>High — showing evidence per line item is the whole point of a self-inspection...</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Effort: S (1-3 days) — make each month cell open a detail view or expand in place, and wire the "+N more" affordance to reveal the full task list. The data is already loaded, this is a UI interaction gap, not a data one.
-Importance: High — a compliance calendar that hides tasks with no way to see them undercuts the module's core promise of showing what a lab owes and when.</t>
+          <t>Effort: M (1-2 weeks) — add a per-item evidence link that reuses the VeritaScan URL-pointer model rather than storing files: let a line item reference an existing VeritaDC controlled document or an external URL, then surface it as completion evidence.
+Importance: High — showing evidence per line item is the whole point of a self-inspection; without it the scan records a status but cannot show the policy or document that satisfies it.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).</t>
+          <t>2026-09-23 session, Michael. Recurring request.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1293,39 +1293,39 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items cannot attach or link evidence (policy or uploaded document)</t>
+          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Open. Not started.
+          <t>Open. Not started. Needs a one-line scope confirmation (which master list).
 ---</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>M (1-2 weeks) — add a per-item evidence link that reuses the VeritaScan URL-p...</t>
+          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>High — showing evidence per line item is the whole point of a self-inspection...</t>
+          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Effort: M (1-2 weeks) — add a per-item evidence link that reuses the VeritaScan URL-pointer model rather than storing files: let a line item reference an existing VeritaDC controlled document or an external URL, then surface it as completion evidence.
-Importance: High — showing evidence per line item is the whole point of a self-inspection; without it the scan records a status but cannot show the policy or document that satisfies it.</t>
+          <t>Effort: S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility toggle that hides not-applicable or unused sections from a master-list view. Smaller if it is a "hide N/A" filter on the existing VeritaDC master list, larger if it also spans VeritaScan domains.
+Importance: Medium-High — came straight from a live prospect today as an onboarding-friction point; a lab that does not run a service line should not have to wade past its requirements.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request.</t>
+          <t>2026-09-23 session, Michael relaying a prospect ask from a demo today.</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
@@ -1333,39 +1333,39 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
+          <t>VeritaComp: derive owed competencies from VeritaStaff instrument/test assignments</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Open. Not started. Needs a one-line scope confirmation (which master list).
+          <t>Open. Investigated 2026-09-24; ready to build mock-first, pending Michael's steer on the two forks.
 ---</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
+          <t>M-L (mock-first design plus the derivation and UI). The data model exists but...</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
+          <t>High — Michael pitches to prospects that VeritaComp bases owed competencies o...</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Effort: S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility toggle that hides not-applicable or unused sections from a master-list view. Smaller if it is a "hide N/A" filter on the existing VeritaDC master list, larger if it also spans VeritaScan domains.
-Importance: Medium-High — came straight from a live prospect today as an onboarding-friction point; a lab that does not run a service line should not have to wade past its requirements.</t>
+          <t>Effort: M-L (mock-first design plus the derivation and UI). The data model exists but the join is not trivial.
+Importance: High — Michael pitches to prospects that VeritaComp bases owed competencies on each staffer's VeritaStaff instrument/test selections. Currently untrue; making the pitch honest is the point.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael relaying a prospect ask from a demo today.</t>
+          <t>2026-09-24 session, Michael (pitch-integrity gap).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -1382,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1440,18 +1440,40 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: PR #1309 (squash on main e398d341), client/src/pages/VeritaTrackAppPage.tsx CalendarView. Month cells with more than 3 tasks are clickable and expand in place (chevron, "+N more" toggles to "Show less", due dates shown when open). Shipped and deployed 2026-09-24. Env-gated spec tests/playwright/veritatrack-calendar-expand.spec.ts.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1463,24 +1485,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1490,24 +1512,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1515,30 +1537,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1549,30 +1571,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1583,29 +1605,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1616,37 +1638,9 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
----</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
-23 years" as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1655,18 +1649,46 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
+23 years" as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 14, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1679,7 +1701,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1687,46 +1709,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
@@ -1734,14 +1727,14 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
+          <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1750,12 +1743,12 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -1763,13 +1756,14 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>session 299e9a73, ~2026-04-28.
+          <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1778,18 +1772,46 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -1798,29 +1820,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -1831,30 +1853,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -1864,59 +1886,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Tier-1 smoke test checklist (formerly #6)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
-smoke-test process and post-deploy verification steps. Shipped via
-PR #81 as part of the 2026-05-10 wave.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Per-module gating (formerly #7)</t>
+          <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
+smoke-test process and post-deploy verification steps. Shipped via
+PR #81 as part of the 2026-05-10 wave.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Per-module gating (formerly #7)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -1931,29 +1953,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -1961,29 +1983,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -1998,33 +2020,6 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
-        </is>
-      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
@@ -2036,18 +2031,45 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>WSLH PT vendor (formerly #15)</t>
+          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>WSLH PT vendor (formerly #15)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2065,38 +2087,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2105,12 +2098,12 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
@@ -2118,15 +2111,14 @@
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
+Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2135,12 +2127,12 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
@@ -2148,35 +2140,65 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2187,7 +2209,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2195,23 +2217,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2222,7 +2244,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2230,23 +2252,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2257,7 +2279,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2266,23 +2288,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2295,7 +2317,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2304,30 +2326,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2336,262 +2358,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H36"/>
+  <autoFilter ref="A1:H37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1175,203 +1175,45 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>License stamp clobbers the §6 lab-identity header/footer and can name the wrong lab</t>
+          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Parked by operator decision 2026-07-16 ("log it, finish PR 4 first"). Not started. No code touched.
+          <t>Open. Not started. Needs a one-line scope confirmation (which master list).
 ---</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>S-M (one shared helper plus a verify script; 8 callsites to re-check)</t>
+          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Medium-High. Every customer-facing workbook currently prints a header and foo...</t>
+          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>licenseCtxFromReq (server/routes.ts:57-61) resolves the licensee lab from resolveActiveLabForRequest, which reads the X-Active-Lab-Id header and silently falls back to the user's default lab inside a bare catch {}. The export body meanwhile resolves the lab from req.scope.labId (the URL path param, set by labScopeMiddleware). Two sources of truth for one document. Separately and unconditionally, applyLicenseToExcelJSWorkbook (shared/licenseExceljs.ts:93-96) *assigns* rather than merges oddHeader/oddFooter on every sheet, so the six lines in the VeritaMap export that carefully set ${labName} CLIA: ${cliaNumber} (routes.ts:13932-13933, 14215-14216, 14224-14225) are dead code, overwritten at routes.ts:14237. §6 rule 3 exists so identity survives cell-level copy-paste; layers (b) and (c) do not currently exist in any shipped workbook.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16 session, PR 4 (#1046) Gate 3 render. Related: feedback_pdf_lab_identity_resolution memory (same resolveActiveLabForRequest swallowed-throw shape).</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Long Excel column headers are clipped, truncating CFR citations mid-string</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Parked by operator decision 2026-07-16. Not started. No code touched.
----</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>S (compute the header row height from the longest wrapped header, or raise th...</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Medium. The VeritaMap workbook currently prints "Reference Range Attestation...</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>CLAUDE.md §6 specifies both "row height 20" for the header row and "wrap text" for cells. Those two rules conflict for any header longer than its column width. Row height 20 renders roughly one line of Calibri 11, so a header that wraps to two or three lines has its tail clipped in print and in PDF export. Confirmed on the live VeritaMap Compliance Map export: header row height is 20.0 with wrapText: true, and the three longest headers are "AMR Attestation (42 CFR 493.1253, per instrument)" (49 chars), "Reference Range Attestation (42 CFR 493.1253)" (45), and "Last Correlation / Method Comparison Date" (41). "Last SOP Review Date" and "AMR High (per instrument)" clip too.</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-16 session, PR 4 (#1046) Gate 3 render. Sibling of [[#43]]; both were found by looking at the rendered workbook, and neither was catchable by the verify scripts.</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>VeritaTrack calendar month cells are not expandable, so hidden tasks are unreachable</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Open. Not started.
----</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>S (1-3 days) — make each month cell open a detail view or expand in place, an...</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>High — a compliance calendar that hides tasks with no way to see them undercu...</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Effort: S (1-3 days) — make each month cell open a detail view or expand in place, and wire the "+N more" affordance to reveal the full task list. The data is already loaded, this is a UI interaction gap, not a data one.
-Importance: High — a compliance calendar that hides tasks with no way to see them undercuts the module's core promise of showing what a lab owes and when.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>VeritaScan line items cannot attach or link evidence (policy or uploaded document)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Open. Not started.
----</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>M (1-2 weeks) — add a per-item evidence link that reuses the VeritaScan URL-p...</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>High — showing evidence per line item is the whole point of a self-inspection...</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Effort: M (1-2 weeks) — add a per-item evidence link that reuses the VeritaScan URL-pointer model rather than storing files: let a line item reference an existing VeritaDC controlled document or an external URL, then surface it as completion evidence.
-Importance: High — showing evidence per line item is the whole point of a self-inspection; without it the scan records a status but cannot show the policy or document that satisfies it.</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23 session, Michael. Recurring request.</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Open. Not started. Needs a one-line scope confirmation (which master list).
----</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Effort: S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility toggle that hides not-applicable or unused sections from a master-list view. Smaller if it is a "hide N/A" filter on the existing VeritaDC master list, larger if it also spans VeritaScan domains.
 Importance: Medium-High — came straight from a live prospect today as an onboarding-friction point; a lab that does not run a service line should not have to wade past its requirements.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-09-23 session, Michael relaying a prospect ask from a demo today.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H20"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1382,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1440,18 +1282,153 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+---</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>C39</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+---</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>C38</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+---</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1463,24 +1440,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1490,24 +1467,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1515,30 +1492,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1549,30 +1526,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1583,29 +1560,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1616,57 +1593,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1679,7 +1656,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1687,109 +1664,109 @@
 ---</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: site-wide search confirmed all surveyor language
 is past-tense, consistent with user's 2021-2025 service. User closed
 the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
 /api/my-studies/export. server/routes.ts line 1491 implements the
 endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: no ghp_* or github_pat_* patterns in current
 SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -1798,29 +1775,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -1831,30 +1808,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -1864,59 +1841,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -1931,29 +1908,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -1961,29 +1938,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -1998,56 +1975,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2065,64 +2042,64 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
 features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaCheck™ already ships the Precision /
 Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
@@ -2130,23 +2107,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
@@ -2154,29 +2131,29 @@
 shipped:</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2187,7 +2164,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2195,23 +2172,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2222,7 +2199,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2230,23 +2207,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2257,7 +2234,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2266,23 +2243,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2295,7 +2272,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2304,30 +2281,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2336,262 +2313,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H36"/>
+  <autoFilter ref="A1:H41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1212,8 +1212,80 @@
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Unify the coverage/competency recurrence into one shared helper (tech debt)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>S (a few hours) - extract "latest study/assessment -&gt; status / nextDueOn / ov...</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Low - the three paths duplicate the +6-month / signed-resets-to-missing logic...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Effort: S (a few hours) - extract "latest study/assessment -&gt; status / nextDueOn / overdue" into one helper used by method comparison, cal-ver/linearity, and the competency owed derivation.
+Importance: Low - the three paths duplicate the +6-month / signed-resets-to-missing logic. They agree today (verified), but a shared helper prevents future drift and settles the dateless-signed edge in one place. No user-facing impact; studies.date is NOT NULL so the one known divergence is unreachable in practice.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24 session, surfaced during the coverage-recurrence build. No live defect; hygiene.
+---</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Competency "assessed this cycle" uses a flat 365-day window</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>S-M - anchor the coverage-map "assessed this cycle" to the person's actual CL...</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Medium - in an employee's first year the semiannual windows differ from a fla...</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Effort: S-M - anchor the coverage-map "assessed this cycle" to the person's actual CLIA cadence (semiannual in year 1 per 42 CFR 493.1451(b)(8), annual thereafter) from staff_competency_schedules, instead of the v1 flat 365-day lookback.
+Importance: Medium - in an employee's first year the semiannual windows differ from a flat annual window, so a first-year assessment could read as current slightly longer or shorter than the true cadence. Fine for the common annual case; refine for year-1 accuracy.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 session, VeritaComp coverage map (#48 Phase 3) v1 simplification, noted in PR #1319.
+---</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1224,7 +1296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1282,12 +1354,12 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -1295,12 +1367,12 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1309,12 +1381,12 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
@@ -1322,12 +1394,12 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1336,12 +1408,12 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -1349,12 +1421,12 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1363,12 +1435,12 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -1376,12 +1448,12 @@
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1390,12 +1462,12 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -1403,12 +1475,12 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1417,18 +1489,99 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+---</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1440,24 +1593,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1467,24 +1620,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1492,30 +1645,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1526,30 +1679,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1560,29 +1713,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1593,57 +1746,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1656,7 +1809,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1664,109 +1817,109 @@
 ---</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 5, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -1775,29 +1928,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -1808,30 +1961,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -1841,59 +1994,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -1908,29 +2061,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -1938,29 +2091,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -1975,56 +2128,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2042,64 +2195,64 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
 features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaCheck™ already ships the Precision /
 Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
@@ -2107,23 +2260,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
@@ -2131,29 +2284,29 @@
 shipped:</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2164,7 +2317,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2172,23 +2325,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2199,7 +2352,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2207,23 +2360,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2234,7 +2387,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2243,23 +2396,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2272,7 +2425,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2281,30 +2434,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2313,262 +2466,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H41"/>
+  <autoFilter ref="A1:H44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1095,40 +1095,38 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (CLAUDE.md §2)</t>
+          <t>Outbound demo-invite messaging campaign to 1st-degree LinkedIn contacts</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CLOSED 2026-06-13. All 8 high-stakes backfill scripts landed (the
-strike-throughs above); see C30. Pre- vs post-COLA: indifferent.
+          <t>Parked. Plan documented. Implementation deferred until trigger conditions met.
 ---</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>L (8 backfill scripts, each ~2-4 hours, total ~3-5 working days if done as on...</t>
+          <t>L (1 week prep + 4-6 weeks of staged sends)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Medium-High. Procedural-debt cleanup against a NON-NEGOTIABLE convention. CLA...</t>
+          <t>High. Converts existing warm network (~2,500 1st-degree contacts and growing...</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Effort: L (8 backfill scripts, each ~2-4 hours, total ~3-5 working days if done as one focused sweep).
-Importance: Medium-High. Procedural-debt cleanup against a NON-NEGOTIABLE convention. CLAUDE.md §2 verify-*.js: every math/logic change ships with a paired script that exercises every meaningful branch. The audit run on 2026-06-02 found 31 of 35 math/logic commits in the last 90 days violated the convention. Some are exempt (renames, citation swaps, copy changes) but at least 8 introduced new math or fixed math defects and should have shipped with verification.</t>
+          <t>A staged outbound DM campaign walking Michael's 1st-degree LinkedIn contacts through tier-segmented demo invitations for VeritaAssure. Goal: convert warmest contacts into demo conversations first, then chain into trials and paid subscriptions. Separate pipeline from COLA cohort follow-up and from content-driven inbound; all three feed the same demo funnel but originate from different warmth sources.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>scripts/audit_verify_script_coverage.py output, run 2026-06-02. Captured as the formal lookback that surfaced the gap.</t>
+          <t>2026-06-04 session, after weekly LinkedIn invite batch completion (80 sent, cap hit at #84 Victoria Allen).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1136,38 +1134,39 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Outbound demo-invite messaging campaign to 1st-degree LinkedIn contacts</t>
+          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Parked. Plan documented. Implementation deferred until trigger conditions met.
+          <t>Open. Not started. Needs a one-line scope confirmation (which master list).
 ---</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>L (1 week prep + 4-6 weeks of staged sends)</t>
+          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>High. Converts existing warm network (~2,500 1st-degree contacts and growing...</t>
+          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>A staged outbound DM campaign walking Michael's 1st-degree LinkedIn contacts through tier-segmented demo invitations for VeritaAssure. Goal: convert warmest contacts into demo conversations first, then chain into trials and paid subscriptions. Separate pipeline from COLA cohort follow-up and from content-driven inbound; all three feed the same demo funnel but originate from different warmth sources.</t>
+          <t>Effort: S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility toggle that hides not-applicable or unused sections from a master-list view. Smaller if it is a "hide N/A" filter on the existing VeritaDC master list, larger if it also spans VeritaScan domains.
+Importance: Medium-High — came straight from a live prospect today as an onboarding-friction point; a lab that does not run a service line should not have to wade past its requirements.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04 session, after weekly LinkedIn invite batch completion (80 sent, cap hit at #84 Victoria Allen).</t>
+          <t>2026-09-23 session, Michael relaying a prospect ask from a demo today.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
@@ -1175,39 +1174,35 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Open. Not started. Needs a one-line scope confirmation (which master list).
----</t>
-        </is>
-      </c>
+          <t>Unify the coverage/competency recurrence into one shared helper (tech debt)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
+          <t>S (a few hours) - extract "latest study/assessment -&gt; status / nextDueOn / ov...</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
+          <t>Low - the three paths duplicate the +6-month / signed-resets-to-missing logic...</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Effort: S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility toggle that hides not-applicable or unused sections from a master-list view. Smaller if it is a "hide N/A" filter on the existing VeritaDC master list, larger if it also spans VeritaScan domains.
-Importance: Medium-High — came straight from a live prospect today as an onboarding-friction point; a lab that does not run a service line should not have to wade past its requirements.</t>
+          <t>Effort: S (a few hours) - extract "latest study/assessment -&gt; status / nextDueOn / overdue" into one helper used by method comparison, cal-ver/linearity, and the competency owed derivation.
+Importance: Low - the three paths duplicate the +6-month / signed-resets-to-missing logic. They agree today (verified), but a shared helper prevents future drift and settles the dateless-signed edge in one place. No user-facing impact; studies.date is NOT NULL so the one known divergence is unreachable in practice.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael relaying a prospect ask from a demo today.</t>
+          <t>2026-09-24 session, surfaced during the coverage-recurrence build. No live defect; hygiene.
+---</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1215,77 +1210,41 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Unify the coverage/competency recurrence into one shared helper (tech debt)</t>
+          <t>Competency "assessed this cycle" uses a flat 365-day window</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>S (a few hours) - extract "latest study/assessment -&gt; status / nextDueOn / ov...</t>
+          <t>S-M - anchor the coverage-map "assessed this cycle" to the person's actual CL...</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Low - the three paths duplicate the +6-month / signed-resets-to-missing logic...</t>
+          <t>Medium - in an employee's first year the semiannual windows differ from a fla...</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Effort: S (a few hours) - extract "latest study/assessment -&gt; status / nextDueOn / overdue" into one helper used by method comparison, cal-ver/linearity, and the competency owed derivation.
-Importance: Low - the three paths duplicate the +6-month / signed-resets-to-missing logic. They agree today (verified), but a shared helper prevents future drift and settles the dateless-signed edge in one place. No user-facing impact; studies.date is NOT NULL so the one known divergence is unreachable in practice.</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, surfaced during the coverage-recurrence build. No live defect; hygiene.
----</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Competency "assessed this cycle" uses a flat 365-day window</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>S-M - anchor the coverage-map "assessed this cycle" to the person's actual CL...</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Medium - in an employee's first year the semiannual windows differ from a fla...</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Effort: S-M - anchor the coverage-map "assessed this cycle" to the person's actual CLIA cadence (semiannual in year 1 per 42 CFR 493.1451(b)(8), annual thereafter) from staff_competency_schedules, instead of the v1 flat 365-day lookback.
 Importance: Medium - in an employee's first year the semiannual windows differ from a flat annual window, so a first-year assessment could read as current slightly longer or shorter than the true cadence. Fine for the common annual case; refine for year-1 accuracy.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>2026-09-24 session, VeritaComp coverage map (#48 Phase 3) v1 simplification, noted in PR #1319.
 ---</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1296,7 +1255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1354,12 +1313,12 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -1367,12 +1326,12 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -1381,12 +1340,12 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
@@ -1394,12 +1353,12 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1408,12 +1367,12 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -1421,12 +1380,12 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1435,12 +1394,12 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -1448,12 +1407,12 @@
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1462,12 +1421,12 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -1475,12 +1434,12 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1489,12 +1448,12 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -1502,12 +1461,12 @@
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1516,12 +1475,12 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -1529,12 +1488,12 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -1543,12 +1502,12 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
@@ -1556,7 +1515,7 @@
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1570,18 +1529,45 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1593,24 +1579,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1620,24 +1606,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1645,30 +1631,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1679,30 +1665,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1713,29 +1699,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1746,37 +1732,9 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
----</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
-23 years" as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1785,18 +1743,46 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
+23 years" as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 14, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1809,7 +1795,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1817,46 +1803,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -1864,14 +1821,14 @@
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
+          <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1880,12 +1837,12 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -1893,13 +1850,14 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>session 299e9a73, ~2026-04-28.
+          <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1908,18 +1866,46 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -1928,29 +1914,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -1961,30 +1947,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -1994,59 +1980,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Tier-1 smoke test checklist (formerly #6)</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
-smoke-test process and post-deploy verification steps. Shipped via
-PR #81 as part of the 2026-05-10 wave.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Per-module gating (formerly #7)</t>
+          <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
+smoke-test process and post-deploy verification steps. Shipped via
+PR #81 as part of the 2026-05-10 wave.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Per-module gating (formerly #7)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2061,29 +2047,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2091,29 +2077,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2128,33 +2114,6 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
@@ -2166,18 +2125,45 @@
     <row r="29" ht="90" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>WSLH PT vendor (formerly #15)</t>
+          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>WSLH PT vendor (formerly #15)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2195,38 +2181,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2235,12 +2192,12 @@
     <row r="31" ht="90" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
@@ -2248,15 +2205,14 @@
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
+Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2265,12 +2221,12 @@
     <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
@@ -2278,35 +2234,65 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2317,7 +2303,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2325,23 +2311,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2352,7 +2338,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2360,23 +2346,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2387,7 +2373,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2396,23 +2382,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2425,7 +2411,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2434,30 +2420,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2466,262 +2452,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H44"/>
+  <autoFilter ref="A1:H45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1174,77 +1174,41 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Unify the coverage/competency recurrence into one shared helper (tech debt)</t>
+          <t>Competency "assessed this cycle" uses a flat 365-day window</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>S (a few hours) - extract "latest study/assessment -&gt; status / nextDueOn / ov...</t>
+          <t>S-M - anchor the coverage-map "assessed this cycle" to the person's actual CL...</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Low - the three paths duplicate the +6-month / signed-resets-to-missing logic...</t>
+          <t>Medium - in an employee's first year the semiannual windows differ from a fla...</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Effort: S (a few hours) - extract "latest study/assessment -&gt; status / nextDueOn / overdue" into one helper used by method comparison, cal-ver/linearity, and the competency owed derivation.
-Importance: Low - the three paths duplicate the +6-month / signed-resets-to-missing logic. They agree today (verified), but a shared helper prevents future drift and settles the dateless-signed edge in one place. No user-facing impact; studies.date is NOT NULL so the one known divergence is unreachable in practice.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, surfaced during the coverage-recurrence build. No live defect; hygiene.
----</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Competency "assessed this cycle" uses a flat 365-day window</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>S-M - anchor the coverage-map "assessed this cycle" to the person's actual CL...</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Medium - in an employee's first year the semiannual windows differ from a fla...</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Effort: S-M - anchor the coverage-map "assessed this cycle" to the person's actual CLIA cadence (semiannual in year 1 per 42 CFR 493.1451(b)(8), annual thereafter) from staff_competency_schedules, instead of the v1 flat 365-day lookback.
 Importance: Medium - in an employee's first year the semiannual windows differ from a flat annual window, so a first-year assessment could read as current slightly longer or shorter than the true cadence. Fine for the common annual case; refine for year-1 accuracy.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-09-24 session, VeritaComp coverage map (#48 Phase 3) v1 simplification, noted in PR #1319.
 ---</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1255,7 +1219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1313,12 +1277,12 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -1326,12 +1290,12 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -1340,12 +1304,12 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
@@ -1353,12 +1317,12 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -1367,12 +1331,12 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -1380,12 +1344,12 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -1394,12 +1358,12 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -1407,12 +1371,12 @@
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1421,12 +1385,12 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -1434,12 +1398,12 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1448,12 +1412,12 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -1461,12 +1425,12 @@
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1475,12 +1439,12 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -1488,12 +1452,12 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1502,12 +1466,12 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
@@ -1515,12 +1479,12 @@
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1529,12 +1493,12 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -1542,12 +1506,12 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -1556,18 +1520,72 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1579,24 +1597,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1606,24 +1624,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1631,30 +1649,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1665,30 +1683,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1699,29 +1717,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1732,57 +1750,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1795,7 +1813,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1803,75 +1821,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
@@ -1879,8 +1839,9 @@
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1894,18 +1855,75 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 5, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -1914,29 +1932,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -1947,30 +1965,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -1980,59 +1998,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2047,29 +2065,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2077,29 +2095,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2114,56 +2132,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2181,68 +2199,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
----</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
 ---</t>
         </is>
       </c>
@@ -2251,12 +2210,12 @@
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
@@ -2264,35 +2223,94 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the feature set ships today.
+---</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>PAL studies guided workflow (formerly #23)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2303,7 +2321,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2311,23 +2329,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2338,7 +2356,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2346,23 +2364,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2373,7 +2391,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2382,23 +2400,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2411,7 +2429,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2420,30 +2438,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2452,262 +2470,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H45"/>
+  <autoFilter ref="A1:H47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Parked 2026-05-26 with a one-line scope intent. Michael indicated he will walk through the requirements in more detail in a follow-up conversation. Do not start building until that walkthrough happ...</t>
+          <t>Scoped, not started (updated 2026-09-28). Now lands in VeritaResponse per Michael's direction above; the earlier "new standalone module" framing is superseded. Do not start building until Michael g...</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1207,8 +1207,94 @@
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>VeritaTrack task owner + owner-scoped reminder routing</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Open, not started. Placeholder pending build. Open questions: is the owner a staff_employee or a seat user, and how are reminder recipients currently chosen.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>S-M (1-3 days to ~1.5 weeks) — add an owner on a VeritaTrack task, selectable...</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Medium — cuts reminder-email noise so people only get the tasks that are thei...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Michael, verbatim (2026-09-28): "In veritatask, we should be able to assign an owner from staff that are built, then in the reminder section, we should be able to designate reminder emails only to the owner. The hem person does not need the chemistry reminders, etc." Module note: there is no VeritaTask module in the codebase; the task/reminder surface is VeritaTrack (client/src/pages/VeritaTrackAppPage.tsx), so this lands there. Today VeritaTrack tasks are not owned by a specific staff member and reminder emails are not recipient-scoped to an owner. The build adds (a) an owner selector on each task drawn from the lab's VeritaStaff roster, and (b) a reminder setting that routes the reminder email to only that owner. Confirm the current reminder recipient model before sizing.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28 session, Michael "for later (placeholder)" optimization #1 (relaying from the Lab Members / VeritaAssure screens).</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Post-COLA. No customer urgency.
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Medical Director seat via account-grant dropdown (designate / transfer MD)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Open, not started. Placeholder. Confirm the current MD-seat assignment path and the one-MD-per-location enforcement point before sizing.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>S-M (1-3 days to ~1.5 weeks) — move MD-seat assignment onto the same per-memb...</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Medium-High — the MD seat is a recurring friction point (Georgetown, SCAHC MD...</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Michael, verbatim (2026-09-28): "The way we are doing the medical director seat is silly. Why not just use the account grant dropdown to give a medical director seat. If the person is already in, then we should just be able to grant the medical director seat the same way we promote people to admin or reduce them to staff as long as we only have 1 per location. Maybe do another block like the transfer ownership block as 'designate medical director or transfer medical director'." So: fold the MD seat into the existing member role dropdown (Admin / Staff / ... + Medical Director) with a single-MD-per-lab constraint, and add a dedicated designate-or-transfer-MD block that mirrors the transfer-ownership UX for changing the MD. Cross-ref [[project_medical_director_designation]] and the seat model.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 session, Michael "for later (placeholder)" optimization #3 (relaying from the Lab Members screen).</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Post-COLA. No customer urgency.
+---</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -564,6 +564,12 @@
         <is>
           <t>Pre-COLA. May 6-8 conference; Saturday + Sunday +
 Monday available before the booth.
+---
+_(item #17 reclassified to CLOSED 2026-09-28; VeritaResponse shipped and live, see C48 below)_
+---
+_(item #18 closed 2026-09-28; all phases shipped, see C47 below)_
+---
+_(item #22 closed 2026-05-28; see C26 below)_
 ---</t>
         </is>
       </c>
@@ -571,130 +577,30 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>New flagship module: VeritaResponse (post-survey deficiency response)</t>
+          <t>Acquire CAP MOL (Molecular) checklist to verify 2 pending entries</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BUILT and LIVE (this entry was stale). VeritaResponse shipped as a
-full module: findings table + CRUD + lifecycle, due-date computation, 30/60/90-day
-effectiveness monitoring (wave C3), cross-modu...</t>
+          <t>Open, blocks on operator obtaining the MOL checklist.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>XL (6+ weeks; flagship-scale)</t>
+          <t>N/A (operator action — ~1 hour of code work once the file is in hand)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>High — booth-validated demand at COLA Nashville; no existing module covers po...</t>
+          <t>Low — two entries total; low traffic; only matters when a customer cites a MO...</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>A new module that helps a lab manage the full lifecycle of
-responding to inspection deficiencies (CAP, TJC, COLA, CMS-2567,
-AABB), from intake of a citation through corrective-action authoring,
-supporting-evidence collection, submission tracking, and 30/60/90-day
-effectiveness verification. Pairs with VeritaCheck (find gaps before
-they cite you) and VeritaPT (prove your PT covers your menu) to
-complete the compliance lifecycle: prevent → respond → prove.</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-07 conference user request, COLA Nashville. User
-asked for thoughts and recommendations on adding a deficiency-response
-module. Online research conducted same session covering CAP, TJC,
-COLA, CMS-2567, AABB. URLs cited above.</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Post-COLA. Build is multi-week regardless;
-zero rationale for any code change before the conference ends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Unregulated analyte / Alternative Assessment (AAA) coverage — cross-module gap</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL as of 2026-05-10.
-- Phase 1 (VeritaScan AAA sub-block, items 169-173) CLOSED via
- PR #78 (client/src/lib/veritaScanData.ts). Item #46 retained as
- AAA gateway; new 5-item block uses ids 16...</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>S (1-3 days once #17 ships) for Phase 3 — Phases 1 and 2 already shipped.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Medium — closes a real workflow loop (AAA failure → VeritaResponse finding) b...</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Effort: S (1-3 days once #17 ships) for Phase 3 — Phases 1 and 2 already shipped.
-Importance: Medium — closes a real workflow loop (AAA failure → VeritaResponse finding) but only matters once #17 exists.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Post-COLA. Phase 1 and Phase 2 data layer
-shipped 2026-05-10.
----
-_(item #22 closed 2026-05-28; see C26 below)_
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Acquire CAP MOL (Molecular) checklist to verify 2 pending entries</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Open, blocks on operator obtaining the MOL checklist.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>N/A (operator action — ~1 hour of code work once the file is in hand)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Low — two entries total; low traffic; only matters when a customer cites a MO...</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>PR #108 left 2 entries in server/capRequirements.ts
 flagged as unverified because the operator does not hold the CAP MOL
@@ -708,48 +614,48 @@
 The MOL module's MAS xlsx is the only one missing from that set.</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>PR #108 commit 92f9573 (closed via merge 2026-05-11),
 audit findings.</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Post-COLA. Two entries; low traffic.
 ---</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Acquire AABB Standards 35th edition + current COLA Accreditation Manual for exhaustive citation verification</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Open, blocks on operator obtaining the gated accreditor
 manuals. Until then, AABB / COLA citations are best-effort against
 the public-source compilations.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A (operator action — ~1-2 days of audit re-run once the manuals are held)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>High — gates #5 from reaching "exhaustively verified" status for AABB and COLA.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>The 2026-05-11 QC audit found that VeritaScan, cfrRequirements
 cross-refs, and colaRequirements.ts cite about 180 AABB and COLA codes
@@ -769,14 +675,14 @@
  does not enumerate fully.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 QC/QA audit, documented in
 OneDrive\Lab\Regulatory\aaa Truth Master Document\PROVENANCE.md
 "Audit-coverage limits" section.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. Operator-side action item, no code
 work pending until the source documents land.
@@ -784,34 +690,34 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>VeritaStock barcode scanning (full mobile scan flow)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Parked pending first paid commitment.
 ---</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>L (12 working days, ~3 weeks calendar)</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>High — strategic moat vs Unity Lab Services ($30K+/yr); presold as included o...</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>The remaining barcode-scanning build for VeritaStock, scoped
 during the 2026-05-20 Pfizer follow-up discussion. Order-now reorder
@@ -820,7 +726,7 @@
 Services-class inventory product.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>2026-05-20 Pfizer follow-up session, after the order-now
 reorder document shipped (PR #286). Strategic decision documented in
@@ -831,31 +737,31 @@
 barcode scanning waits on revenue...</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Plain-language summary layer for verbatim CFR citations</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>M (multi-day content authoring across 96 Master List rows if redesigned corre...</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Medium — director readability win; no customer urgency.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>server/cfrRequirements.ts carries verbatim eCFR text in
 the description field (PR #301 closed #26). The verbatim text is
@@ -864,8 +770,8 @@
 director read faster.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. No customer urgency. Operator
 has not yet authorized a redesign attempt as of 2026-05-21.
@@ -873,29 +779,29 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Lab leader community / forum (paid subscription idea)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>XL (ongoing operational commitment, not a build) as paid; S (a few days to sp...</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Low as paid product (SWOT verdict: don't build); Medium as free lead-funnel a...</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Operator-floated 2026-05-22: a vetted online forum for
 laboratory leaders (directors, managers, supervisors). Pricing as
@@ -908,8 +814,8 @@
 lab-leader water cooler.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Post-COLA. No customer urgency.
 ---
@@ -920,39 +826,39 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>New module: laboratory non-conforming event documentation</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Scoped, not started (updated 2026-09-28). Now lands in VeritaResponse per Michael's direction above; the earlier "new standalone module" framing is superseded. Do not start building until Michael g...</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>L (initial estimate, pending Michael's scope walkthrough — likely new DB tabl...</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>High — every accredited laboratory (TJC, CAP, COLA, AABB) has to document non...</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Build a module to document laboratory non-conforming events (NCEs). Surfaces a lab needs to capture include specimen rejection, temperature excursions, reagent issues, equipment failures, result-reporting errors, transcription errors, lost specimens, contamination events, and similar quality incidents. Full scope, target accreditor mapping, terminology preference (NCE / NCR / event / incident / occurrence), and how it should relate to the existing VeritaQC corrective-action engine and VeritaResponse deficiency tracker are TBD pending Michael's scope walkthrough.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. No customer urgency yet, but high strategic value once defined — closes a real gap every lab has and that no other Verita module currently serves.
 ---
@@ -961,76 +867,76 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Screen-capture video: VeritaCheck method comparison in 60 seconds</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Open. Re-parked 2026-05-27 (originally PR #117, abandoned with merge conflicts then closed-and-re-authored at current numbering). Pending operator decision on whether to record this themselves or p...</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>S for agent prep (storyboard / pre-fill / captions / checklist); ~1 hour of o...</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Medium — operator selected this as the highest-impact positioning artifact du...</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>30-60 second screen recording demonstrating the "experienced lab tech figures it out in seconds" claim. From blank method-comparison study to completed PDF, no voiceover, no narration, visible cursor motion. Embed autoplay-muted on the marketing site, include in conference follow-up emails.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>2026-05-12 conversation. Michael selected the screen-cap video as the highest-impact positioning artifact, then asked the agent to record it. Agent does not have screen-recording capability; option parked rather than fudged.</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Post-COLA, conference-driven.
 ---</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>MediaLab parity hardening (VeritaPolicy approval workflow depth)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Open, customer-triggered. No urgency until a prospect specifically asks for one of the listed depth items.</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>L (1-2 weeks for the high-value items; each independent feature is M)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Medium-High — the C29 build shipped the surface MediaLab markets but depth is...</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>The VeritaPolicy approval workflow build (C29, 2026-05-29) hit roughly 60-70% MediaLab feature surface. The following gaps remain when comparing against an enterprise MediaLab Document Control deployment:
 - Quizzes on attestations. Schema columns quiz_score and quiz_total_questions exist on policy_attestations but the quiz authoring + presentation UI was scoped out of Phase 4. MediaLab labs use 5-10 multiple-choice questions per policy to confirm comprehension, not just attestation. Adds compliance defensibility.
@@ -1040,54 +946,133 @@
 - In-browser DOCX editing. MediaLab has a structured editor that creates a Table of Contents from headings. We treat documents as...</t>
         </is>
       </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29 QA pass after C29 shipped (qa-policy-build.js + qa-policy-ui.js: 54/54 happy path verified). Honest depth assessment surfaced by Michael's "how confident are you" question — see C29 entry for full QA receipts.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Post-COLA. Defensive against MediaLab in head-to-head sales calls.
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>VeritaQC Import Phase A: human-in-the-loop Gate 3 click-through (deferred)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Open, awaiting Michael's 5-minute click test. Will move task #77 to completed only after he reports the user-visible result.
+---</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>XS (~5 minutes of Michael's time on a live URL).</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Low. Backend contract is fully verified via 35/35 passing offline contract ch...</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Effort: XS (~5 minutes of Michael's time on a live URL).
+Importance: Low. Backend contract is fully verified via 35/35 passing offline contract checks (scripts/verify-veritaqc-import.js) plus three live-API smoke checks against prod (candidates, preview, mappings PUT/GET) on Riverside Regional with seed lot SEED-1780436709094 (18 Glucose results). The browser-driven click was not run because Claude-in-Chrome's renderer froze repeatedly on the Radix Select inside VeritaCheckPage, not on Phase A code itself. Risk of a UX bug surviving to a customer is small but not zero.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>task #77 stalled at Gate 3 step 8 on 2026-06-02. PR #500 squash-merged at commit 17a91ff, prod /api/health confirmed ACTIVE on that commit at 20:43 UTC.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Outbound demo-invite messaging campaign to 1st-degree LinkedIn contacts</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Parked. Plan documented. Implementation deferred until trigger conditions met.
+---</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>L (1 week prep + 4-6 weeks of staged sends)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>High. Converts existing warm network (~2,500 1st-degree contacts and growing...</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>A staged outbound DM campaign walking Michael's 1st-degree LinkedIn contacts through tier-segmented demo invitations for VeritaAssure. Goal: convert warmest contacts into demo conversations first, then chain into trials and paid subscriptions. Separate pipeline from COLA cohort follow-up and from content-driven inbound; all three feed the same demo funnel but originate from different warmth sources.</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29 QA pass after C29 shipped (qa-policy-build.js + qa-policy-ui.js: 54/54 happy path verified). Honest depth assessment surfaced by Michael's "how confident are you" question — see C29 entry for full QA receipts.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Post-COLA. Defensive against MediaLab in head-to-head sales calls.
----</t>
-        </is>
-      </c>
+          <t>2026-06-04 session, after weekly LinkedIn invite batch completion (80 sent, cap hit at #84 Victoria Allen).</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VeritaQC Import Phase A: human-in-the-loop Gate 3 click-through (deferred)</t>
+          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Open, awaiting Michael's 5-minute click test. Will move task #77 to completed only after he reports the user-visible result.
+          <t>Open. Not started. Needs a one-line scope confirmation (which master list).
 ---</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>XS (~5 minutes of Michael's time on a live URL).</t>
+          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Low. Backend contract is fully verified via 35/35 passing offline contract ch...</t>
+          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Effort: XS (~5 minutes of Michael's time on a live URL).
-Importance: Low. Backend contract is fully verified via 35/35 passing offline contract checks (scripts/verify-veritaqc-import.js) plus three live-API smoke checks against prod (candidates, preview, mappings PUT/GET) on Riverside Regional with seed lot SEED-1780436709094 (18 Glucose results). The browser-driven click was not run because Claude-in-Chrome's renderer froze repeatedly on the Radix Select inside VeritaCheckPage, not on Phase A code itself. Risk of a UX bug surviving to a customer is small but not zero.</t>
+          <t>Effort: S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility toggle that hides not-applicable or unused sections from a master-list view. Smaller if it is a "hide N/A" filter on the existing VeritaDC master list, larger if it also spans VeritaScan domains.
+Importance: Medium-High — came straight from a live prospect today as an onboarding-friction point; a lab that does not run a service line should not have to wade past its requirements.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>task #77 stalled at Gate 3 step 8 on 2026-06-02. PR #500 squash-merged at commit 17a91ff, prod /api/health confirmed ACTIVE on that commit at 20:43 UTC.</t>
+          <t>2026-09-23 session, Michael relaying a prospect ask from a demo today.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
@@ -1095,38 +1080,35 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Outbound demo-invite messaging campaign to 1st-degree LinkedIn contacts</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Parked. Plan documented. Implementation deferred until trigger conditions met.
----</t>
-        </is>
-      </c>
+          <t>Competency "assessed this cycle" uses a flat 365-day window</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>L (1 week prep + 4-6 weeks of staged sends)</t>
+          <t>S-M - anchor the coverage-map "assessed this cycle" to the person's actual CL...</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>High. Converts existing warm network (~2,500 1st-degree contacts and growing...</t>
+          <t>Medium - in an employee's first year the semiannual windows differ from a fla...</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>A staged outbound DM campaign walking Michael's 1st-degree LinkedIn contacts through tier-segmented demo invitations for VeritaAssure. Goal: convert warmest contacts into demo conversations first, then chain into trials and paid subscriptions. Separate pipeline from COLA cohort follow-up and from content-driven inbound; all three feed the same demo funnel but originate from different warmth sources.</t>
+          <t>Effort: S-M - anchor the coverage-map "assessed this cycle" to the person's actual CLIA cadence (semiannual in year 1 per 42 CFR 493.1451(b)(8), annual thereafter) from staff_competency_schedules, instead of the v1 flat 365-day lookback.
+Importance: Medium - in an employee's first year the semiannual windows differ from a flat annual window, so a first-year assessment could read as current slightly longer or shorter than the true cadence. Fine for the common annual case; refine for year-1 accuracy.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 session, after weekly LinkedIn invite batch completion (80 sent, cap hit at #84 Victoria Allen).</t>
+          <t>2026-09-24 session, VeritaComp coverage map (#48 Phase 3) v1 simplification, noted in PR #1319.
+---</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1134,167 +1116,91 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
+          <t>VeritaTrack task owner + owner-scoped reminder routing</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Open. Not started. Needs a one-line scope confirmation (which master list).
----</t>
+          <t>Open, not started. Placeholder pending build. Open questions: is the owner a staff_employee or a seat user, and how are reminder recipients currently chosen.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
+          <t>S-M (1-3 days to ~1.5 weeks) — add an owner on a VeritaTrack task, selectable...</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
+          <t>Medium — cuts reminder-email noise so people only get the tasks that are thei...</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Effort: S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility toggle that hides not-applicable or unused sections from a master-list view. Smaller if it is a "hide N/A" filter on the existing VeritaDC master list, larger if it also spans VeritaScan domains.
-Importance: Medium-High — came straight from a live prospect today as an onboarding-friction point; a lab that does not run a service line should not have to wade past its requirements.</t>
+          <t>Michael, verbatim (2026-09-28): "In veritatask, we should be able to assign an owner from staff that are built, then in the reminder section, we should be able to designate reminder emails only to the owner. The hem person does not need the chemistry reminders, etc." Module note: there is no VeritaTask module in the codebase; the task/reminder surface is VeritaTrack (client/src/pages/VeritaTrackAppPage.tsx), so this lands there. Today VeritaTrack tasks are not owned by a specific staff member and reminder emails are not recipient-scoped to an owner. The build adds (a) an owner selector on each task drawn from the lab's VeritaStaff roster, and (b) a reminder setting that routes the reminder email to only that owner. Confirm the current reminder recipient model before sizing.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael relaying a prospect ask from a demo today.</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
+          <t>2026-09-28 session, Michael "for later (placeholder)" optimization #1 (relaying from the Lab Members / VeritaAssure screens).</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Post-COLA. No customer urgency.
+---</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" uses a flat 365-day window</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>Medical Director seat via account-grant dropdown (designate / transfer MD)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Open, not started. Placeholder. Confirm the current MD-seat assignment path and the one-MD-per-location enforcement point before sizing.</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>S-M - anchor the coverage-map "assessed this cycle" to the person's actual CL...</t>
+          <t>S-M (1-3 days to ~1.5 weeks) — move MD-seat assignment onto the same per-memb...</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Medium - in an employee's first year the semiannual windows differ from a fla...</t>
+          <t>Medium-High — the MD seat is a recurring friction point (Georgetown, SCAHC MD...</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Effort: S-M - anchor the coverage-map "assessed this cycle" to the person's actual CLIA cadence (semiannual in year 1 per 42 CFR 493.1451(b)(8), annual thereafter) from staff_competency_schedules, instead of the v1 flat 365-day lookback.
-Importance: Medium - in an employee's first year the semiannual windows differ from a flat annual window, so a first-year assessment could read as current slightly longer or shorter than the true cadence. Fine for the common annual case; refine for year-1 accuracy.</t>
+          <t>Michael, verbatim (2026-09-28): "The way we are doing the medical director seat is silly. Why not just use the account grant dropdown to give a medical director seat. If the person is already in, then we should just be able to grant the medical director seat the same way we promote people to admin or reduce them to staff as long as we only have 1 per location. Maybe do another block like the transfer ownership block as 'designate medical director or transfer medical director'." So: fold the MD seat into the existing member role dropdown (Admin / Staff / ... + Medical Director) with a single-MD-per-lab constraint, and add a dedicated designate-or-transfer-MD block that mirrors the transfer-ownership UX for changing the MD. Cross-ref [[project_medical_director_designation]] and the seat model.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, VeritaComp coverage map (#48 Phase 3) v1 simplification, noted in PR #1319.
----</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>VeritaTrack task owner + owner-scoped reminder routing</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Open, not started. Placeholder pending build. Open questions: is the owner a staff_employee or a seat user, and how are reminder recipients currently chosen.</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>S-M (1-3 days to ~1.5 weeks) — add an owner on a VeritaTrack task, selectable...</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Medium — cuts reminder-email noise so people only get the tasks that are thei...</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Michael, verbatim (2026-09-28): "In veritatask, we should be able to assign an owner from staff that are built, then in the reminder section, we should be able to designate reminder emails only to the owner. The hem person does not need the chemistry reminders, etc." Module note: there is no VeritaTask module in the codebase; the task/reminder surface is VeritaTrack (client/src/pages/VeritaTrackAppPage.tsx), so this lands there. Today VeritaTrack tasks are not owned by a specific staff member and reminder emails are not recipient-scoped to an owner. The build adds (a) an owner selector on each task drawn from the lab's VeritaStaff roster, and (b) a reminder setting that routes the reminder email to only that owner. Confirm the current reminder recipient model before sizing.</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28 session, Michael "for later (placeholder)" optimization #1 (relaying from the Lab Members / VeritaAssure screens).</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+          <t>2026-09-28 session, Michael "for later (placeholder)" optimization #3 (relaying from the Lab Members screen).</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. No customer urgency.
 ---</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Medical Director seat via account-grant dropdown (designate / transfer MD)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Open, not started. Placeholder. Confirm the current MD-seat assignment path and the one-MD-per-location enforcement point before sizing.</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>S-M (1-3 days to ~1.5 weeks) — move MD-seat assignment onto the same per-memb...</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Medium-High — the MD seat is a recurring friction point (Georgetown, SCAHC MD...</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Michael, verbatim (2026-09-28): "The way we are doing the medical director seat is silly. Why not just use the account grant dropdown to give a medical director seat. If the person is already in, then we should just be able to grant the medical director seat the same way we promote people to admin or reduce them to staff as long as we only have 1 per location. Maybe do another block like the transfer ownership block as 'designate medical director or transfer medical director'." So: fold the MD seat into the existing member role dropdown (Admin / Staff / ... + Medical Director) with a single-MD-per-lab constraint, and add a dedicated designate-or-transfer-MD block that mirrors the transfer-ownership UX for changing the MD. Cross-ref [[project_medical_director_designation]] and the seat model.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 session, Michael "for later (placeholder)" optimization #3 (relaying from the Lab Members screen).</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Post-COLA. No customer urgency.
----</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1305,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1363,66 +1269,64 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -1430,12 +1334,12 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -1444,12 +1348,12 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -1457,12 +1361,12 @@
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -1471,12 +1375,12 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -1484,12 +1388,12 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -1498,12 +1402,12 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -1511,12 +1415,12 @@
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1525,12 +1429,12 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -1538,12 +1442,12 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1552,12 +1456,12 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
@@ -1565,12 +1469,12 @@
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1579,12 +1483,12 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -1592,12 +1496,12 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1606,12 +1510,12 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
@@ -1619,12 +1523,12 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1633,12 +1537,12 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -1646,12 +1550,12 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -1660,18 +1564,72 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1683,24 +1641,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1710,24 +1668,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1735,30 +1693,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1769,30 +1727,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1803,29 +1761,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1836,57 +1794,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1899,7 +1857,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1907,75 +1865,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
@@ -1983,8 +1883,9 @@
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1998,18 +1899,75 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 5, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2018,29 +1976,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2051,30 +2009,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2084,59 +2042,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2151,29 +2109,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2181,29 +2139,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2218,56 +2176,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2285,68 +2243,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
----</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
 ---</t>
         </is>
       </c>
@@ -2355,12 +2254,12 @@
     <row r="35" ht="90" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
@@ -2368,35 +2267,94 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the feature set ships today.
+---</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>PAL studies guided workflow (formerly #23)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2407,7 +2365,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2415,23 +2373,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2442,7 +2400,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2450,23 +2408,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2477,7 +2435,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2486,23 +2444,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2515,7 +2473,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2524,30 +2482,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2556,262 +2514,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H47"/>
+  <autoFilter ref="A1:H49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1199,8 +1199,52 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>VeritaCEU: curated free-continuing-education provider list (seed / reference)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Open, reference captured. Not started.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>S (1-2 days to seed a curated provider list and surface it in VeritaCEU; XS t...</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Low-Medium — quality-of-life for VeritaCEU users (find free CE fast); not blo...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Effort: S (1-2 days to seed a curated provider list and surface it in VeritaCEU; XS to just store the reference)
+Importance: Low-Medium — quality-of-life for VeritaCEU users (find free CE fast); not blocking any sale.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Jennifer Small (jennifer.small@lifepointhealth.net) email 2026-09-25, forwarded by Michael 2026-09-28 for the future CEU module.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Post-COLA. No customer urgency.
+---</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1051,7 +1051,10 @@
       <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Open. Not started. Needs a one-line scope confirmation (which master list).
----</t>
+---
+_(item #50 closed 2026-09-28; shipped PR #1356, prod-verified, see C49 below)_
+---
+_(item #51 closed 2026-09-28;...</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1080,163 +1083,41 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" uses a flat 365-day window</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
+          <t>VeritaCEU: curated free-continuing-education provider list (seed / reference)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Open, reference captured. Not started.</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>S-M - anchor the coverage-map "assessed this cycle" to the person's actual CL...</t>
+          <t>S (1-2 days to seed a curated provider list and surface it in VeritaCEU; XS t...</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Medium - in an employee's first year the semiannual windows differ from a fla...</t>
+          <t>Low-Medium — quality-of-life for VeritaCEU users (find free CE fast); not blo...</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Effort: S-M - anchor the coverage-map "assessed this cycle" to the person's actual CLIA cadence (semiannual in year 1 per 42 CFR 493.1451(b)(8), annual thereafter) from staff_competency_schedules, instead of the v1 flat 365-day lookback.
-Importance: Medium - in an employee's first year the semiannual windows differ from a flat annual window, so a first-year assessment could read as current slightly longer or shorter than the true cadence. Fine for the common annual case; refine for year-1 accuracy.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, VeritaComp coverage map (#48 Phase 3) v1 simplification, noted in PR #1319.
----</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>VeritaTrack task owner + owner-scoped reminder routing</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Open, not started. Placeholder pending build. Open questions: is the owner a staff_employee or a seat user, and how are reminder recipients currently chosen.</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>S-M (1-3 days to ~1.5 weeks) — add an owner on a VeritaTrack task, selectable...</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Medium — cuts reminder-email noise so people only get the tasks that are thei...</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Michael, verbatim (2026-09-28): "In veritatask, we should be able to assign an owner from staff that are built, then in the reminder section, we should be able to designate reminder emails only to the owner. The hem person does not need the chemistry reminders, etc." Module note: there is no VeritaTask module in the codebase; the task/reminder surface is VeritaTrack (client/src/pages/VeritaTrackAppPage.tsx), so this lands there. Today VeritaTrack tasks are not owned by a specific staff member and reminder emails are not recipient-scoped to an owner. The build adds (a) an owner selector on each task drawn from the lab's VeritaStaff roster, and (b) a reminder setting that routes the reminder email to only that owner. Confirm the current reminder recipient model before sizing.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28 session, Michael "for later (placeholder)" optimization #1 (relaying from the Lab Members / VeritaAssure screens).</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Post-COLA. No customer urgency.
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Medical Director seat via account-grant dropdown (designate / transfer MD)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Open, not started. Placeholder. Confirm the current MD-seat assignment path and the one-MD-per-location enforcement point before sizing.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>S-M (1-3 days to ~1.5 weeks) — move MD-seat assignment onto the same per-memb...</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Medium-High — the MD seat is a recurring friction point (Georgetown, SCAHC MD...</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Michael, verbatim (2026-09-28): "The way we are doing the medical director seat is silly. Why not just use the account grant dropdown to give a medical director seat. If the person is already in, then we should just be able to grant the medical director seat the same way we promote people to admin or reduce them to staff as long as we only have 1 per location. Maybe do another block like the transfer ownership block as 'designate medical director or transfer medical director'." So: fold the MD seat into the existing member role dropdown (Admin / Staff / ... + Medical Director) with a single-MD-per-lab constraint, and add a dedicated designate-or-transfer-MD block that mirrors the transfer-ownership UX for changing the MD. Cross-ref [[project_medical_director_designation]] and the seat model.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 session, Michael "for later (placeholder)" optimization #3 (relaying from the Lab Members screen).</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Post-COLA. No customer urgency.
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>VeritaCEU: curated free-continuing-education provider list (seed / reference)</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Open, reference captured. Not started.</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>S (1-2 days to seed a curated provider list and surface it in VeritaCEU; XS t...</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Low-Medium — quality-of-life for VeritaCEU users (find free CE fast); not blo...</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Effort: S (1-2 days to seed a curated provider list and surface it in VeritaCEU; XS to just store the reference)
 Importance: Low-Medium — quality-of-life for VeritaCEU users (find free CE fast); not blocking any sale.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Jennifer Small (jennifer.small@lifepointhealth.net) email 2026-09-25, forwarded by Michael 2026-09-28 for the future CEU module.</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. No customer urgency.
 ---</t>
@@ -1244,7 +1125,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1255,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1313,24 +1194,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1339,24 +1220,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1365,93 +1246,90 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>was S-M / Importance: Medium-High</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S-M / Importance: Medium-High</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -1459,12 +1337,12 @@
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -1473,12 +1351,12 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -1486,12 +1364,12 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -1500,12 +1378,12 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
@@ -1513,12 +1391,12 @@
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -1527,12 +1405,12 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -1540,12 +1418,12 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1554,12 +1432,12 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
@@ -1567,12 +1445,12 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1581,12 +1459,12 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -1594,12 +1472,12 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1608,12 +1486,12 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
@@ -1621,12 +1499,12 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1635,12 +1513,12 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -1648,12 +1526,12 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1662,18 +1540,99 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+---</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1685,24 +1644,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1712,24 +1671,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1737,30 +1696,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1771,30 +1730,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1805,29 +1764,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1838,57 +1797,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1901,7 +1860,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1909,109 +1868,109 @@
 ---</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 5, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2020,29 +1979,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2053,30 +2012,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2086,59 +2045,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2153,29 +2112,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2183,29 +2142,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2220,56 +2179,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2287,64 +2246,64 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
 features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaCheck™ already ships the Precision /
 Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
@@ -2352,23 +2311,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
@@ -2376,29 +2335,29 @@
 shipped:</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2409,7 +2368,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2417,23 +2376,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2444,7 +2403,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2452,23 +2411,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2479,7 +2438,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2488,23 +2447,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2517,7 +2476,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2526,30 +2485,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2558,262 +2517,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H49"/>
+  <autoFilter ref="A1:H52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -923,7 +923,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Open, customer-triggered. No urgency until a prospect specifically asks for one of the listed depth items.</t>
+          <t>Small-item sequence COMPLETE (items 1-5 all shipped; verified against the codebase 2026-09-29, print view PR #1367). Remaining depth items (SSO/AD, delegation, in-browser editing, per-department ro...</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -1050,11 +1050,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Open. Not started. Needs a one-line scope confirmation (which master list).
----
-_(item #50 closed 2026-09-28; shipped PR #1356, prod-verified, see C49 below)_
----
-_(item #51 closed 2026-09-28;...</t>
+          <t>SHIPPED (PR #1364, in origin/main; predates this session, entry was stale). Built as the VeritaDC (VeritaPolicy) Master List "Show only applicable" toggle in client/src/pages/VeritaPolicyAppPage.ts...</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -822,6 +822,10 @@
 _(item #33 closed 2026-05-28; see C27 below)_
 ---
 _(items #34 and #35 closed 2026-05-24; see C23 and C24 below)_
+---
+_(item #36 closed 2026-09-29; shipped PR #1368, prod-verified, see C52 below)_
+---
+_(item #37 closed 2026-05-28; see C28 below)_
 ---</t>
         </is>
       </c>
@@ -829,40 +833,42 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>New module: laboratory non-conforming event documentation</t>
+          <t>Screen-capture video: VeritaCheck method comparison in 60 seconds</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Scoped, not started (updated 2026-09-28). Now lands in VeritaResponse per Michael's direction above; the earlier "new standalone module" framing is superseded. Do not start building until Michael g...</t>
+          <t>Open. Re-parked 2026-05-27 (originally PR #117, abandoned with merge conflicts then closed-and-re-authored at current numbering). Pending operator decision on whether to record this themselves or p...</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>L (initial estimate, pending Michael's scope walkthrough — likely new DB tabl...</t>
+          <t>S for agent prep (storyboard / pre-fill / captions / checklist); ~1 hour of o...</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>High — every accredited laboratory (TJC, CAP, COLA, AABB) has to document non...</t>
+          <t>Medium — operator selected this as the highest-impact positioning artifact du...</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Build a module to document laboratory non-conforming events (NCEs). Surfaces a lab needs to capture include specimen rejection, temperature excursions, reagent issues, equipment failures, result-reporting errors, transcription errors, lost specimens, contamination events, and similar quality incidents. Full scope, target accreditor mapping, terminology preference (NCE / NCR / event / incident / occurrence), and how it should relate to the existing VeritaQC corrective-action engine and VeritaResponse deficiency tracker are TBD pending Michael's scope walkthrough.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>30-60 second screen recording demonstrating the "experienced lab tech figures it out in seconds" claim. From blank method-comparison study to completed PDF, no voiceover, no narration, visible cursor motion. Embed autoplay-muted on the marketing site, include in conference follow-up emails.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12 conversation. Michael selected the screen-cap video as the highest-impact positioning artifact, then asked the agent to record it. Agent does not have screen-recording capability; option parked rather than fudged.</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Post-COLA. No customer urgency yet, but high strategic value once defined — closes a real gap every lab has and that no other Verita module currently serves.
----
-_(item #37 closed 2026-05-28; see C28 below)_
+          <t>Post-COLA, conference-driven.
 ---</t>
         </is>
       </c>
@@ -870,73 +876,30 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Screen-capture video: VeritaCheck method comparison in 60 seconds</t>
+          <t>MediaLab parity hardening (VeritaPolicy approval workflow depth)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Open. Re-parked 2026-05-27 (originally PR #117, abandoned with merge conflicts then closed-and-re-authored at current numbering). Pending operator decision on whether to record this themselves or p...</t>
+          <t>Small-item sequence COMPLETE (items 1-5 all shipped; verified against the codebase 2026-09-29, print view PR #1367). Remaining depth items (SSO/AD, delegation, in-browser editing, per-department ro...</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>S for agent prep (storyboard / pre-fill / captions / checklist); ~1 hour of o...</t>
+          <t>L (1-2 weeks for the high-value items; each independent feature is M)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Medium — operator selected this as the highest-impact positioning artifact du...</t>
+          <t>Medium-High — the C29 build shipped the surface MediaLab markets but depth is...</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>30-60 second screen recording demonstrating the "experienced lab tech figures it out in seconds" claim. From blank method-comparison study to completed PDF, no voiceover, no narration, visible cursor motion. Embed autoplay-muted on the marketing site, include in conference follow-up emails.</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-12 conversation. Michael selected the screen-cap video as the highest-impact positioning artifact, then asked the agent to record it. Agent does not have screen-recording capability; option parked rather than fudged.</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Post-COLA, conference-driven.
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>MediaLab parity hardening (VeritaPolicy approval workflow depth)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Small-item sequence COMPLETE (items 1-5 all shipped; verified against the codebase 2026-09-29, print view PR #1367). Remaining depth items (SSO/AD, delegation, in-browser editing, per-department ro...</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>L (1-2 weeks for the high-value items; each independent feature is M)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Medium-High — the C29 build shipped the surface MediaLab markets but depth is...</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>The VeritaPolicy approval workflow build (C29, 2026-05-29) hit roughly 60-70% MediaLab feature surface. The following gaps remain when comparing against an enterprise MediaLab Document Control deployment:
 - Quizzes on attestations. Schema columns quiz_score and quiz_total_questions exist on policy_attestations but the quiz authoring + presentation UI was scoped out of Phase 4. MediaLab labs use 5-10 multiple-choice questions per policy to confirm comprehension, not just attestation. Adds compliance defensibility.
@@ -946,54 +909,93 @@
 - In-browser DOCX editing. MediaLab has a structured editor that creates a Table of Contents from headings. We treat documents as...</t>
         </is>
       </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-29 QA pass after C29 shipped (qa-policy-build.js + qa-policy-ui.js: 54/54 happy path verified). Honest depth assessment surfaced by Michael's "how confident are you" question — see C29 entry for full QA receipts.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Post-COLA. Defensive against MediaLab in head-to-head sales calls.
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>VeritaQC Import Phase A: human-in-the-loop Gate 3 click-through (deferred)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Open, awaiting Michael's 5-minute click test. Will move task #77 to completed only after he reports the user-visible result.
+---</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>XS (~5 minutes of Michael's time on a live URL).</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Low. Backend contract is fully verified via 35/35 passing offline contract ch...</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Effort: XS (~5 minutes of Michael's time on a live URL).
+Importance: Low. Backend contract is fully verified via 35/35 passing offline contract checks (scripts/verify-veritaqc-import.js) plus three live-API smoke checks against prod (candidates, preview, mappings PUT/GET) on Riverside Regional with seed lot SEED-1780436709094 (18 Glucose results). The browser-driven click was not run because Claude-in-Chrome's renderer froze repeatedly on the Radix Select inside VeritaCheckPage, not on Phase A code itself. Risk of a UX bug surviving to a customer is small but not zero.</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29 QA pass after C29 shipped (qa-policy-build.js + qa-policy-ui.js: 54/54 happy path verified). Honest depth assessment surfaced by Michael's "how confident are you" question — see C29 entry for full QA receipts.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Post-COLA. Defensive against MediaLab in head-to-head sales calls.
----</t>
-        </is>
-      </c>
+          <t>task #77 stalled at Gate 3 step 8 on 2026-06-02. PR #500 squash-merged at commit 17a91ff, prod /api/health confirmed ACTIVE on that commit at 20:43 UTC.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaQC Import Phase A: human-in-the-loop Gate 3 click-through (deferred)</t>
+          <t>Outbound demo-invite messaging campaign to 1st-degree LinkedIn contacts</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Open, awaiting Michael's 5-minute click test. Will move task #77 to completed only after he reports the user-visible result.
+          <t>Parked. Plan documented. Implementation deferred until trigger conditions met.
 ---</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>XS (~5 minutes of Michael's time on a live URL).</t>
+          <t>L (1 week prep + 4-6 weeks of staged sends)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Low. Backend contract is fully verified via 35/35 passing offline contract ch...</t>
+          <t>High. Converts existing warm network (~2,500 1st-degree contacts and growing...</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Effort: XS (~5 minutes of Michael's time on a live URL).
-Importance: Low. Backend contract is fully verified via 35/35 passing offline contract checks (scripts/verify-veritaqc-import.js) plus three live-API smoke checks against prod (candidates, preview, mappings PUT/GET) on Riverside Regional with seed lot SEED-1780436709094 (18 Glucose results). The browser-driven click was not run because Claude-in-Chrome's renderer froze repeatedly on the Radix Select inside VeritaCheckPage, not on Phase A code itself. Risk of a UX bug surviving to a customer is small but not zero.</t>
+          <t>A staged outbound DM campaign walking Michael's 1st-degree LinkedIn contacts through tier-segmented demo invitations for VeritaAssure. Goal: convert warmest contacts into demo conversations first, then chain into trials and paid subscriptions. Separate pipeline from COLA cohort follow-up and from content-driven inbound; all three feed the same demo funnel but originate from different warmth sources.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>task #77 stalled at Gate 3 step 8 on 2026-06-02. PR #500 squash-merged at commit 17a91ff, prod /api/health confirmed ACTIVE on that commit at 20:43 UTC.</t>
+          <t>2026-06-04 session, after weekly LinkedIn invite batch completion (80 sent, cap hit at #84 Victoria Allen).</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
@@ -1001,38 +1003,38 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Outbound demo-invite messaging campaign to 1st-degree LinkedIn contacts</t>
+          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Parked. Plan documented. Implementation deferred until trigger conditions met.
----</t>
+          <t>SHIPPED (PR #1364, in origin/main; predates this session, entry was stale). Built as the VeritaDC (VeritaPolicy) Master List "Show only applicable" toggle in client/src/pages/VeritaPolicyAppPage.ts...</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>L (1 week prep + 4-6 weeks of staged sends)</t>
+          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>High. Converts existing warm network (~2,500 1st-degree contacts and growing...</t>
+          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>A staged outbound DM campaign walking Michael's 1st-degree LinkedIn contacts through tier-segmented demo invitations for VeritaAssure. Goal: convert warmest contacts into demo conversations first, then chain into trials and paid subscriptions. Separate pipeline from COLA cohort follow-up and from content-driven inbound; all three feed the same demo funnel but originate from different warmth sources.</t>
+          <t>Effort: S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility toggle that hides not-applicable or unused sections from a master-list view. Smaller if it is a "hide N/A" filter on the existing VeritaDC master list, larger if it also spans VeritaScan domains.
+Importance: Medium-High — came straight from a live prospect today as an onboarding-friction point; a lab that does not run a service line should not have to wade past its requirements.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04 session, after weekly LinkedIn invite batch completion (80 sent, cap hit at #84 Victoria Allen).</t>
+          <t>2026-09-23 session, Michael relaying a prospect ask from a demo today.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1040,80 +1042,41 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
+          <t>VeritaCEU: curated free-continuing-education provider list (seed / reference)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>SHIPPED (PR #1364, in origin/main; predates this session, entry was stale). Built as the VeritaDC (VeritaPolicy) Master List "Show only applicable" toggle in client/src/pages/VeritaPolicyAppPage.ts...</t>
+          <t>Open, reference captured. Not started.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
+          <t>S (1-2 days to seed a curated provider list and surface it in VeritaCEU; XS t...</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
+          <t>Low-Medium — quality-of-life for VeritaCEU users (find free CE fast); not blo...</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Effort: S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility toggle that hides not-applicable or unused sections from a master-list view. Smaller if it is a "hide N/A" filter on the existing VeritaDC master list, larger if it also spans VeritaScan domains.
-Importance: Medium-High — came straight from a live prospect today as an onboarding-friction point; a lab that does not run a service line should not have to wade past its requirements.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23 session, Michael relaying a prospect ask from a demo today.</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>VeritaCEU: curated free-continuing-education provider list (seed / reference)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Open, reference captured. Not started.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>S (1-2 days to seed a curated provider list and surface it in VeritaCEU; XS t...</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Low-Medium — quality-of-life for VeritaCEU users (find free CE fast); not blo...</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Effort: S (1-2 days to seed a curated provider list and surface it in VeritaCEU; XS to just store the reference)
 Importance: Low-Medium — quality-of-life for VeritaCEU users (find free CE fast); not blocking any sale.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Jennifer Small (jennifer.small@lifepointhealth.net) email 2026-09-25, forwarded by Michael 2026-09-28 for the future CEU module.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Post-COLA. No customer urgency.
 ---</t>
@@ -1121,7 +1084,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1132,7 +1095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1190,24 +1153,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1216,12 +1179,12 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
@@ -1242,24 +1205,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1268,24 +1231,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1294,24 +1257,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1320,39 +1283,38 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -1360,12 +1322,12 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -1374,12 +1336,12 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
@@ -1387,12 +1349,12 @@
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -1401,12 +1363,12 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -1414,12 +1376,12 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -1428,12 +1390,12 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
@@ -1441,12 +1403,12 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1455,12 +1417,12 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -1468,12 +1430,12 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1482,12 +1444,12 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
@@ -1495,12 +1457,12 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1509,12 +1471,12 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -1522,12 +1484,12 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1536,12 +1498,12 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
@@ -1549,12 +1511,12 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1563,12 +1525,12 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -1576,12 +1538,12 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -1590,12 +1552,12 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -1603,7 +1565,7 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1617,18 +1579,45 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1640,24 +1629,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1667,24 +1656,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1692,30 +1681,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1726,30 +1715,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1760,29 +1749,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1793,37 +1782,9 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
----</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
-23 years" as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1832,18 +1793,46 @@
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
+23 years" as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 14, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1856,7 +1845,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1864,46 +1853,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
@@ -1911,14 +1871,14 @@
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
+          <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1927,12 +1887,12 @@
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
@@ -1940,13 +1900,14 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>session 299e9a73, ~2026-04-28.
+          <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1955,18 +1916,46 @@
     <row r="29" ht="90" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -1975,29 +1964,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2008,30 +1997,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2041,59 +2030,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Tier-1 smoke test checklist (formerly #6)</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
-smoke-test process and post-deploy verification steps. Shipped via
-PR #81 as part of the 2026-05-10 wave.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Per-module gating (formerly #7)</t>
+          <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
+smoke-test process and post-deploy verification steps. Shipped via
+PR #81 as part of the 2026-05-10 wave.</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Per-module gating (formerly #7)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2108,29 +2097,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2138,29 +2127,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2175,33 +2164,6 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
@@ -2213,18 +2175,45 @@
     <row r="37" ht="90" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>WSLH PT vendor (formerly #15)</t>
+          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>WSLH PT vendor (formerly #15)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2242,38 +2231,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2282,12 +2242,12 @@
     <row r="39" ht="90" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
@@ -2295,15 +2255,14 @@
       <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
+Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2312,12 +2271,12 @@
     <row r="40" ht="90" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
@@ -2325,35 +2284,65 @@
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2364,7 +2353,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2372,23 +2361,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2399,7 +2388,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2407,23 +2396,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2434,7 +2423,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2443,23 +2432,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2472,7 +2461,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2481,30 +2470,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2513,262 +2502,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H52"/>
+  <autoFilter ref="A1:H53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1083,8 +1083,140 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VeritaTrack: quarterly task loads as monthly until re-saved (frequency display/state bug)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Open, not started. Needs reproduction in Michael's lab first.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>S (1-3 days: reproduce, find where the task-create frequency is stored vs ren...</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Medium — data-integrity/UX. A task entered as quarterly that shows as monthly...</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Effort: S (1-3 days: reproduce, find where the task-create frequency is stored vs rendered on the list, fix the load/display path)
+Importance: Medium — data-integrity/UX. A task entered as quarterly that shows as monthly on the tracker until someone re-saves it can drive the wrong due cadence and false "overdue" signals; silent and easy to miss.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-01 (parking lot).</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Either; small.
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>VeritaScan: let sites add their own custom questions</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Open, not started. Needs a short design decision on scoring treatment.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>M (1-2 weeks: a per-lab custom-question model, admin UI to author them, inclu...</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Medium-High — site-requested flexibility and a differentiator; lets a lab ext...</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Effort: M (1-2 weeks: a per-lab custom-question model, admin UI to author them, inclusion in the scan run + scoring/readiness, and export rendering)
+Importance: Medium-High — site-requested flexibility and a differentiator; lets a lab extend the standardized scan with its own internal checks without us hard-coding them.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-01 (parking lot).</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Post-COLA unless a named prospect asks.
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>VeritaQC: flag/popup when a datapoint is outside +/- 2 SD at entry</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Open, not started.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>S-M (3 days to ~1.5 weeks: compute mean/SD context at entry, warn when |z| &gt;...</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>High — patient-safety/usability gap. Right now an out-of-2SD control result i...</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Effort: S-M (3 days to ~1.5 weeks: compute mean/SD context at entry, warn when |z| &gt; 2, surface an inline flag + a confirm/acknowledge prompt; reuse the existing LJ/Westgard evaluation)
+Importance: High — patient-safety/usability gap. Right now an out-of-2SD control result is accepted silently; unless the tech scrolls to the Levey-Jennings chart they have no idea it was out, so a real QC excursion can be missed at the moment it matters.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-01 (parking lot).</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Either; strong quality-of-life + safety win.
+---</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1083,140 +1083,8 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>VeritaTrack: quarterly task loads as monthly until re-saved (frequency display/state bug)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Open, not started. Needs reproduction in Michael's lab first.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>S (1-3 days: reproduce, find where the task-create frequency is stored vs ren...</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Medium — data-integrity/UX. A task entered as quarterly that shows as monthly...</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Effort: S (1-3 days: reproduce, find where the task-create frequency is stored vs rendered on the list, fix the load/display path)
-Importance: Medium — data-integrity/UX. A task entered as quarterly that shows as monthly on the tracker until someone re-saves it can drive the wrong due cadence and false "overdue" signals; silent and easy to miss.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-01 (parking lot).</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Either; small.
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>VeritaScan: let sites add their own custom questions</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Open, not started. Needs a short design decision on scoring treatment.</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>M (1-2 weeks: a per-lab custom-question model, admin UI to author them, inclu...</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Medium-High — site-requested flexibility and a differentiator; lets a lab ext...</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Effort: M (1-2 weeks: a per-lab custom-question model, admin UI to author them, inclusion in the scan run + scoring/readiness, and export rendering)
-Importance: Medium-High — site-requested flexibility and a differentiator; lets a lab extend the standardized scan with its own internal checks without us hard-coding them.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-01 (parking lot).</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Post-COLA unless a named prospect asks.
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>VeritaQC: flag/popup when a datapoint is outside +/- 2 SD at entry</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Open, not started.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>S-M (3 days to ~1.5 weeks: compute mean/SD context at entry, warn when |z| &gt;...</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>High — patient-safety/usability gap. Right now an out-of-2SD control result i...</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Effort: S-M (3 days to ~1.5 weeks: compute mean/SD context at entry, warn when |z| &gt; 2, surface an inline flag + a confirm/acknowledge prompt; reuse the existing LJ/Westgard evaluation)
-Importance: High — patient-safety/usability gap. Right now an out-of-2SD control result is accepted silently; unless the tech scrolls to the Levey-Jennings chart they have no idea it was out, so a real QC excursion can be missed at the moment it matters.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-01 (parking lot).</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Either; strong quality-of-life + safety win.
----</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1227,7 +1095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1285,24 +1153,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1311,24 +1179,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1337,24 +1205,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1363,24 +1231,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1389,24 +1257,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1415,24 +1283,24 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1441,93 +1309,90 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>was S-M / Importance: Medium-High</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S-M / Importance: Medium-High</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
@@ -1535,12 +1400,12 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -1549,12 +1414,12 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -1562,12 +1427,12 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -1576,12 +1441,12 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
@@ -1589,12 +1454,12 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -1603,12 +1468,12 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -1616,12 +1481,12 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1630,12 +1495,12 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
@@ -1643,12 +1508,12 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1657,12 +1522,12 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -1670,12 +1535,12 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1684,12 +1549,12 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -1697,12 +1562,12 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1711,12 +1576,12 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -1724,12 +1589,12 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1738,18 +1603,99 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+---</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1761,24 +1707,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1788,24 +1734,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1813,30 +1759,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1847,30 +1793,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1881,29 +1827,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1914,57 +1860,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1977,7 +1923,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1985,109 +1931,109 @@
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H29" s="3" t="inlineStr"/>
     </row>
     <row r="30" ht="90" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 5, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2096,29 +2042,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2129,30 +2075,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2162,59 +2108,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2229,29 +2175,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2259,29 +2205,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2296,56 +2242,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2363,64 +2309,64 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
 features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaCheck™ already ships the Precision /
 Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
@@ -2428,23 +2374,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
@@ -2452,29 +2398,29 @@
 shipped:</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2485,7 +2431,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2493,23 +2439,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2520,7 +2466,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2528,23 +2474,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2555,7 +2501,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2564,23 +2510,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2593,7 +2539,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2602,30 +2548,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2634,262 +2580,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H53"/>
+  <autoFilter ref="A1:H56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -975,7 +975,10 @@
       <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Parked. Plan documented. Implementation deferred until trigger conditions met.
----</t>
+---
+_(item #50 closed 2026-09-28; shipped PR #1356, prod-verified, see C49 below)_
+---
+_(item #51 closed 2026-09-2...</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1000,91 +1003,8 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Hide sections a lab does not use from a master list, to reduce clutter (prospect-requested)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>SHIPPED (PR #1364, in origin/main; predates this session, entry was stale). Built as the VeritaDC (VeritaPolicy) Master List "Show only applicable" toggle in client/src/pages/VeritaPolicyAppPage.ts...</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility togg...</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Medium-High — came straight from a live prospect today as an onboarding-frict...</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Effort: S-M (a few days to ~2 weeks depending on scope) — a lab-level visibility toggle that hides not-applicable or unused sections from a master-list view. Smaller if it is a "hide N/A" filter on the existing VeritaDC master list, larger if it also spans VeritaScan domains.
-Importance: Medium-High — came straight from a live prospect today as an onboarding-friction point; a lab that does not run a service line should not have to wade past its requirements.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23 session, Michael relaying a prospect ask from a demo today.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>VeritaCEU: curated free-continuing-education provider list (seed / reference)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Open, reference captured. Not started.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>S (1-2 days to seed a curated provider list and surface it in VeritaCEU; XS t...</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Low-Medium — quality-of-life for VeritaCEU users (find free CE fast); not blo...</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Effort: S (1-2 days to seed a curated provider list and surface it in VeritaCEU; XS to just store the reference)
-Importance: Low-Medium — quality-of-life for VeritaCEU users (find free CE fast); not blocking any sale.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Jennifer Small (jennifer.small@lifepointhealth.net) email 2026-09-25, forwarded by Michael 2026-09-28 for the future CEU module.</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Post-COLA. No customer urgency.
----</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1095,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1153,24 +1073,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1179,24 +1099,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1205,24 +1125,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1231,24 +1151,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1257,24 +1177,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1283,24 +1203,24 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1309,24 +1229,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1335,24 +1255,24 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1361,24 +1281,24 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1387,66 +1307,64 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
@@ -1454,12 +1372,12 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -1468,12 +1386,12 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -1481,12 +1399,12 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -1495,12 +1413,12 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
@@ -1508,12 +1426,12 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -1522,12 +1440,12 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -1535,12 +1453,12 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1549,12 +1467,12 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -1562,12 +1480,12 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1576,12 +1494,12 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -1589,12 +1507,12 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1603,12 +1521,12 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -1616,12 +1534,12 @@
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1630,12 +1548,12 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -1643,12 +1561,12 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1657,12 +1575,12 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
@@ -1670,12 +1588,12 @@
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -1684,18 +1602,72 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1707,24 +1679,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1734,24 +1706,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1759,30 +1731,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1793,30 +1765,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1827,29 +1799,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1860,57 +1832,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1923,7 +1895,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1931,75 +1903,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H31" s="3" t="inlineStr"/>
     </row>
     <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
@@ -2007,8 +1921,9 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2022,18 +1937,75 @@
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 5, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2042,29 +2014,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2075,30 +2047,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2108,59 +2080,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2175,29 +2147,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2205,29 +2177,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2242,56 +2214,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2309,68 +2281,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
----</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
 ---</t>
         </is>
       </c>
@@ -2379,12 +2292,12 @@
     <row r="44" ht="90" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
@@ -2392,35 +2305,94 @@
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the feature set ships today.
+---</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>PAL studies guided workflow (formerly #23)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2431,7 +2403,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2439,23 +2411,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2466,7 +2438,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2474,23 +2446,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2501,7 +2473,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2510,23 +2482,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2539,7 +2511,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2548,30 +2520,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2580,262 +2552,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H56"/>
+  <autoFilter ref="A1:H58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1003,8 +1003,39 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
     </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Manual Differential complexity is MODERATE in VeritaMap, should be HIGH</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>XS (under 1 day)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>High — a wrong complexity under-applies HIGH-complexity requirements, produci...</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Effort: XS (under 1 day)
+Importance: High — a wrong complexity under-applies HIGH-complexity requirements, producing a false readiness picture and regulatory exposure.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1003,8 +1003,86 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
     </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the finding-closure signer policy (non-MD admins now blocked)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Open, awaiting operator confirmation. Reverting is a one-line change (re-add the owner/admin path in the findings/:id/signoff handler) if admins should retain finding closure.
+---</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>XS (a yes/no decision; ~15 min to loosen the gate if reversed).</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Medium — changes who can close VeritaResponse findings in production; affects...</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Item 5 Phase 2 tightened VeritaResponse finding closure from "any owner / admin / edit-seat" to "the designated medical director, a delegated designee holding finding-closure for the lab's complexity, or the account owner as a logged break-glass override." This is live on prod (#1443). It follows the agreed MD-or-designee model (QB=1), and the same gate now guards QC period-review co-sign. It has not been confirmed against real customer workflows: if any lab relies on non-MD admins closing findings, they now need a Letter of Delegation, or the gate must be loosened.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>this session, delegation feature build (2026-10-04). Flagged repeatedly in-session; awaiting explicit operator sign-off.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Regenerate the 119-function access-inventory Excel with the corrected MD persona</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Open, low priority. Offered to Michael; skippable if the sweep was a one-off working artifact.
+---</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>XS (~15 min to re-run the sweep harness and re-deliver).</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Low — the harness and the shipped fixes are correct; only the recorded Excel'...</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>The full-inventory 4-login access sweep (VeritaAssure_Function_Inventory.xlsx) was first generated with the medical-director test persona mis-seeded as a seatless member, which over-flagged its column. The harness was then corrected to seat the MD as the active writer it actually is (scripts/qa-sweep/inventory-sweep.ts). The delivered Excel still shows the old md results; re-running reclassifies the md-artifact flags down to the real findings, which were already fixed in PR A (#1441). Only worth doing if the sheet gets filed or shared externally.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>this session, QA sweep (2026-10-03 to 2026-10-04).</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1093,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1151,24 +1151,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list (was #47)</t>
+          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1177,24 +1177,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Low-Medium</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Low-Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1203,24 +1203,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1229,24 +1229,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1255,24 +1255,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1281,24 +1281,24 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1307,24 +1307,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1333,12 +1333,12 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
@@ -1359,24 +1359,24 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1385,24 +1385,24 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1411,24 +1411,24 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1437,39 +1437,38 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -1477,12 +1476,12 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -1491,12 +1490,12 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
@@ -1504,12 +1503,12 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -1518,12 +1517,12 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -1531,12 +1530,12 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -1545,12 +1544,12 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -1558,12 +1557,12 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1572,12 +1571,12 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -1585,12 +1584,12 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1599,12 +1598,12 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -1612,12 +1611,12 @@
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1626,12 +1625,12 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -1639,12 +1638,12 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1653,12 +1652,12 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
@@ -1666,12 +1665,12 @@
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1680,12 +1679,12 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
@@ -1693,12 +1692,12 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -1707,12 +1706,12 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
@@ -1720,7 +1719,7 @@
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1734,18 +1733,45 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1757,24 +1783,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1784,24 +1810,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1809,30 +1835,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1843,30 +1869,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1877,29 +1903,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1910,37 +1936,9 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
----</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
-23 years" as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1949,18 +1947,46 @@
     <row r="31" ht="90" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
+23 years" as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 14, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1973,7 +1999,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1981,46 +2007,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
@@ -2028,14 +2025,14 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
+          <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2044,12 +2041,12 @@
     <row r="34" ht="90" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
@@ -2057,13 +2054,14 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>session 299e9a73, ~2026-04-28.
+          <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2072,18 +2070,46 @@
     <row r="35" ht="90" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="3" t="inlineStr"/>
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2092,29 +2118,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2125,30 +2151,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2158,59 +2184,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Tier-1 smoke test checklist (formerly #6)</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
-smoke-test process and post-deploy verification steps. Shipped via
-PR #81 as part of the 2026-05-10 wave.</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr"/>
     </row>
     <row r="39" ht="90" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Per-module gating (formerly #7)</t>
+          <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
+smoke-test process and post-deploy verification steps. Shipped via
+PR #81 as part of the 2026-05-10 wave.</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Per-module gating (formerly #7)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2225,29 +2251,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2255,29 +2281,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2292,33 +2318,6 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
@@ -2330,18 +2329,45 @@
     <row r="43" ht="90" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WSLH PT vendor (formerly #15)</t>
+          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>WSLH PT vendor (formerly #15)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2359,38 +2385,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2399,12 +2396,12 @@
     <row r="45" ht="90" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
@@ -2412,15 +2409,14 @@
       <c r="E45" s="3" t="inlineStr"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
+Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2429,12 +2425,12 @@
     <row r="46" ht="90" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
@@ -2442,35 +2438,65 @@
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2481,7 +2507,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2489,23 +2515,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2516,7 +2542,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2524,23 +2550,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2551,7 +2577,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2560,23 +2586,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2589,7 +2615,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2598,30 +2624,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2630,262 +2656,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="90" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H58"/>
+  <autoFilter ref="A1:H59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1006,83 +1006,44 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Confirm the finding-closure signer policy (non-MD admins now blocked)</t>
+          <t>Regenerate the 119-function access-inventory Excel with the corrected MD persona</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Open, awaiting operator confirmation. Reverting is a one-line change (re-add the owner/admin path in the findings/:id/signoff handler) if admins should retain finding closure.
+          <t>Open, low priority. Offered to Michael; skippable if the sweep was a one-off working artifact.
 ---</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>XS (a yes/no decision; ~15 min to loosen the gate if reversed).</t>
+          <t>XS (~15 min to re-run the sweep harness and re-deliver).</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Medium — changes who can close VeritaResponse findings in production; affects...</t>
+          <t>Low — the harness and the shipped fixes are correct; only the recorded Excel'...</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Item 5 Phase 2 tightened VeritaResponse finding closure from "any owner / admin / edit-seat" to "the designated medical director, a delegated designee holding finding-closure for the lab's complexity, or the account owner as a logged break-glass override." This is live on prod (#1443). It follows the agreed MD-or-designee model (QB=1), and the same gate now guards QC period-review co-sign. It has not been confirmed against real customer workflows: if any lab relies on non-MD admins closing findings, they now need a Letter of Delegation, or the gate must be loosened.</t>
+          <t>The full-inventory 4-login access sweep (VeritaAssure_Function_Inventory.xlsx) was first generated with the medical-director test persona mis-seeded as a seatless member, which over-flagged its column. The harness was then corrected to seat the MD as the active writer it actually is (scripts/qa-sweep/inventory-sweep.ts). The delivered Excel still shows the old md results; re-running reclassifies the md-artifact flags down to the real findings, which were already fixed in PR A (#1441). Only worth doing if the sheet gets filed or shared externally.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>this session, delegation feature build (2026-10-04). Flagged repeatedly in-session; awaiting explicit operator sign-off.</t>
+          <t>this session, QA sweep (2026-10-03 to 2026-10-04).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Regenerate the 119-function access-inventory Excel with the corrected MD persona</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Open, low priority. Offered to Michael; skippable if the sweep was a one-off working artifact.
----</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>XS (~15 min to re-run the sweep harness and re-deliver).</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Low — the harness and the shipped fixes are correct; only the recorded Excel'...</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>The full-inventory 4-login access sweep (VeritaAssure_Function_Inventory.xlsx) was first generated with the medical-director test persona mis-seeded as a seatless member, which over-flagged its column. The harness was then corrected to seat the MD as the active writer it actually is (scripts/qa-sweep/inventory-sweep.ts). The delivered Excel still shows the old md results; re-running reclassifies the md-artifact flags down to the real findings, which were already fixed in PR A (#1441). Only worth doing if the sheet gets filed or shared externally.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>this session, QA sweep (2026-10-03 to 2026-10-04).</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1093,7 +1054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1151,24 +1112,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C58</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
+          <t>Confirm the finding-closure signer policy (was #43)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1177,24 +1138,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list (was #47)</t>
+          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1203,24 +1164,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Low-Medium</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Low-Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1229,24 +1190,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1255,24 +1216,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1281,24 +1242,24 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1307,24 +1268,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1333,24 +1294,24 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1359,12 +1320,12 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -1385,24 +1346,24 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1411,24 +1372,24 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1437,24 +1398,24 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1463,39 +1424,38 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
@@ -1503,12 +1463,12 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -1517,12 +1477,12 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -1530,12 +1490,12 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -1544,12 +1504,12 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -1557,12 +1517,12 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -1571,12 +1531,12 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -1584,12 +1544,12 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1598,12 +1558,12 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -1611,12 +1571,12 @@
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1625,12 +1585,12 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -1638,12 +1598,12 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1652,12 +1612,12 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
@@ -1665,12 +1625,12 @@
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1679,12 +1639,12 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
@@ -1692,12 +1652,12 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1706,12 +1666,12 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
@@ -1719,12 +1679,12 @@
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -1733,12 +1693,12 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
@@ -1746,7 +1706,7 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1760,18 +1720,45 @@
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1783,24 +1770,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1810,24 +1797,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1835,30 +1822,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1869,30 +1856,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1903,29 +1890,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1936,37 +1923,9 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
----</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
-23 years" as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1975,18 +1934,46 @@
     <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
+23 years" as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 14, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1999,7 +1986,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -2007,46 +1994,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H33" s="3" t="inlineStr"/>
     </row>
     <row r="34" ht="90" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
@@ -2054,14 +2012,14 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
+          <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2070,12 +2028,12 @@
     <row r="35" ht="90" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
@@ -2083,13 +2041,14 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>session 299e9a73, ~2026-04-28.
+          <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2098,18 +2057,46 @@
     <row r="36" ht="90" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2118,29 +2105,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2151,30 +2138,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2184,59 +2171,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Tier-1 smoke test checklist (formerly #6)</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
-smoke-test process and post-deploy verification steps. Shipped via
-PR #81 as part of the 2026-05-10 wave.</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
       <c r="H39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="90" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Per-module gating (formerly #7)</t>
+          <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
+smoke-test process and post-deploy verification steps. Shipped via
+PR #81 as part of the 2026-05-10 wave.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Per-module gating (formerly #7)</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2251,29 +2238,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2281,29 +2268,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2318,33 +2305,6 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
-        </is>
-      </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
@@ -2356,18 +2316,45 @@
     <row r="44" ht="90" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>WSLH PT vendor (formerly #15)</t>
+          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>WSLH PT vendor (formerly #15)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2385,38 +2372,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2425,12 +2383,12 @@
     <row r="46" ht="90" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
@@ -2438,15 +2396,14 @@
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
+Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2455,12 +2412,12 @@
     <row r="47" ht="90" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr"/>
@@ -2468,35 +2425,65 @@
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2507,7 +2494,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2515,23 +2502,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2542,7 +2529,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2550,23 +2537,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2577,7 +2564,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2586,23 +2573,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2615,7 +2602,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2624,30 +2611,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2656,262 +2643,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="90" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="90" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="90" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H59"/>
+  <autoFilter ref="A1:H60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -924,55 +924,15 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC Import Phase A: human-in-the-loop Gate 3 click-through (deferred)</t>
+          <t>Outbound demo-invite messaging campaign to 1st-degree LinkedIn contacts</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Open, awaiting Michael's 5-minute click test. Will move task #77 to completed only after he reports the user-visible result.
----</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>XS (~5 minutes of Michael's time on a live URL).</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Low. Backend contract is fully verified via 35/35 passing offline contract ch...</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Effort: XS (~5 minutes of Michael's time on a live URL).
-Importance: Low. Backend contract is fully verified via 35/35 passing offline contract checks (scripts/verify-veritaqc-import.js) plus three live-API smoke checks against prod (candidates, preview, mappings PUT/GET) on Riverside Regional with seed lot SEED-1780436709094 (18 Glucose results). The browser-driven click was not run because Claude-in-Chrome's renderer froze repeatedly on the Radix Select inside VeritaCheckPage, not on Phase A code itself. Risk of a UX bug surviving to a customer is small but not zero.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>task #77 stalled at Gate 3 step 8 on 2026-06-02. PR #500 squash-merged at commit 17a91ff, prod /api/health confirmed ACTIVE on that commit at 20:43 UTC.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Outbound demo-invite messaging campaign to 1st-degree LinkedIn contacts</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Parked. Plan documented. Implementation deferred until trigger conditions met.
 ---
@@ -981,69 +941,69 @@
 _(item #51 closed 2026-09-2...</t>
         </is>
       </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>L (1 week prep + 4-6 weeks of staged sends)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>High. Converts existing warm network (~2,500 1st-degree contacts and growing...</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>A staged outbound DM campaign walking Michael's 1st-degree LinkedIn contacts through tier-segmented demo invitations for VeritaAssure. Goal: convert warmest contacts into demo conversations first, then chain into trials and paid subscriptions. Separate pipeline from COLA cohort follow-up and from content-driven inbound; all three feed the same demo funnel but originate from different warmth sources.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 session, after weekly LinkedIn invite batch completion (80 sent, cap hit at #84 Victoria Allen).</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Regenerate the 119-function access-inventory Excel with the corrected MD persona</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Open, low priority. Offered to Michael; skippable if the sweep was a one-off working artifact.
+---</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>L (1 week prep + 4-6 weeks of staged sends)</t>
+          <t>XS (~15 min to re-run the sweep harness and re-deliver).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>High. Converts existing warm network (~2,500 1st-degree contacts and growing...</t>
+          <t>Low — the harness and the shipped fixes are correct; only the recorded Excel'...</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>A staged outbound DM campaign walking Michael's 1st-degree LinkedIn contacts through tier-segmented demo invitations for VeritaAssure. Goal: convert warmest contacts into demo conversations first, then chain into trials and paid subscriptions. Separate pipeline from COLA cohort follow-up and from content-driven inbound; all three feed the same demo funnel but originate from different warmth sources.</t>
+          <t>The full-inventory 4-login access sweep (VeritaAssure_Function_Inventory.xlsx) was first generated with the medical-director test persona mis-seeded as a seatless member, which over-flagged its column. The harness was then corrected to seat the MD as the active writer it actually is (scripts/qa-sweep/inventory-sweep.ts). The delivered Excel still shows the old md results; re-running reclassifies the md-artifact flags down to the real findings, which were already fixed in PR A (#1441). Only worth doing if the sheet gets filed or shared externally.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04 session, after weekly LinkedIn invite batch completion (80 sent, cap hit at #84 Victoria Allen).</t>
+          <t>this session, QA sweep (2026-10-03 to 2026-10-04).</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Regenerate the 119-function access-inventory Excel with the corrected MD persona</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Open, low priority. Offered to Michael; skippable if the sweep was a one-off working artifact.
----</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>XS (~15 min to re-run the sweep harness and re-deliver).</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Low — the harness and the shipped fixes are correct; only the recorded Excel'...</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>The full-inventory 4-login access sweep (VeritaAssure_Function_Inventory.xlsx) was first generated with the medical-director test persona mis-seeded as a seatless member, which over-flagged its column. The harness was then corrected to seat the MD as the active writer it actually is (scripts/qa-sweep/inventory-sweep.ts). The delivered Excel still shows the old md results; re-running reclassifies the md-artifact flags down to the real findings, which were already fixed in PR A (#1441). Only worth doing if the sheet gets filed or shared externally.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>this session, QA sweep (2026-10-03 to 2026-10-04).</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1054,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1112,24 +1072,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C59</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Confirm the finding-closure signer policy (was #43)</t>
+          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1138,24 +1098,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C58</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
+          <t>Confirm the finding-closure signer policy (was #43)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1164,24 +1124,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list (was #47)</t>
+          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1190,24 +1150,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Low-Medium</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Low-Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1216,24 +1176,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1242,24 +1202,24 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1268,24 +1228,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1294,24 +1254,24 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1320,24 +1280,24 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1346,12 +1306,12 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
@@ -1372,24 +1332,24 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1398,24 +1358,24 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1424,24 +1384,24 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1450,39 +1410,38 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -1490,12 +1449,12 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -1504,12 +1463,12 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -1517,12 +1476,12 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -1531,12 +1490,12 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -1544,12 +1503,12 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -1558,12 +1517,12 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -1571,12 +1530,12 @@
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1585,12 +1544,12 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -1598,12 +1557,12 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1612,12 +1571,12 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
@@ -1625,12 +1584,12 @@
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1639,12 +1598,12 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
@@ -1652,12 +1611,12 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1666,12 +1625,12 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
@@ -1679,12 +1638,12 @@
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1693,12 +1652,12 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
@@ -1706,12 +1665,12 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -1720,12 +1679,12 @@
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
@@ -1733,7 +1692,7 @@
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1747,18 +1706,45 @@
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1770,24 +1756,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1797,24 +1783,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1822,30 +1808,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1856,30 +1842,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1890,29 +1876,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1923,37 +1909,9 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
----</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
-23 years" as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1962,18 +1920,46 @@
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
+23 years" as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 14, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1986,7 +1972,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1994,46 +1980,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="90" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
@@ -2041,14 +1998,14 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
+          <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2057,12 +2014,12 @@
     <row r="36" ht="90" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
@@ -2070,13 +2027,14 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>session 299e9a73, ~2026-04-28.
+          <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2085,18 +2043,46 @@
     <row r="37" ht="90" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2105,29 +2091,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2138,30 +2124,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2171,59 +2157,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Tier-1 smoke test checklist (formerly #6)</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
-smoke-test process and post-deploy verification steps. Shipped via
-PR #81 as part of the 2026-05-10 wave.</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
       <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41" ht="90" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Per-module gating (formerly #7)</t>
+          <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="3" t="inlineStr"/>
       <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
+smoke-test process and post-deploy verification steps. Shipped via
+PR #81 as part of the 2026-05-10 wave.</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Per-module gating (formerly #7)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2238,29 +2224,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2268,29 +2254,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2305,33 +2291,6 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
@@ -2343,18 +2302,45 @@
     <row r="45" ht="90" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>WSLH PT vendor (formerly #15)</t>
+          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="3" t="inlineStr"/>
       <c r="E45" s="3" t="inlineStr"/>
       <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>WSLH PT vendor (formerly #15)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2372,38 +2358,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2412,12 +2369,12 @@
     <row r="47" ht="90" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr"/>
@@ -2425,15 +2382,14 @@
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
+Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2442,12 +2398,12 @@
     <row r="48" ht="90" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
@@ -2455,35 +2411,65 @@
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2494,7 +2480,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2502,23 +2488,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2529,7 +2515,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2537,23 +2523,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2564,7 +2550,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2573,23 +2559,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2602,7 +2588,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2611,30 +2597,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2643,262 +2629,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="90" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="90" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="90" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="90" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="90" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H60"/>
+  <autoFilter ref="A1:H61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -963,47 +963,8 @@
       </c>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Regenerate the 119-function access-inventory Excel with the corrected MD persona</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Open, low priority. Offered to Michael; skippable if the sweep was a one-off working artifact.
----</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>XS (~15 min to re-run the sweep harness and re-deliver).</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Low — the harness and the shipped fixes are correct; only the recorded Excel'...</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>The full-inventory 4-login access sweep (VeritaAssure_Function_Inventory.xlsx) was first generated with the medical-director test persona mis-seeded as a seatless member, which over-flagged its column. The harness was then corrected to seat the MD as the active writer it actually is (scripts/qa-sweep/inventory-sweep.ts). The delivered Excel still shows the old md results; re-running reclassifies the md-artifact flags down to the real findings, which were already fixed in PR A (#1441). Only worth doing if the sheet gets filed or shared externally.</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>this session, QA sweep (2026-10-03 to 2026-10-04).</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1014,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1072,12 +1033,12 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C60</t>
+          <t>C61</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
+          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -1098,24 +1059,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C59</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Confirm the finding-closure signer policy (was #43)</t>
+          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1124,24 +1085,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C58</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
+          <t>Confirm the finding-closure signer policy (was #43)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1150,24 +1111,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list (was #47)</t>
+          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1176,24 +1137,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Low-Medium</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Low-Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1202,24 +1163,24 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1228,24 +1189,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1254,24 +1215,24 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1280,24 +1241,24 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1306,24 +1267,24 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1332,12 +1293,12 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -1358,24 +1319,24 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1384,24 +1345,24 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1410,24 +1371,24 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1436,39 +1397,38 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -1476,12 +1436,12 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -1490,12 +1450,12 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -1503,12 +1463,12 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -1517,12 +1477,12 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -1530,12 +1490,12 @@
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -1544,12 +1504,12 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -1557,12 +1517,12 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -1571,12 +1531,12 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
@@ -1584,12 +1544,12 @@
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -1598,12 +1558,12 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
@@ -1611,12 +1571,12 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -1625,12 +1585,12 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
@@ -1638,12 +1598,12 @@
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -1652,12 +1612,12 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
@@ -1665,12 +1625,12 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -1679,12 +1639,12 @@
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
@@ -1692,12 +1652,12 @@
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -1706,12 +1666,12 @@
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
@@ -1719,7 +1679,7 @@
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1733,18 +1693,45 @@
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -1756,24 +1743,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -1783,24 +1770,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -1808,30 +1795,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1842,30 +1829,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1876,29 +1863,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1909,37 +1896,9 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
----</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
-23 years" as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -1948,18 +1907,46 @@
     <row r="34" ht="90" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
+23 years" as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 14, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1972,7 +1959,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1980,46 +1967,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H35" s="3" t="inlineStr"/>
     </row>
     <row r="36" ht="90" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
@@ -2027,14 +1985,14 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
+          <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2043,12 +2001,12 @@
     <row r="37" ht="90" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
@@ -2056,13 +2014,14 @@
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>session 299e9a73, ~2026-04-28.
+          <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2071,18 +2030,46 @@
     <row r="38" ht="90" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2091,29 +2078,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2124,30 +2111,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2157,59 +2144,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Tier-1 smoke test checklist (formerly #6)</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
-smoke-test process and post-deploy verification steps. Shipped via
-PR #81 as part of the 2026-05-10 wave.</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
       <c r="H41" s="3" t="inlineStr"/>
     </row>
     <row r="42" ht="90" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Per-module gating (formerly #7)</t>
+          <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
+smoke-test process and post-deploy verification steps. Shipped via
+PR #81 as part of the 2026-05-10 wave.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Per-module gating (formerly #7)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2224,29 +2211,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2254,29 +2241,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2291,33 +2278,6 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
-        </is>
-      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
@@ -2329,18 +2289,45 @@
     <row r="46" ht="90" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>WSLH PT vendor (formerly #15)</t>
+          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>WSLH PT vendor (formerly #15)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2358,38 +2345,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2398,12 +2356,12 @@
     <row r="48" ht="90" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
@@ -2411,15 +2369,14 @@
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
+Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2428,12 +2385,12 @@
     <row r="49" ht="90" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr"/>
@@ -2441,35 +2398,65 @@
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2480,7 +2467,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2488,23 +2475,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2515,7 +2502,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2523,23 +2510,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2550,7 +2537,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2559,23 +2546,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2588,7 +2575,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2597,30 +2584,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2629,262 +2616,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="90" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="90" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="90" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="90" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="90" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61" ht="90" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="90" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H61"/>
+  <autoFilter ref="A1:H62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Open. Multi-hour subagent fan-out work.</t>
+          <t>Open. Multi-hour subagent fan-out work. Work-pass 2026-10-04: BLOCKED on materials. AABB and COLA columns cannot be source-grounded without the gated manuals (item #28); CAP is 11/12 modules verifi...</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Open, blocks on operator obtaining the MOL checklist.</t>
+          <t>Open, blocks on operator obtaining the MOL checklist. Work-pass 2026-10-04: NEEDS MICHAEL. The MAS_MOL xlsx download requires CAP e-LAB credentials (agent cannot download). Drop MAS_MOL_*.xlsx in t...</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -642,7 +642,8 @@
         <is>
           <t>Open, blocks on operator obtaining the gated accreditor
 manuals. Until then, AABB / COLA citations are best-effort against
-the public-source compilations.</t>
+the public-source compilations. Work-pass 2026-10-04: NEEDS MICHAEL.
+AABB...</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -703,8 +704,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Parked pending first paid commitment.
----</t>
+          <t>Parked pending first paid commitment. Work-pass 2026-10-04: HELD BY STRATEGY, build-decision needs Michael. Already fully scoped (12-day plan below), so nothing to add by re-scoping. Trigger remain...</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -750,7 +750,11 @@
           <t>Plain-language summary layer for verbatim CFR citations</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Open. Work-pass 2026-10-04: APPROACH FORK, needs Michael. Verified live that the 5 operator-approved summaries (sections 1235/1252/1253/1281/1289) exist inert in server/cfrRequirements.ts and no UI...</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>M (multi-day content authoring across 96 Master List rows if redesigned corre...</t>
@@ -790,7 +794,11 @@
           <t>Lab leader community / forum (paid subscription idea)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Open. Work-pass 2026-10-04: BUSINESS DECISION, needs Michael. SWOT verdict stands (do not build a paid forum; economics kill it). The recommended free invite-only Slack/Discord plus quarterly round...</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>XL (ongoing operational commitment, not a build) as paid; S (a few days to sp...</t>
@@ -817,16 +825,7 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Post-COLA. No customer urgency.
----
-_(item #33 closed 2026-05-28; see C27 below)_
----
-_(items #34 and #35 closed 2026-05-24; see C23 and C24 below)_
----
-_(item #36 closed 2026-09-29; shipped PR #1368, prod-verified, see C52 below)_
----
-_(item #37 closed 2026-05-28; see C28 below)_
----</t>
+          <t>Post-COLA. No customer urgency.</t>
         </is>
       </c>
     </row>
@@ -886,7 +885,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Small-item sequence COMPLETE (items 1-5 all shipped; verified against the codebase 2026-09-29, print view PR #1367). Remaining depth items (SSO/AD, delegation, in-browser editing, per-department ro...</t>
+          <t>Small-item sequence COMPLETE (items 1-5 all shipped; verified against the codebase 2026-09-29, print view PR #1367). Note (2026-10-04): the "delegation" listed here is VeritaPolicy APPROVAL-workflo...</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -934,11 +933,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Parked. Plan documented. Implementation deferred until trigger conditions met.
----
-_(item #50 closed 2026-09-28; shipped PR #1356, prod-verified, see C49 below)_
----
-_(item #51 closed 2026-09-2...</t>
+          <t>Parked. Plan documented. Implementation deferred until trigger conditions met. Work-pass 2026-10-04: AGENT HALF DELIVERED. Pre-implementation step 5 done: linkedin_search/outbound_messages_v1.md sh...</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Open. Work-pass 2026-10-04: APPROACH FORK, needs Michael. Verified live that the 5 operator-approved summaries (sections 1235/1252/1253/1281/1289) exist inert in server/cfrRequirements.ts and no UI...</t>
+          <t>BUILT 2026-10-04 (approach (a)). A read-only "CFR Reference" tab in VeritaDC (VeritaPolicyCfrReferencePage.tsx + VeritaPolicyTabs + route) surfaces the 5 operator-approved plain-language summaries...</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BUILT 2026-10-04 (approach (a)). A read-only "CFR Reference" tab in VeritaDC (VeritaPolicyCfrReferencePage.tsx + VeritaPolicyTabs + route) surfaces the 5 operator-approved plain-language summaries...</t>
+          <t>BUILT 2026-10-04 (approach (a)), then EXPANDED 5 -&gt; 19 sections. A read-only "CFR Reference" tab in VeritaDC (VeritaPolicyCfrReferencePage.tsx + VeritaPolicyTabs + route) surfaces plain-language su...</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BUILT 2026-10-04 (approach (a)), then EXPANDED 5 -&gt; 19 sections. A read-only "CFR Reference" tab in VeritaDC (VeritaPolicyCfrReferencePage.tsx + VeritaPolicyTabs + route) surfaces plain-language su...</t>
+          <t>BUILT 2026-10-04 (approach (a)), then EXPANDED 5 -&gt; 27 sections (two tranches). A read-only "CFR Reference" tab in VeritaDC (VeritaPolicyCfrReferencePage.tsx + VeritaPolicyTabs + route) surfaces pl...</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BUILT 2026-10-04 (approach (a)), then EXPANDED 5 -&gt; 27 sections (two tranches). A read-only "CFR Reference" tab in VeritaDC (VeritaPolicyCfrReferencePage.tsx + VeritaPolicyTabs + route) surfaces pl...</t>
+          <t>BUILT 2026-10-04 (approach (a)), then EXPANDED 5 -&gt; 35 sections (three tranches: quality systems/PT, pre/analytic/postanalytic + facilities/specimens, and the full CLIA personnel subpart via add_cf...</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Open. Work-pass 2026-10-04: APPROACH FORK, needs Michael. Verified live that the 5 operator-approved summaries (sections 1235/1252/1253/1281/1289) exist inert in server/cfrRequirements.ts and no UI...</t>
+          <t>BUILT 2026-10-04 (approach (a)), then EXPANDED 5 -&gt; 35 sections (three tranches: quality systems/PT, pre/analytic/postanalytic + facilities/specimens, and the full CLIA personnel subpart via add_cf...</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -958,8 +958,279 @@
       </c>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>VeritaMap test-menu accuracy audit (menus incomplete, not just missing instruments)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Open. First instance fixed 2026-10-06 (Sodium/Potassium/Chloride added to the three Roche photometric-module entries); broad audit not started.
+---</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>L (3-5 weeks)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>High — wrong or partial menus surface live in demos and undercut VeritaMap as...</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Beyond confirming every instrument exists, the per-instrument analyte
+menus in client/src/lib/fdaInstrumentData.json need verification for
+completeness and accuracy. Surfaced when a Roche demo hit a cobas 8000 with no
+Sodium or Potassium: that entry was scoped to the c702 photometric module and
+omitted the ISE-module electrolytes. The cobas 8000 / c702 / c502 electrolyte
+gap was fixed 2026-10-06 (see Status), but the systemic issue — module-scoped
+or partial menus across vendors — remains. A full pass (vendor/FDA-sourced,
+no fabrication) would make VeritaMap demo-safe across the board.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-06 Roche demo.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>VeritaCheck instrument-verification: multi-select analyte menu (stop adding one by one)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Open. Design presented and approved in principle; awaiting explicit go to build.
+---</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>High — core usability of the instrument-verification flow; cumbersome enough...</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>On a new Instrument Verification Package, analytes are added one at a
+time via free text. The existing "FDA-cleared" dropdown only renders when the
+verification is linked to a VeritaMap instrument (map_instrument_id), which
+standalone verifications lack, and even then it is single-select. Fix: source
+the menu from fdaInstrumentData.json by the verification's instrument name
+(e.g., Sysmex XN-2000 = 40 analytes), show a multi-select checklist with
+Select-all, and bulk-insert in one transaction (new bulk endpoint). Keep
+free-text for custom analytes.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-06 screenshot (/labs/3/dashboard/verifications).</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>VeritaComp legacy program modal shows no VeritaStaff employees (Option 2)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Open. Approved ("build it that way"); code paths already traced; ready to build.
+---</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Medium — fixes a confusing dead-end next to the employee-centric flow; mostly...</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>The legacy "New Technical Assessment" program modal reads
+competency_employees (empty for most labs) instead of VeritaStaff's
+staff_employees, so it says "No active employees" even when staff are
+assigned the program's instruments (observed on lab 5 / Alecia Lillico-Perry
+with the Atellica CH 930). Michael chose Option 2: populate the modal with the
+lab's active VeritaStaff employees who are assigned the program's instruments,
+auto-bridged into competency_employees on the fly (reusing the existing
+idempotent bridge). Fixes the roster drift rather than hiding the flow.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-06.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPT: load the CAP vendor program catalog (Program Name dropdown for CAP)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Open. Diagnosed; awaiting go to compile the CAP list for verification.
+---</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>High — CAP is the dominant PT vendor; free-text entry looks broken in demos.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The Program Name field becomes a dropdown only when the vendor's
+catalog is loaded in pt_vendor_programs. API is loaded; CAP is not, so CAP
+falls back to free text ("No CAP catalog loaded yet"). By design the system
+refuses to invent catalog rows — CAP data must be vendor-sourced and
+operator-verified. Fix: compile the real CAP Survey programs across the 10 PT
+categories, present for Michael's verification, then load via
+POST /api/admin/veritapt/vendor-programs. No code change; data load only.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-06 screenshot (PT Program Enrollments modal).</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>VeritaMap: remove duplicate demo maps (dedupe tool shipped; awaiting selection)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Open. Tool live; awaiting Michael's deletion selection.
+---</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>XS (under 1 day)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Low-Medium — demo-lab hygiene; not customer-facing.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Michael created many maps while demoing and asked to remove
+duplicates. The read-only-by-default admin dedupe-maps endpoint shipped
+2026-10-06 (PR #1475). The audit found only a handful of strict content
+duplicates (plus false matches from empty maps, and items in Lisa's live lab 4
+that must not be touched). Needs Michael to pick what to delete — the strict
+dupes, or a broader clean-out of lab 3's 21 maps. Deletion runs scoped per lab
+with full cascade once he approves the ids.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-06.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Vendor instrument expansion PR #1474 (25 platforms; awaiting complexity sign-off)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Open. PR green; awaiting merge approval.
+---</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>XS (under 1 day)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Medium — closes demo-reported instrument gaps for Bio-Rad, Tosoh, Horiba, and...</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>PR #1474 adds 25 current platforms to fdaInstrumentData.json with
+FDA-anchored CLIA complexity (269 -&gt; 294 instruments). Held for Michael's
+sign-off because complexity is a regulatory property and his call. Green and
+ready; once approved, merge and confirm the new instruments appear in the
+VeritaMap instrument search on prod.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-06.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H10"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -971,8 +971,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Open. First instance fixed 2026-10-06 (Sodium/Potassium/Chloride added to the three Roche photometric-module entries); broad audit not started.
----</t>
+          <t>IN PROGRESS. Michael chose Option 2 (exhaustive) 2026-10-06. Executing vendor-by-vendor, sourced and verified against the manufacturer's own parameter lists. Batch 1 (Roche chemistry c-module) reco...</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1229,8 +1228,57 @@
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Open. Root cause diagnosed; mechanical class fix ready to slot in on request.
+---</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Medium — intermittent, customer-facing failure on PDF deliverables (studies,...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Some PDF opens land on an about:blank tab instead of the document.
+Root cause: the fragile window.open('/api/pdf/&lt;one-time-token&gt;') pattern, still
+used on ~6 paths (VeritaOps, VeritaPace, VeritaQA, VeritaResponse x3, the
+Why-VeritaCheck article, CMS-116). With Adobe Acrobat as the PDF handler it opens
+a blank tab while Acrobat grabs the PDF, orphaning about:blank, and worse when
+the one-time token GET races or expires (the PR #286 class). Most downloads were
+migrated to the safe anchor helper downloadPdfToken (client/src/lib/utils.ts),
+which is why it is "mostly removed." Fix: route every remaining PDF open through
+the safe download helper, and verify the /api/pdf server Content-Disposition
+(the competency main path already uses the safe helper, so its blank is likely an
+inline-disposition + Acrobat interaction to confirm when fixing).</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-06 screenshot (competency PDF opened as about:blank in Acrobat).</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1277,8 +1277,113 @@
       </c>
       <c r="H17" s="3" t="inlineStr"/>
     </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Milford VeritaMap view-only cascade: every value/date save fails for operator + lab director</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Access fix in PR #1483 (dryRun-verify, then apply). Client UX class bug open. Final confirmation needs a click-test on Milford after the access fix (Gate 3 step 8).
+---</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>S (access fix in flight) + S (client UX class bug)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>High. Blocks Michael and Lisa from editing Milford (labs 4/5) VeritaMap at al...</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>On Milford labs 4 and 5, loading a VeritaMap test menu and entering any
+value (AMR, reference range) or completion date (Cal Verification, Method
+Comparison, Precision, SOP Review) fails to auto-save, throwing a cascade of
+destructive toasts ("AMR not saved" / "Values not saved" / "Auto-save failed").
+Confirmed on BOTH Michael's and Lisa's accounts, on both labs.
+Root cause (two layers):
+ 1. ACCESS (server): the save routes are gated by requireModuleEdit('veritamap')
+ (server/routes.ts ~1038), which passes only lab owner / active admin
+ lab_member / org_admin / active edit seat. Reads only need membership, so the
+ map LOADS but every write 403s "view-only access to veritamap." Neither
+ Michael nor Lisa currently clears that bar on labs 4/5 (a boot-backfill
+ cleanup on 2026-05-24 removed admin rows; add-lab-membership no-ops on an
+ existing row so there was no path to re-grant). FIX IN FLIGHT: PR #1483
+ POST /api/admin/repair-lab-admins grants/promotes both to admin on 4/5.
+ 2. UX CLASS BUG (client): VeritaMapMapPage gates its inputs on
+ useIsReadOnly('veritamap'), which reflects SUBSCRIPTION read-only, NOT
+ per-user seat/membership view-only. A genuine view-only user (e.g. Lis...</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-06 screenshots (lab 4 AMR cascade; lab 5 / Lisa SOP Review "Auto-save failed").</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>VeritaQC LJ chart vs Westgard rule mean-source mismatch (point near chart mean fires 1-3s)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Root cause confirmed in code. Need his lot's live numbers to quantify the customer reply (blocked on live-data access), then the product fix to unify baselines.
+---</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>High. Customer-visible correctness and trust issue; the chart and the rule fl...</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>A QC point can fire the 1-3s rejection rule while the Levey-Jennings
+chart shows it near the mean. Root cause: the two use DIFFERENT baselines. The
+Westgard engine (evaluateWestgardForLot, server/routes.ts ~3717) computes mean/SD
+FRESH from the lab's accepted QC history and flags |value - historyMean| / historySD
+&gt; 3. The LJ chart draws its center line and SD bands from the lot's MANUFACTURER
+insert values (mfr_mean / mfr_sd, the columns the chart-data query pulls at
+server/routes.ts ~4250). When the lab's own running mean/SD differs from the
+manufacturer insert (common once a lab establishes its own stats), a point near the
+mfr mean on the chart can be &gt;3 lab-SD out. Per CLIA/CLSI C24, QC should be
+evaluated against the lab's established mean/SD; the fix is to make the chart plot
+the SAME established mean/SD the rules use (or a consistent mfr-vs-cumulative mode
+applied to both chart and rules).</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Mike Hiltunen (MedStar), 2026-10-06 email "LJ Graph Question". Gameday Plymouth PSA Frend B Level 1, 9/28 point fired 1-3s but sits near the mean on the chart.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -742,74 +742,30 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Plain-language summary layer for verbatim CFR citations</t>
+          <t>Lab leader community / forum (paid subscription idea)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BUILT 2026-10-04 (approach (a)), then EXPANDED 5 -&gt; 35 sections (three tranches: quality systems/PT, pre/analytic/postanalytic + facilities/specimens, and the full CLIA personnel subpart via add_cf...</t>
+          <t>Open. Work-pass 2026-10-04: BUSINESS DECISION, needs Michael. SWOT verdict stands (do not build a paid forum; economics kill it). The recommended free invite-only Slack/Discord plus quarterly round...</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>M (multi-day content authoring across 96 Master List rows if redesigned corre...</t>
+          <t>XL (ongoing operational commitment, not a build) as paid; S (a few days to sp...</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Medium — director readability win; no customer urgency.</t>
+          <t>Low as paid product (SWOT verdict: don't build); Medium as free lead-funnel a...</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>server/cfrRequirements.ts carries verbatim eCFR text in
-the description field (PR #301 closed #26). The verbatim text is
-authoritative but written for regulators, not lab directors. A
-plain-language paraphrase next to the verbatim would help the
-director read faster.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Post-COLA. No customer urgency. Operator
-has not yet authorized a redesign attempt as of 2026-05-21.
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Lab leader community / forum (paid subscription idea)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Open. Work-pass 2026-10-04: BUSINESS DECISION, needs Michael. SWOT verdict stands (do not build a paid forum; economics kill it). The recommended free invite-only Slack/Discord plus quarterly round...</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>XL (ongoing operational commitment, not a build) as paid; S (a few days to sp...</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Low as paid product (SWOT verdict: don't build); Medium as free lead-funnel a...</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Operator-floated 2026-05-22: a vetted online forum for
 laboratory leaders (directors, managers, supervisors). Pricing as
@@ -822,83 +778,83 @@
 lab-leader water cooler.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Post-COLA. No customer urgency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Screen-capture video: VeritaCheck method comparison in 60 seconds</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Open. Re-parked 2026-05-27 (originally PR #117, abandoned with merge conflicts then closed-and-re-authored at current numbering). Pending operator decision on whether to record this themselves or p...</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>S for agent prep (storyboard / pre-fill / captions / checklist); ~1 hour of o...</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Medium — operator selected this as the highest-impact positioning artifact du...</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>30-60 second screen recording demonstrating the "experienced lab tech figures it out in seconds" claim. From blank method-comparison study to completed PDF, no voiceover, no narration, visible cursor motion. Embed autoplay-muted on the marketing site, include in conference follow-up emails.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-12 conversation. Michael selected the screen-cap video as the highest-impact positioning artifact, then asked the agent to record it. Agent does not have screen-recording capability; option parked rather than fudged.</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Post-COLA. No customer urgency.</t>
+          <t>Post-COLA, conference-driven.
+---</t>
         </is>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Screen-capture video: VeritaCheck method comparison in 60 seconds</t>
+          <t>MediaLab parity hardening (VeritaPolicy approval workflow depth)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Open. Re-parked 2026-05-27 (originally PR #117, abandoned with merge conflicts then closed-and-re-authored at current numbering). Pending operator decision on whether to record this themselves or p...</t>
+          <t>Small-item sequence COMPLETE (items 1-5 all shipped; verified against the codebase 2026-09-29, print view PR #1367). Note (2026-10-04): the "delegation" listed here is VeritaPolicy APPROVAL-workflo...</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>S for agent prep (storyboard / pre-fill / captions / checklist); ~1 hour of o...</t>
+          <t>L (1-2 weeks for the high-value items; each independent feature is M)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Medium — operator selected this as the highest-impact positioning artifact du...</t>
+          <t>Medium-High — the C29 build shipped the surface MediaLab markets but depth is...</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30-60 second screen recording demonstrating the "experienced lab tech figures it out in seconds" claim. From blank method-comparison study to completed PDF, no voiceover, no narration, visible cursor motion. Embed autoplay-muted on the marketing site, include in conference follow-up emails.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-12 conversation. Michael selected the screen-cap video as the highest-impact positioning artifact, then asked the agent to record it. Agent does not have screen-recording capability; option parked rather than fudged.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Post-COLA, conference-driven.
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>MediaLab parity hardening (VeritaPolicy approval workflow depth)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Small-item sequence COMPLETE (items 1-5 all shipped; verified against the codebase 2026-09-29, print view PR #1367). Note (2026-10-04): the "delegation" listed here is VeritaPolicy APPROVAL-workflo...</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>L (1-2 weeks for the high-value items; each independent feature is M)</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Medium-High — the C29 build shipped the surface MediaLab markets but depth is...</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>The VeritaPolicy approval workflow build (C29, 2026-05-29) hit roughly 60-70% MediaLab feature surface. The following gaps remain when comparing against an enterprise MediaLab Document Control deployment:
 - Quizzes on attestations. Schema columns quiz_score and quiz_total_questions exist on policy_attestations but the quiz authoring + presentation UI was scoped out of Phase 4. MediaLab labs use 5-10 multiple-choice questions per policy to confirm comprehension, not just attestation. Adds compliance defensibility.
@@ -908,83 +864,83 @@
 - In-browser DOCX editing. MediaLab has a structured editor that creates a Table of Contents from headings. We treat documents as...</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29 QA pass after C29 shipped (qa-policy-build.js + qa-policy-ui.js: 54/54 happy path verified). Honest depth assessment surfaced by Michael's "how confident are you" question — see C29 entry for full QA receipts.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Post-COLA. Defensive against MediaLab in head-to-head sales calls.
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Outbound demo-invite messaging campaign to 1st-degree LinkedIn contacts</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Parked. Plan documented. Implementation deferred until trigger conditions met. Work-pass 2026-10-04: AGENT HALF DELIVERED. Pre-implementation step 5 done: linkedin_search/outbound_messages_v1.md sh...</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>L (1 week prep + 4-6 weeks of staged sends)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>High. Converts existing warm network (~2,500 1st-degree contacts and growing...</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>A staged outbound DM campaign walking Michael's 1st-degree LinkedIn contacts through tier-segmented demo invitations for VeritaAssure. Goal: convert warmest contacts into demo conversations first, then chain into trials and paid subscriptions. Separate pipeline from COLA cohort follow-up and from content-driven inbound; all three feed the same demo funnel but originate from different warmth sources.</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29 QA pass after C29 shipped (qa-policy-build.js + qa-policy-ui.js: 54/54 happy path verified). Honest depth assessment surfaced by Michael's "how confident are you" question — see C29 entry for full QA receipts.</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Post-COLA. Defensive against MediaLab in head-to-head sales calls.
----</t>
-        </is>
-      </c>
+          <t>2026-06-04 session, after weekly LinkedIn invite batch completion (80 sent, cap hit at #84 Victoria Allen).</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Outbound demo-invite messaging campaign to 1st-degree LinkedIn contacts</t>
+          <t>VeritaMap test-menu accuracy audit (menus incomplete, not just missing instruments)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Parked. Plan documented. Implementation deferred until trigger conditions met. Work-pass 2026-10-04: AGENT HALF DELIVERED. Pre-implementation step 5 done: linkedin_search/outbound_messages_v1.md sh...</t>
+          <t>IN PROGRESS. Michael chose Option 2 (exhaustive) 2026-10-06. Executing vendor-by-vendor, sourced and verified against the manufacturer's own parameter lists. Batch 1 (Roche chemistry c-module) reco...</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>L (1 week prep + 4-6 weeks of staged sends)</t>
+          <t>L (3-5 weeks)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>High. Converts existing warm network (~2,500 1st-degree contacts and growing...</t>
+          <t>High — wrong or partial menus surface live in demos and undercut VeritaMap as...</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>A staged outbound DM campaign walking Michael's 1st-degree LinkedIn contacts through tier-segmented demo invitations for VeritaAssure. Goal: convert warmest contacts into demo conversations first, then chain into trials and paid subscriptions. Separate pipeline from COLA cohort follow-up and from content-driven inbound; all three feed the same demo funnel but originate from different warmth sources.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-04 session, after weekly LinkedIn invite batch completion (80 sent, cap hit at #84 Victoria Allen).</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>VeritaMap test-menu accuracy audit (menus incomplete, not just missing instruments)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>IN PROGRESS. Michael chose Option 2 (exhaustive) 2026-10-06. Executing vendor-by-vendor, sourced and verified against the manufacturer's own parameter lists. Batch 1 (Roche chemistry c-module) reco...</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>L (3-5 weeks)</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>High — wrong or partial menus surface live in demos and undercut VeritaMap as...</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Beyond confirming every instrument exists, the per-instrument analyte
 menus in client/src/lib/fdaInstrumentData.json need verification for
@@ -996,87 +952,43 @@
 no fabrication) would make VeritaMap demo-safe across the board.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06 Roche demo.</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>VeritaCheck instrument-verification: multi-select analyte menu (stop adding one by one)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Open. Design presented and approved in principle; awaiting explicit go to build.
----</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>VeritaComp legacy program modal shows no VeritaStaff employees (Option 2)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Open. Approved ("build it that way"); code paths already traced; ready to build.
+---
+_(item #60 closed 2026-10-07; 74 CAP programs loaded 2026-10-06, see C64 below)_
+---</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>High — core usability of the instrument-verification flow; cumbersome enough...</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>On a new Instrument Verification Package, analytes are added one at a
-time via free text. The existing "FDA-cleared" dropdown only renders when the
-verification is linked to a VeritaMap instrument (map_instrument_id), which
-standalone verifications lack, and even then it is single-select. Fix: source
-the menu from fdaInstrumentData.json by the verification's instrument name
-(e.g., Sysmex XN-2000 = 40 analytes), show a multi-select checklist with
-Select-all, and bulk-insert in one transaction (new bulk endpoint). Keep
-free-text for custom analytes.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-06 screenshot (/labs/3/dashboard/verifications).</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>VeritaComp legacy program modal shows no VeritaStaff employees (Option 2)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Open. Approved ("build it that way"); code paths already traced; ready to build.
----</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>S (1-3 days)</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Medium — fixes a confusing dead-end next to the employee-centric flow; mostly...</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>The legacy "New Technical Assessment" program modal reads
 competency_employees (empty for most labs) instead of VeritaStaff's
@@ -1088,86 +1000,43 @@
 idempotent bridge). Fixes the roster drift rather than hiding the flow.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06.</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>VeritaPT: load the CAP vendor program catalog (Program Name dropdown for CAP)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Open. Diagnosed; awaiting go to compile the CAP list for verification.
----</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>S (1-3 days)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>High — CAP is the dominant PT vendor; free-text entry looks broken in demos.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>The Program Name field becomes a dropdown only when the vendor's
-catalog is loaded in pt_vendor_programs. API is loaded; CAP is not, so CAP
-falls back to free text ("No CAP catalog loaded yet"). By design the system
-refuses to invent catalog rows — CAP data must be vendor-sourced and
-operator-verified. Fix: compile the real CAP Survey programs across the 10 PT
-categories, present for Michael's verification, then load via
-POST /api/admin/veritapt/vendor-programs. No code change; data load only.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-06 screenshot (PT Program Enrollments modal).</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>VeritaMap: remove duplicate demo maps (dedupe tool shipped; awaiting selection)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Open. Tool live; awaiting Michael's deletion selection.
----</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+---
+_(item #62 closed 2026-10-07; PR #1474 merged + deployed 2026-10-06, see C65 below)_
+---</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day)</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Low-Medium — demo-lab hygiene; not customer-facing.</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Michael created many maps while demoing and asked to remove
 duplicates. The read-only-by-default admin dedupe-maps endpoint shipped
@@ -1178,84 +1047,43 @@
 with full cascade once he approves the ids.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06.</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Vendor instrument expansion PR #1474 (25 platforms; awaiting complexity sign-off)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Open. PR green; awaiting merge approval.
----</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>XS (under 1 day)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Medium — closes demo-reported instrument gaps for Bio-Rad, Tosoh, Horiba, and...</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>PR #1474 adds 25 current platforms to fdaInstrumentData.json with
-FDA-anchored CLIA complexity (269 -&gt; 294 instruments). Held for Michael's
-sign-off because complexity is a regulatory property and his call. Green and
-ready; once approved, merge and confirm the new instruments appear in the
-VeritaMap instrument search on prod.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-06.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Open. Root cause diagnosed; mechanical class fix ready to slot in on request.
----</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+---
+_(item #64 closed 2026-10-07; three real causes fixed, PR #1486 + #1487 deployed, see C66 below)_
+---</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Medium — intermittent, customer-facing failure on PDF deliverables (studies,...</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Some PDF opens land on an about:blank tab instead of the document.
 Root cause: the fragile window.open('/api/pdf/&lt;one-time-token&gt;') pattern, still
@@ -1270,96 +1098,40 @@
 inline-disposition + Acrobat interaction to confirm when fixing).</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06 screenshot (competency PDF opened as about:blank in Acrobat).</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Milford VeritaMap view-only cascade: every value/date save fails for operator + lab director</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Access fix in PR #1483 (dryRun-verify, then apply). Client UX class bug open. Final confirmation needs a click-test on Milford after the access fix (Gate 3 step 8).
----</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>S (access fix in flight) + S (client UX class bug)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>High. Blocks Michael and Lisa from editing Milford (labs 4/5) VeritaMap at al...</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>On Milford labs 4 and 5, loading a VeritaMap test menu and entering any
-value (AMR, reference range) or completion date (Cal Verification, Method
-Comparison, Precision, SOP Review) fails to auto-save, throwing a cascade of
-destructive toasts ("AMR not saved" / "Values not saved" / "Auto-save failed").
-Confirmed on BOTH Michael's and Lisa's accounts, on both labs.
-Root cause (two layers):
- 1. ACCESS (server): the save routes are gated by requireModuleEdit('veritamap')
- (server/routes.ts ~1038), which passes only lab owner / active admin
- lab_member / org_admin / active edit seat. Reads only need membership, so the
- map LOADS but every write 403s "view-only access to veritamap." Neither
- Michael nor Lisa currently clears that bar on labs 4/5 (a boot-backfill
- cleanup on 2026-05-24 removed admin rows; add-lab-membership no-ops on an
- existing row so there was no path to re-grant). FIX IN FLIGHT: PR #1483
- POST /api/admin/repair-lab-admins grants/promotes both to admin on 4/5.
- 2. UX CLASS BUG (client): VeritaMapMapPage gates its inputs on
- useIsReadOnly('veritamap'), which reflects SUBSCRIPTION read-only, NOT
- per-user seat/membership view-only. A genuine view-only user (e.g. Lis...</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-06 screenshots (lab 4 AMR cascade; lab 5 / Lisa SOP Review "Auto-save failed").</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>VeritaQC LJ chart vs Westgard rule mean-source mismatch (point near chart mean fires 1-3s)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Root cause confirmed in code. Need his lot's live numbers to quantify the customer reply (blocked on live-data access), then the product fix to unify baselines.
----</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Root cause confirmed in code AND in data (2026-10-07, read-only prod copy): lab 29 Gameday Plymouth, lot 27 "PSA (FREND B)" Level 1 (6361A26001), manufacturer mean 1.29 / SD 0.35; lab history n=30...</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>High. Customer-visible correctness and trust issue; the chart and the rule fl...</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>A QC point can fire the 1-3s rejection rule while the Levey-Jennings
 chart shows it near the mean. Root cause: the two use DIFFERENT baselines. The
@@ -1375,15 +1147,320 @@
 applied to both chart and rules).</t>
         </is>
       </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Mike Hiltunen (MedStar), 2026-10-06 email "LJ Graph Question". Gameday Plymouth PSA Frend B Level 1, 9/28 point fired 1-3s but sits near the mean on the chart.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Open. Root-caused. Fix: NAME_MAP-aware hasCanonicalTea, CFR section derived from the analyte's specialty, extend scripts/verify-canonical-tea-matching.js.
+---</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>High. Customer-facing PDF regulatory language on hematology studies.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>hasCanonicalTea() (server/backfillAbsoluteFloor.ts:119) matches aliases
+built from the TEa table but never consults NAME_MAP, so plain "Hemoglobin" /
+"HGB" / "Hgb" (which NAME_MAP maps to "CBC - Hemoglobin" for the floor) renders
+as a laboratory-defined goal ("Lab-Set Internal Goal", "per laboratory director
+or designee policy") instead of the CLIA TEa. Separately, pdfReport.ts:1219 reads
+study.cfr, which nothing ever sets, so every narrative cites 42 CFR 493.931
+(Chemistry), including hematology studies that should cite 493.941. PR #1466
+fixed the lookup table and the public article only, not this engine path.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>QA sweep 2026-10-04 21:07 (memory project_veritacheck_tea_canonicalization_bug).</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Open. Needs a verify script over the actual per-sample and aggregate logic with a dual-criterion case, then Michael's regulatory call.
+---</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The 2026-10-04 sweep claimed a method-comparison study can FAIL on
+aggregate mean |bias| while every sample passes. Michael: "If every sample has to
+be a pass, it is not possible for the aggregate to be a fail." The assistant
+conceded the claim was sloppy and that it is only possible for dual-criterion
+analytes (percent OR absolute floor), then never resolved whether the override
+(server/routes.ts ~395-420) is a real defect or correct behavior.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-04 21:58-22:03.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Open. Fix: client sends the active band; server scopes by (map_id, analyte, age_min_days, age_max_days, sex) with the All-ages default for old clients.
+---</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Medium-High. 42 CFR 493.1253 attestation provenance.</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>attest-ref, unlock-ref and mec-review (server/routes.ts ~14714 /
+14743 / 14770) run UPDATE veritamap_analyte_values ... WHERE map_id = ? AND analyte = ?
+without the band key, so attesting the adult band also attests and locks every
+pediatric band, and unlocking unlocks all of them; the client never sends the
+band. (The CFR default to 493.931 for a specialty missing from CFR_MAP, flagged
+in the same sweep, is BY DESIGN per CLAUDE.md section 5 and is not a defect.)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>VeritaMap sweep 2026-10-05 10:30.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Open. Identify the 4 studies, fix the shape read, and make the boot recompute SKIP (not fail) any study it cannot evaluate.
+---</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>High. Verdict integrity.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>The Railway log shows, on every boot since at least the 2026-10-06
+19:49Z deploy, four lines of [computeStudyStatus] Error recomputing status:
+TypeError: Cannot read properties of undefined (reading 'Beckman AU5800 Primary
+vs Beckman AU5800 Backup'). computeStudyStatus returns "fail" on any
+exception, and recomputeAllStudyStatuses() writes that verdict back whenever it
+differs from the stored one, so a study whose data shape the recompute cannot read
+is silently marked FAIL at boot.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>prod log, noticed 2026-10-06 20:46 ET.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Open. Fix: snapshot the real-user email list in backup_integrity_log, diff and NAME the dropped accounts, audit-log admin deletions, and classify a drop as explained (note) vs unexplained (anomaly)...</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>checkBackupIntegrity (server/backup.ts:170) alerts whenever
+real_user_count is below the previous run, with zero tolerance and no record of
+WHICH account disappeared; DELETE /api/admin/users/:id only console.logs the
+deletion. Intentional deletions (Tywauna 2026-10-05; 54 -&gt; 53 on 2026-10-06)
+therefore produce an ANOMALY email that reads like data loss.</t>
+        </is>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Mike Hiltunen (MedStar), 2026-10-06 email "LJ Graph Question". Gameday Plymouth PSA Frend B Level 1, 9/28 point fired 1-3s but sits near the mean on the chart.</t>
+          <t>VLS Leads 2026-10-06 20:32; bug report written 20:37.</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
     </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Milford (labs 4/5) house policy format for VeritaDC drafts</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Not started. Needs a per-lab DOCX template option (design, then build).
+---</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>M (multi-day)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Medium. Lisa's lab.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>"Update the UMASS Milford sites to this policy template." The house
+format (sections I-V, revision table, footer) was extracted from the sample DOCX
+on 2026-10-06 13:21 but was never built into the VeritaDC DOCX generator for labs
+4 and 5.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-06 ~13:19 (.eml).</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>In-app Getting Started wizard (per-module checklists inside the system)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Not started. Design needed (where it lives, what "done" reads from).
+---</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>M (multi-day)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>The public /resources/getting-started page shipped (PR #1480).
+Michael: "Love it being built into the system." The in-app per-module checklist
+(progress read from the lab's actual state) was stated as a follow-up and not
+started.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-06 13:15.</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H19"/>
+  <autoFilter ref="A1:H21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1394,7 +1471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1452,24 +1529,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C61</t>
+          <t>C66</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
+          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Low</t>
+          <t>was S + S / Importance: High</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Low</t>
+          <t>Effort: was S + S / Importance: High</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1478,24 +1555,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C60</t>
+          <t>C65</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
+          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Low</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Low</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1504,24 +1581,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C59</t>
+          <t>C64</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Confirm the finding-closure signer policy (was #43)</t>
+          <t>VeritaPT CAP vendor program catalog (was #60)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1530,24 +1607,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C58</t>
+          <t>C63</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
+          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1556,24 +1633,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C62</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list (was #47)</t>
+          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>was M / Importance: Medium</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>Effort: was M / Importance: Medium</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1582,24 +1659,24 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C61</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
+          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Low-Medium</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Low-Medium</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1608,24 +1685,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1634,24 +1711,24 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>Confirm the finding-closure signer policy (was #43)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1660,24 +1737,24 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1686,24 +1763,24 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1712,24 +1789,24 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1738,24 +1815,24 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1764,24 +1841,24 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1790,24 +1867,24 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1816,24 +1893,24 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1842,147 +1919,142 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>was S-M / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S-M / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>was S-M / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S-M / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>was S-M / Importance: Medium-High</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S-M / Importance: Medium-High</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr"/>
     </row>
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
----</t>
-        </is>
-      </c>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
@@ -1990,12 +2062,12 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -2004,12 +2076,12 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
@@ -2017,12 +2089,12 @@
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -2031,12 +2103,12 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
@@ -2044,12 +2116,12 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -2058,12 +2130,12 @@
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
@@ -2071,12 +2143,12 @@
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -2085,12 +2157,12 @@
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
@@ -2098,12 +2170,12 @@
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -2112,12 +2184,12 @@
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
@@ -2125,12 +2197,12 @@
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -2139,18 +2211,153 @@
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+---</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>C39</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+---</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>C38</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+---</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -2162,24 +2369,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -2189,24 +2396,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -2214,30 +2421,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -2248,30 +2455,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -2282,29 +2489,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -2315,57 +2522,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -2378,7 +2585,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -2386,109 +2593,109 @@
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: site-wide search confirmed all surveyor language
 is past-tense, consistent with user's 2021-2025 service. User closed
 the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
 /api/my-studies/export. server/routes.ts line 1491 implements the
 endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: no ghp_* or github_pat_* patterns in current
 SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2497,29 +2704,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2530,30 +2737,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2563,59 +2770,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2630,29 +2837,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2660,29 +2867,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2697,56 +2904,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2764,64 +2971,64 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
 features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaCheck™ already ships the Precision /
 Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
@@ -2829,23 +3036,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
@@ -2853,29 +3060,29 @@
 shipped:</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -2886,7 +3093,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2894,23 +3101,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2921,7 +3128,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2929,23 +3136,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2956,7 +3163,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2965,23 +3172,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2994,7 +3201,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -3003,30 +3210,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="90" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -3035,262 +3242,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="90" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="90" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="90" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="90" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="90" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="90" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="90" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="90" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61" ht="90" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="90" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62" ht="90" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="90" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H62"/>
+  <autoFilter ref="A1:H67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1023,7 +1023,8 @@
           <t>Open. Tool live; awaiting Michael's deletion selection.
 ---
 _(item #62 closed 2026-10-07; PR #1474 merged + deployed 2026-10-06, see C65 below)_
----</t>
+---
+_(item #63 closed 2026-10-07; PR #1493 deplo...</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1057,81 +1058,30 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat)</t>
+          <t>VeritaQC LJ chart vs Westgard rule mean-source mismatch (point near chart mean fires 1-3s)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Open. Root cause diagnosed; mechanical class fix ready to slot in on request.
----
-_(item #64 closed 2026-10-07; three real causes fixed, PR #1486 + #1487 deployed, see C66 below)_
----</t>
+          <t>Root cause confirmed in code AND in data (2026-10-07, read-only prod copy): lab 29 Gameday Plymouth, lot 27 "PSA (FREND B)" Level 1 (6361A26001), manufacturer mean 1.29 / SD 0.35; lab history n=30...</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>S (1-3 days)</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Medium — intermittent, customer-facing failure on PDF deliverables (studies,...</t>
+          <t>High. Customer-visible correctness and trust issue; the chart and the rule fl...</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Some PDF opens land on an about:blank tab instead of the document.
-Root cause: the fragile window.open('/api/pdf/&lt;one-time-token&gt;') pattern, still
-used on ~6 paths (VeritaOps, VeritaPace, VeritaQA, VeritaResponse x3, the
-Why-VeritaCheck article, CMS-116). With Adobe Acrobat as the PDF handler it opens
-a blank tab while Acrobat grabs the PDF, orphaning about:blank, and worse when
-the one-time token GET races or expires (the PR #286 class). Most downloads were
-migrated to the safe anchor helper downloadPdfToken (client/src/lib/utils.ts),
-which is why it is "mostly removed." Fix: route every remaining PDF open through
-the safe download helper, and verify the /api/pdf server Content-Disposition
-(the competency main path already uses the safe helper, so its blank is likely an
-inline-disposition + Acrobat interaction to confirm when fixing).</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-06 screenshot (competency PDF opened as about:blank in Acrobat).</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>VeritaQC LJ chart vs Westgard rule mean-source mismatch (point near chart mean fires 1-3s)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Root cause confirmed in code AND in data (2026-10-07, read-only prod copy): lab 29 Gameday Plymouth, lot 27 "PSA (FREND B)" Level 1 (6361A26001), manufacturer mean 1.29 / SD 0.35; lab history n=30...</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>High. Customer-visible correctness and trust issue; the chart and the rule fl...</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>A QC point can fire the 1-3s rejection rule while the Levey-Jennings
 chart shows it near the mean. Root cause: the two use DIFFERENT baselines. The
@@ -1147,87 +1097,40 @@
 applied to both chart and rules).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Mike Hiltunen (MedStar), 2026-10-06 email "LJ Graph Question". Gameday Plymouth PSA Frend B Level 1, 9/28 point fired 1-3s but sits near the mean on the chart.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Open. Root-caused. Fix: NAME_MAP-aware hasCanonicalTea, CFR section derived from the analyte's specialty, extend scripts/verify-canonical-tea-matching.js.
----</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Receipt done 2026-10-07 (tests/integration/d1-aggregate-override.test.ts, real engine via recomputeAllStudyStatuses): percent-only and absolute-only TEa with every sample passing stay PASS, and a 2...</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>High. Customer-facing PDF regulatory language on hematology studies.</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>hasCanonicalTea() (server/backfillAbsoluteFloor.ts:119) matches aliases
-built from the TEa table but never consults NAME_MAP, so plain "Hemoglobin" /
-"HGB" / "Hgb" (which NAME_MAP maps to "CBC - Hemoglobin" for the floor) renders
-as a laboratory-defined goal ("Lab-Set Internal Goal", "per laboratory director
-or designee policy") instead of the CLIA TEa. Separately, pdfReport.ts:1219 reads
-study.cfr, which nothing ever sets, so every narrative cites 42 CFR 493.931
-(Chemistry), including hematology studies that should cite 493.941. PR #1466
-fixed the lookup table and the public article only, not this engine path.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>QA sweep 2026-10-04 21:07 (memory project_veritacheck_tea_canonicalization_bug).</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Open. Needs a verify script over the actual per-sample and aggregate logic with a dual-criterion case, then Michael's regulatory call.
----</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>S (1-3 days)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>The 2026-10-04 sweep claimed a method-comparison study can FAIL on
 aggregate mean |bias| while every sample passes. Michael: "If every sample has to
@@ -1237,172 +1140,40 @@
 (server/routes.ts ~395-420) is a real defect or correct behavior.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Michael, 2026-10-04 21:58-22:03.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Open. Fix: client sends the active band; server scopes by (map_id, analyte, age_min_days, age_max_days, sex) with the All-ages default for old clients.
----</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>S (1-3 days)</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Medium-High. 42 CFR 493.1253 attestation provenance.</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>attest-ref, unlock-ref and mec-review (server/routes.ts ~14714 /
-14743 / 14770) run UPDATE veritamap_analyte_values ... WHERE map_id = ? AND analyte = ?
-without the band key, so attesting the adult band also attests and locks every
-pediatric band, and unlocking unlocks all of them; the client never sends the
-band. (The CFR default to 493.931 for a specialty missing from CFR_MAP, flagged
-in the same sweep, is BY DESIGN per CLAUDE.md section 5 and is not a defect.)</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>VeritaMap sweep 2026-10-05 10:30.</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Open. Identify the 4 studies, fix the shape read, and make the boot recompute SKIP (not fail) any study it cannot evaluate.
----</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>S (1-3 days)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>High. Verdict integrity.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>The Railway log shows, on every boot since at least the 2026-10-06
-19:49Z deploy, four lines of [computeStudyStatus] Error recomputing status:
-TypeError: Cannot read properties of undefined (reading 'Beckman AU5800 Primary
-vs Beckman AU5800 Backup'). computeStudyStatus returns "fail" on any
-exception, and recomputeAllStudyStatuses() writes that verdict back whenever it
-differs from the stored one, so a study whose data shape the recompute cannot read
-is silently marked FAIL at boot.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>prod log, noticed 2026-10-06 20:46 ET.</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Open. Fix: snapshot the real-user email list in backup_integrity_log, diff and NAME the dropped accounts, audit-log admin deletions, and classify a drop as explained (note) vs unexplained (anomaly)...</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>S (1-3 days)</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>checkBackupIntegrity (server/backup.ts:170) alerts whenever
-real_user_count is below the previous run, with zero tolerance and no record of
-WHICH account disappeared; DELETE /api/admin/users/:id only console.logs the
-deletion. Intentional deletions (Tywauna 2026-10-05; 54 -&gt; 53 on 2026-10-06)
-therefore produce an ANOMALY email that reads like data loss.</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>VLS Leads 2026-10-06 20:32; bug report written 20:37.</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Milford (labs 4/5) house policy format for VeritaDC drafts</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Not started. Needs a per-lab DOCX template option (design, then build).
----</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>DESIGN written 2026-10-07: docs/VERITADC_HOUSE_FORMAT_DESIGN.md (per-lab docx_format setting, a format registry in veritapolicyDocx.ts rendering I. Purpose / II. Policy / III. Guidelines / IV. Pers...</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>M (multi-day)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Medium. Lisa's lab.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>"Update the UMASS Milford sites to this policy template." The house
 format (sections I-V, revision table, footer) was extracted from the sample DOCX
@@ -1410,41 +1181,40 @@
 4 and 5.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06 ~13:19 (.eml).</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>In-app Getting Started wizard (per-module checklists inside the system)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Not started. Design needed (where it lives, what "done" reads from).
----</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>DESIGN written 2026-10-07: docs/IN_APP_GETTING_STARTED_DESIGN.md (reuses gettingStartedContent.ts as the single source; GET /api/labs/:labId/getting-started derives every step's status from real ta...</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>M (multi-day)</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>The public /resources/getting-started page shipped (PR #1480).
 Michael: "Love it being built into the system." The in-app per-module checklist
@@ -1452,15 +1222,62 @@
 started.</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06 13:15.</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Env-gated Playwright specs never run in CI; two shipped unrunnable</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Open. Specs repaired and shipped; the CI token/QA-lab decision is Michael's (cost: one seeded demo lab on prod plus a repo secret).
+---</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Medium. The Gate 3 step 8 receipts for authenticated UI are skipped in CI (no...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>playwright-smoke runs 74 specs as "skip without PW_TOKEN". The
+2026-10-07 local pass over merged UI PRs found two that could never pass as
+written: module-howto-card-layout.spec (#1472) used two routes that do not
+exist and measured the width of a text node, and
+veritacheck-analyte-multiselect.spec (#1481) looked for a button that lives on
+a package's Analytes tab, not the list page. Both repaired in PR #1493 and
+proven on a local build (5/5 and 1/1). The fixes themselves were fine; the
+receipts were not. A CI QA lab with a scoped PW_TOKEN secret (own test
+system, never a client lab) would run these on every PR.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>overnight audit 2026-10-07 (local Playwright pass, see overnight log section 16).</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H21"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1471,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1529,24 +1346,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C66</t>
+          <t>C72</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
+          <t>Nightly backup studyCount anomaly on every user-deleted study (was #73)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was S + S / Importance: High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S + S / Importance: High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1555,24 +1372,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C65</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
+          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody (was #70)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1581,12 +1398,12 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C64</t>
+          <t>C70</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VeritaPT CAP vendor program catalog (was #60)</t>
+          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL (was #69)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -1607,24 +1424,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C63</t>
+          <t>C69</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
+          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte (was #68)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1633,24 +1450,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C62</t>
+          <t>C68</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
+          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931 (was #66)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1659,24 +1476,24 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C61</t>
+          <t>C67</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
+          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat) (was #63)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Low</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Low</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1685,24 +1502,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C60</t>
+          <t>C66</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
+          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Low</t>
+          <t>was S + S / Importance: High</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Low</t>
+          <t>Effort: was S + S / Importance: High</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1711,12 +1528,12 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C59</t>
+          <t>C65</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Confirm the finding-closure signer policy (was #43)</t>
+          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
@@ -1737,24 +1554,24 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C58</t>
+          <t>C64</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
+          <t>VeritaPT CAP vendor program catalog (was #60)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1763,24 +1580,24 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C63</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list (was #47)</t>
+          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1789,24 +1606,24 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C62</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
+          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Low-Medium</t>
+          <t>was M / Importance: Medium</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Low-Medium</t>
+          <t>Effort: was M / Importance: Medium</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1815,24 +1632,24 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C61</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1841,24 +1658,24 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1867,24 +1684,24 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>Confirm the finding-closure signer policy (was #43)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1893,24 +1710,24 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1919,24 +1736,24 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1945,24 +1762,24 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1971,24 +1788,24 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1997,24 +1814,24 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -2023,24 +1840,24 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -2049,174 +1866,168 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>was S-M / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S-M / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr"/>
     </row>
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>was S-M / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S-M / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>was S-M / Importance: Medium-High</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
----</t>
-        </is>
-      </c>
+          <t>Effort: was S-M / Importance: Medium-High</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
----</t>
-        </is>
-      </c>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
@@ -2224,12 +2035,12 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -2238,12 +2049,12 @@
     <row r="29" ht="90" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
@@ -2251,12 +2062,12 @@
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -2265,12 +2076,12 @@
     <row r="30" ht="90" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
@@ -2278,12 +2089,12 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -2292,12 +2103,12 @@
     <row r="31" ht="90" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
@@ -2305,12 +2116,12 @@
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -2319,12 +2130,12 @@
     <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
@@ -2332,12 +2143,12 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -2346,18 +2157,180 @@
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+---</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>C40</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+---</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>C39</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+---</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>C38</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+---</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -2369,24 +2342,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -2396,24 +2369,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -2421,30 +2394,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -2455,30 +2428,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -2489,29 +2462,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -2522,57 +2495,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -2585,7 +2558,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -2593,109 +2566,109 @@
 ---</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: site-wide search confirmed all surveyor language
 is past-tense, consistent with user's 2021-2025 service. User closed
 the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
 /api/my-studies/export. server/routes.ts line 1491 implements the
 endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: no ghp_* or github_pat_* patterns in current
 SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2704,29 +2677,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2737,30 +2710,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2770,59 +2743,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2837,29 +2810,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2867,29 +2840,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2904,56 +2877,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2971,64 +2944,64 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
 features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="90" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaCheck™ already ships the Precision /
 Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
@@ -3036,23 +3009,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="90" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
@@ -3060,29 +3033,29 @@
 shipped:</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="90" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -3093,7 +3066,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -3101,23 +3074,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="90" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -3128,7 +3101,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -3136,23 +3109,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="90" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="90" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -3163,7 +3136,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -3172,23 +3145,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="90" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="90" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -3201,7 +3174,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -3210,30 +3183,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="90" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="90" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -3242,262 +3215,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61" ht="90" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="90" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62" ht="90" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="90" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63" ht="90" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="90" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr"/>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64" ht="90" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="90" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65" ht="90" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="90" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66" ht="90" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72" ht="90" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67" ht="90" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="90" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H67"/>
+  <autoFilter ref="A1:H73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -962,63 +962,15 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp legacy program modal shows no VeritaStaff employees (Option 2)</t>
+          <t>VeritaMap: remove duplicate demo maps (dedupe tool shipped; awaiting selection)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Open. Approved ("build it that way"); code paths already traced; ready to build.
----
-_(item #60 closed 2026-10-07; 74 CAP programs loaded 2026-10-06, see C64 below)_
----</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>S (1-3 days)</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Medium — fixes a confusing dead-end next to the employee-centric flow; mostly...</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>The legacy "New Technical Assessment" program modal reads
-competency_employees (empty for most labs) instead of VeritaStaff's
-staff_employees, so it says "No active employees" even when staff are
-assigned the program's instruments (observed on lab 5 / Alecia Lillico-Perry
-with the Atellica CH 930). Michael chose Option 2: populate the modal with the
-lab's active VeritaStaff employees who are assigned the program's instruments,
-auto-bridged into competency_employees on the fly (reusing the existing
-idempotent bridge). Fixes the roster drift rather than hiding the flow.</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-06.</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>VeritaMap: remove duplicate demo maps (dedupe tool shipped; awaiting selection)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Open. Tool live; awaiting Michael's deletion selection.
 ---
@@ -1027,17 +979,17 @@
 _(item #63 closed 2026-10-07; PR #1493 deplo...</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Low-Medium — demo-lab hygiene; not customer-facing.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Michael created many maps while demoing and asked to remove
 duplicates. The read-only-by-default admin dedupe-maps endpoint shipped
@@ -1048,40 +1000,40 @@
 with full cascade once he approves the ids.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>VeritaQC LJ chart vs Westgard rule mean-source mismatch (point near chart mean fires 1-3s)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Root cause confirmed in code AND in data (2026-10-07, read-only prod copy): lab 29 Gameday Plymouth, lot 27 "PSA (FREND B)" Level 1 (6361A26001), manufacturer mean 1.29 / SD 0.35; lab history n=30...</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>High. Customer-visible correctness and trust issue; the chart and the rule fl...</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>A QC point can fire the 1-3s rejection rule while the Levey-Jennings
 chart shows it near the mean. Root cause: the two use DIFFERENT baselines. The
@@ -1097,40 +1049,40 @@
 applied to both chart and rules).</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Mike Hiltunen (MedStar), 2026-10-06 email "LJ Graph Question". Gameday Plymouth PSA Frend B Level 1, 9/28 point fired 1-3s but sits near the mean on the chart.</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Receipt done 2026-10-07 (tests/integration/d1-aggregate-override.test.ts, real engine via recomputeAllStudyStatuses): percent-only and absolute-only TEa with every sample passing stay PASS, and a 2...</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>The 2026-10-04 sweep claimed a method-comparison study can FAIL on
 aggregate mean |bias| while every sample passes. Michael: "If every sample has to
@@ -1140,40 +1092,40 @@
 (server/routes.ts ~395-420) is a real defect or correct behavior.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-04 21:58-22:03.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Milford (labs 4/5) house policy format for VeritaDC drafts</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>DESIGN written 2026-10-07: docs/VERITADC_HOUSE_FORMAT_DESIGN.md (per-lab docx_format setting, a format registry in veritapolicyDocx.ts rendering I. Purpose / II. Policy / III. Guidelines / IV. Pers...</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>M (multi-day)</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Medium. Lisa's lab.</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>"Update the UMASS Milford sites to this policy template." The house
 format (sections I-V, revision table, footer) was extracted from the sample DOCX
@@ -1181,40 +1133,40 @@
 4 and 5.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06 ~13:19 (.eml).</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>In-app Getting Started wizard (per-module checklists inside the system)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>DESIGN written 2026-10-07: docs/IN_APP_GETTING_STARTED_DESIGN.md (reuses gettingStartedContent.ts as the single source; GET /api/labs/:labId/getting-started derives every step's status from real ta...</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>M (multi-day)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>The public /resources/getting-started page shipped (PR #1480).
 Michael: "Love it being built into the system." The in-app per-module checklist
@@ -1222,41 +1174,41 @@
 started.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06 13:15.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Env-gated Playwright specs never run in CI; two shipped unrunnable</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Open. Specs repaired and shipped; the CI token/QA-lab decision is Michael's (cost: one seeded demo lab on prod plus a repo secret).
 ---</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Medium. The Gate 3 step 8 receipts for authenticated UI are skipped in CI (no...</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>playwright-smoke runs 74 specs as "skip without PW_TOKEN". The
 2026-10-07 local pass over merged UI PRs found two that could never pass as
@@ -1269,15 +1221,15 @@
 system, never a client lab) would run these on every PR.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>overnight audit 2026-10-07 (local Playwright pass, see overnight log section 16).</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1288,7 +1240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1346,24 +1298,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C72</t>
+          <t>C73</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Nightly backup studyCount anomaly on every user-deleted study (was #73)</t>
+          <t>VeritaComp legacy program modal shows no VeritaStaff employees (was #59)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1372,24 +1324,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C71</t>
+          <t>C72</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody (was #70)</t>
+          <t>Nightly backup studyCount anomaly on every user-deleted study (was #73)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1398,24 +1350,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C70</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL (was #69)</t>
+          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody (was #70)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1424,24 +1376,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C69</t>
+          <t>C70</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte (was #68)</t>
+          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL (was #69)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium-High</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1450,24 +1402,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C68</t>
+          <t>C69</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931 (was #66)</t>
+          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte (was #68)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1476,24 +1428,24 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C67</t>
+          <t>C68</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat) (was #63)</t>
+          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931 (was #66)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1502,24 +1454,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C66</t>
+          <t>C67</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
+          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat) (was #63)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>was S + S / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S + S / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1528,24 +1480,24 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C65</t>
+          <t>C66</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
+          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S + S / Importance: High</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S + S / Importance: High</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1554,24 +1506,24 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C64</t>
+          <t>C65</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaPT CAP vendor program catalog (was #60)</t>
+          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1580,12 +1532,12 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C63</t>
+          <t>C64</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
+          <t>VeritaPT CAP vendor program catalog (was #60)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
@@ -1606,24 +1558,24 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C62</t>
+          <t>C63</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
+          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1632,24 +1584,24 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C61</t>
+          <t>C62</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
+          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Low</t>
+          <t>was M / Importance: Medium</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Low</t>
+          <t>Effort: was M / Importance: Medium</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1658,12 +1610,12 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C60</t>
+          <t>C61</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
+          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -1684,24 +1636,24 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C59</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Confirm the finding-closure signer policy (was #43)</t>
+          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1710,24 +1662,24 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C58</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
+          <t>Confirm the finding-closure signer policy (was #43)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1736,24 +1688,24 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list (was #47)</t>
+          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1762,24 +1714,24 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Low-Medium</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Low-Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1788,24 +1740,24 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1814,24 +1766,24 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1840,24 +1792,24 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -1866,24 +1818,24 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1892,24 +1844,24 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -1918,12 +1870,12 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
@@ -1944,24 +1896,24 @@
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
@@ -1970,24 +1922,24 @@
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1996,24 +1948,24 @@
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -2022,39 +1974,38 @@
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="90" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
@@ -2062,12 +2013,12 @@
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -2076,12 +2027,12 @@
     <row r="30" ht="90" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
@@ -2089,12 +2040,12 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -2103,12 +2054,12 @@
     <row r="31" ht="90" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
@@ -2116,12 +2067,12 @@
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -2130,12 +2081,12 @@
     <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
@@ -2143,12 +2094,12 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -2157,12 +2108,12 @@
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
@@ -2170,12 +2121,12 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -2184,12 +2135,12 @@
     <row r="34" ht="90" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
@@ -2197,12 +2148,12 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -2211,12 +2162,12 @@
     <row r="35" ht="90" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
@@ -2224,12 +2175,12 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -2238,12 +2189,12 @@
     <row r="36" ht="90" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
@@ -2251,12 +2202,12 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -2265,12 +2216,12 @@
     <row r="37" ht="90" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
@@ -2278,12 +2229,12 @@
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -2292,12 +2243,12 @@
     <row r="38" ht="90" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
@@ -2305,7 +2256,7 @@
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2319,18 +2270,45 @@
     <row r="39" ht="90" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -2342,24 +2320,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -2369,24 +2347,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -2394,30 +2372,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -2428,30 +2406,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -2462,29 +2440,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -2495,37 +2473,9 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
----</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
-23 years" as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2534,18 +2484,46 @@
     <row r="46" ht="90" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
+23 years" as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 14, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -2558,7 +2536,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -2566,46 +2544,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H47" s="3" t="inlineStr"/>
     </row>
     <row r="48" ht="90" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
@@ -2613,14 +2562,14 @@
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
+          <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2629,12 +2578,12 @@
     <row r="49" ht="90" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr"/>
@@ -2642,13 +2591,14 @@
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>session 299e9a73, ~2026-04-28.
+          <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2657,18 +2607,46 @@
     <row r="50" ht="90" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2677,29 +2655,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2710,30 +2688,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2743,59 +2721,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Tier-1 smoke test checklist (formerly #6)</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
-smoke-test process and post-deploy verification steps. Shipped via
-PR #81 as part of the 2026-05-10 wave.</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
       <c r="H53" s="3" t="inlineStr"/>
     </row>
     <row r="54" ht="90" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Per-module gating (formerly #7)</t>
+          <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
+smoke-test process and post-deploy verification steps. Shipped via
+PR #81 as part of the 2026-05-10 wave.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Per-module gating (formerly #7)</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2810,29 +2788,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2840,29 +2818,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2877,33 +2855,6 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
-        </is>
-      </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
@@ -2915,18 +2866,45 @@
     <row r="58" ht="90" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>WSLH PT vendor (formerly #15)</t>
+          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>WSLH PT vendor (formerly #15)</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2944,38 +2922,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="90" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2984,12 +2933,12 @@
     <row r="60" ht="90" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
@@ -2997,15 +2946,14 @@
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
+Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -3014,12 +2962,12 @@
     <row r="61" ht="90" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr"/>
@@ -3027,35 +2975,65 @@
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="90" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62" ht="90" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="90" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -3066,7 +3044,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -3074,23 +3052,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63" ht="90" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="90" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr"/>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -3101,7 +3079,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -3109,23 +3087,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64" ht="90" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="90" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -3136,7 +3114,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -3145,23 +3123,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65" ht="90" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="90" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -3174,7 +3152,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -3183,30 +3161,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66" ht="90" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="90" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -3215,262 +3193,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67" ht="90" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="90" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" ht="90" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="90" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69" ht="90" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="90" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr"/>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70" ht="90" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="90" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71" ht="90" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72" ht="90" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72" ht="90" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="90" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73" ht="90" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74" ht="90" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr"/>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H73"/>
+  <autoFilter ref="A1:H74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1059,73 +1059,30 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed</t>
+          <t>Milford (labs 4/5) house policy format for VeritaDC drafts</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Receipt done 2026-10-07 (tests/integration/d1-aggregate-override.test.ts, real engine via recomputeAllStudyStatuses): percent-only and absolute-only TEa with every sample passing stay PASS, and a 2...</t>
+          <t>DESIGN written 2026-10-07: docs/VERITADC_HOUSE_FORMAT_DESIGN.md (per-lab docx_format setting, a format registry in veritapolicyDocx.ts rendering I. Purpose / II. Policy / III. Guidelines / IV. Pers...</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>S (1-3 days)</t>
+          <t>M (multi-day)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Medium. Lisa's lab.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>The 2026-10-04 sweep claimed a method-comparison study can FAIL on
-aggregate mean |bias| while every sample passes. Michael: "If every sample has to
-be a pass, it is not possible for the aggregate to be a fail." The assistant
-conceded the claim was sloppy and that it is only possible for dual-criterion
-analytes (percent OR absolute floor), then never resolved whether the override
-(server/routes.ts ~395-420) is a real defect or correct behavior.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-04 21:58-22:03.</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Milford (labs 4/5) house policy format for VeritaDC drafts</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>DESIGN written 2026-10-07: docs/VERITADC_HOUSE_FORMAT_DESIGN.md (per-lab docx_format setting, a format registry in veritapolicyDocx.ts rendering I. Purpose / II. Policy / III. Guidelines / IV. Pers...</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>M (multi-day)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Medium. Lisa's lab.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>"Update the UMASS Milford sites to this policy template." The house
 format (sections I-V, revision table, footer) was extracted from the sample DOCX
@@ -1133,40 +1090,40 @@
 4 and 5.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06 ~13:19 (.eml).</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>In-app Getting Started wizard (per-module checklists inside the system)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>DESIGN written 2026-10-07: docs/IN_APP_GETTING_STARTED_DESIGN.md (reuses gettingStartedContent.ts as the single source; GET /api/labs/:labId/getting-started derives every step's status from real ta...</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>M (multi-day)</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>The public /resources/getting-started page shipped (PR #1480).
 Michael: "Love it being built into the system." The in-app per-module checklist
@@ -1174,41 +1131,41 @@
 started.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06 13:15.</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Env-gated Playwright specs never run in CI; two shipped unrunnable</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Open. Specs repaired and shipped; the CI token/QA-lab decision is Michael's (cost: one seeded demo lab on prod plus a repo secret).
 ---</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Medium. The Gate 3 step 8 receipts for authenticated UI are skipped in CI (no...</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>playwright-smoke runs 74 specs as "skip without PW_TOKEN". The
 2026-10-07 local pass over merged UI PRs found two that could never pass as
@@ -1221,9 +1178,57 @@
 system, never a client lab) would run these on every PR.</t>
         </is>
       </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>overnight audit 2026-10-07 (local Playwright pass, see overnight log section 16).</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>VeritaComp assessment dialog: the Element 2 (and 3, 4) date picker is nearly unclickable</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Open. Root cause located; XS fix, build on request or fold into the next VeritaComp PR.
+---</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>XS (under 1 day)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Medium. Every technical competency assessment goes through these rows.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>In NewAssessmentDialog the per-element Date field is a native
+&lt;Input type="date"&gt; in a fixed 128 px column (w-32, text-xs h-7,
+client/src/pages/VeritaCompAppPage.tsx 3568-3570) beside the Pass checkbox in a
+flex gap-2 items-end row. At that width the browser's date control cannot fit
+the formatted value plus its calendar icon, so the icon is clipped at the right
+edge and sits under the "Pass" label (Michael's screenshot: a sliver of the icon
+next to Pass). Elements 3 (3599) and 4 (3628) use the same pattern, so it is a
+class fix: give the date column room (w-40 / min-w) or put Pass on its own line
+under the date, keep the control height readable, and check it in a browser at
+the dialog's max-w-3xl width and in dark mode.</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>overnight audit 2026-10-07 (local Playwright pass, see overnight log section 16).</t>
+          <t>Michael, 2026-10-07 morning screenshot (Element 2, Blood Bank Tube method program).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1240,7 +1245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1298,12 +1303,12 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C73</t>
+          <t>C74</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp legacy program modal shows no VeritaStaff employees (was #59)</t>
+          <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed (was #67)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -1324,24 +1329,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C72</t>
+          <t>C73</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Nightly backup studyCount anomaly on every user-deleted study (was #73)</t>
+          <t>VeritaComp legacy program modal shows no VeritaStaff employees (was #59)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1350,24 +1355,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C71</t>
+          <t>C72</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody (was #70)</t>
+          <t>Nightly backup studyCount anomaly on every user-deleted study (was #73)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1376,24 +1381,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C70</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL (was #69)</t>
+          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody (was #70)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1402,24 +1407,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C69</t>
+          <t>C70</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte (was #68)</t>
+          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL (was #69)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium-High</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1428,24 +1433,24 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C68</t>
+          <t>C69</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931 (was #66)</t>
+          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte (was #68)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1454,24 +1459,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C67</t>
+          <t>C68</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat) (was #63)</t>
+          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931 (was #66)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1480,24 +1485,24 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C66</t>
+          <t>C67</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
+          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat) (was #63)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>was S + S / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S + S / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1506,24 +1511,24 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C65</t>
+          <t>C66</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
+          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S + S / Importance: High</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S + S / Importance: High</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1532,24 +1537,24 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C64</t>
+          <t>C65</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaPT CAP vendor program catalog (was #60)</t>
+          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1558,12 +1563,12 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C63</t>
+          <t>C64</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
+          <t>VeritaPT CAP vendor program catalog (was #60)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -1584,24 +1589,24 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C62</t>
+          <t>C63</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
+          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1610,24 +1615,24 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C61</t>
+          <t>C62</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
+          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Low</t>
+          <t>was M / Importance: Medium</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Low</t>
+          <t>Effort: was M / Importance: Medium</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1636,12 +1641,12 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C60</t>
+          <t>C61</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
+          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
@@ -1662,24 +1667,24 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C59</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Confirm the finding-closure signer policy (was #43)</t>
+          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1688,24 +1693,24 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C58</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
+          <t>Confirm the finding-closure signer policy (was #43)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1714,24 +1719,24 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list (was #47)</t>
+          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1740,24 +1745,24 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Low-Medium</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Low-Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1766,24 +1771,24 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1792,24 +1797,24 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -1818,24 +1823,24 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1844,24 +1849,24 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -1870,24 +1875,24 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1896,12 +1901,12 @@
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
@@ -1922,24 +1927,24 @@
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1948,24 +1953,24 @@
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -1974,24 +1979,24 @@
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -2000,39 +2005,38 @@
     <row r="29" ht="90" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr"/>
     </row>
     <row r="30" ht="90" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
@@ -2040,12 +2044,12 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -2054,12 +2058,12 @@
     <row r="31" ht="90" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
@@ -2067,12 +2071,12 @@
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -2081,12 +2085,12 @@
     <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
@@ -2094,12 +2098,12 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -2108,12 +2112,12 @@
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
@@ -2121,12 +2125,12 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -2135,12 +2139,12 @@
     <row r="34" ht="90" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
@@ -2148,12 +2152,12 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -2162,12 +2166,12 @@
     <row r="35" ht="90" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
@@ -2175,12 +2179,12 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -2189,12 +2193,12 @@
     <row r="36" ht="90" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
@@ -2202,12 +2206,12 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -2216,12 +2220,12 @@
     <row r="37" ht="90" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
@@ -2229,12 +2233,12 @@
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -2243,12 +2247,12 @@
     <row r="38" ht="90" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
@@ -2256,12 +2260,12 @@
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -2270,12 +2274,12 @@
     <row r="39" ht="90" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
@@ -2283,7 +2287,7 @@
       <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2297,18 +2301,45 @@
     <row r="40" ht="90" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -2320,24 +2351,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -2347,24 +2378,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -2372,30 +2403,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -2406,30 +2437,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -2440,29 +2471,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -2473,37 +2504,9 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
----</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
-23 years" as of 2026-05-01.</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2512,18 +2515,46 @@
     <row r="47" ht="90" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr"/>
       <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
+23 years" as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 14, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -2536,7 +2567,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -2544,46 +2575,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="90" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr"/>
@@ -2591,14 +2593,14 @@
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
+          <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2607,12 +2609,12 @@
     <row r="50" ht="90" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
@@ -2620,13 +2622,14 @@
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>session 299e9a73, ~2026-04-28.
+          <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
@@ -2635,18 +2638,46 @@
     <row r="51" ht="90" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr"/>
       <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="3" t="inlineStr"/>
       <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2655,29 +2686,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2688,30 +2719,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2721,59 +2752,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Tier-1 smoke test checklist (formerly #6)</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
-smoke-test process and post-deploy verification steps. Shipped via
-PR #81 as part of the 2026-05-10 wave.</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
       <c r="H54" s="2" t="inlineStr"/>
     </row>
     <row r="55" ht="90" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Per-module gating (formerly #7)</t>
+          <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr"/>
       <c r="D55" s="3" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
+smoke-test process and post-deploy verification steps. Shipped via
+PR #81 as part of the 2026-05-10 wave.</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Per-module gating (formerly #7)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2788,29 +2819,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2818,29 +2849,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2855,33 +2886,6 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="90" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
-        </is>
-      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
@@ -2893,18 +2897,45 @@
     <row r="59" ht="90" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>WSLH PT vendor (formerly #15)</t>
+          <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr"/>
       <c r="D59" s="3" t="inlineStr"/>
       <c r="E59" s="3" t="inlineStr"/>
       <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Operator instruction 2026-05-10 in this session.
+---</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="90" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>WSLH PT vendor (formerly #15)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -2922,38 +2953,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="90" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2962,12 +2964,12 @@
     <row r="61" ht="90" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr"/>
@@ -2975,15 +2977,14 @@
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
+Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
@@ -2992,12 +2993,12 @@
     <row r="62" ht="90" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
@@ -3005,35 +3006,65 @@
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="90" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63" ht="90" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="90" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr"/>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -3044,7 +3075,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -3052,23 +3083,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64" ht="90" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="90" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -3079,7 +3110,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -3087,23 +3118,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65" ht="90" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="90" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -3114,7 +3145,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -3123,23 +3154,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66" ht="90" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="90" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -3152,7 +3183,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -3161,30 +3192,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67" ht="90" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="90" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -3193,262 +3224,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" ht="90" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="90" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69" ht="90" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="90" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr"/>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70" ht="90" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="90" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71" ht="90" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72" ht="90" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72" ht="90" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="90" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73" ht="90" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74" ht="90" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr"/>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74" ht="90" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75" ht="90" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H74"/>
+  <autoFilter ref="A1:H75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1233,8 +1233,61 @@
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>VeritaMap: Manual Diff cell lines never pair with the analyzer differential, so no correlation is triggered</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Open. Names on both sides confirmed in the library; build on request.
+---</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>High. 42 CFR 493.1281 comparability: the same analyte on two methods (manual...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Correlation grouping in the map intelligence matches instruments on
+the exact analyte string. The library's "Manual Differential" entry names the
+cell lines "Lymphocytes / Neutrophils / Monocytes / Eosinophils / Basophils";
+the hematology analyzers (Sysmex XN-1000/XN-2000 and the rest) name them
+"LYMPH% / NEUT% / MONO% / EO% / BASO%" (plus the absolute "#" rows). Same
+measurand (the percentage differential), different strings, so Lymph on the
+manual diff and LYMPH% on the analyzer show as two unrelated tests and the
+Pri/Backup correlation requirement is never raised. Same for every cell line.
+Fix: a canonical-analyte layer for correlation grouping (manual "Lymphocytes"
+&lt;-&gt; analyzer "LYMPH%" / "Lymphocytes (%)" and the same for NEUT/MONO/EO/BASO;
+the "%" row is the comparable one, not "#"), plus harmonizing the library's
+Manual Differential names toward the analyzer convention so new maps do not
+inherit the split. Receipt: a map with Sysmex XN + Manual Differential shows
+one correlation requirement per cell line, and the existing name-based matches
+are unchanged.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-07 morning ("Manual diff Lymph is the same as lymph% on the hematology analyzers, but they are showing as different tests and not triggering correlations. Same for the other cell lines").</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -917,60 +917,15 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaMap test-menu accuracy audit (menus incomplete, not just missing instruments)</t>
+          <t>VeritaMap: remove duplicate demo maps (dedupe tool shipped; awaiting selection)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>IN PROGRESS. Michael chose Option 2 (exhaustive) 2026-10-06. Executing vendor-by-vendor, sourced and verified against the manufacturer's own parameter lists. Batch 1 (Roche chemistry c-module) reco...</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>L (3-5 weeks)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>High — wrong or partial menus surface live in demos and undercut VeritaMap as...</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Beyond confirming every instrument exists, the per-instrument analyte
-menus in client/src/lib/fdaInstrumentData.json need verification for
-completeness and accuracy. Surfaced when a Roche demo hit a cobas 8000 with no
-Sodium or Potassium: that entry was scoped to the c702 photometric module and
-omitted the ISE-module electrolytes. The cobas 8000 / c702 / c502 electrolyte
-gap was fixed 2026-10-06 (see Status), but the systemic issue — module-scoped
-or partial menus across vendors — remains. A full pass (vendor/FDA-sourced,
-no fabrication) would make VeritaMap demo-safe across the board.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-06 Roche demo.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>VeritaMap: remove duplicate demo maps (dedupe tool shipped; awaiting selection)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Open. Tool live; awaiting Michael's deletion selection.
 ---
@@ -979,17 +934,17 @@
 _(item #63 closed 2026-10-07; PR #1493 deplo...</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day)</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Low-Medium — demo-lab hygiene; not customer-facing.</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Michael created many maps while demoing and asked to remove
 duplicates. The read-only-by-default admin dedupe-maps endpoint shipped
@@ -1000,40 +955,40 @@
 with full cascade once he approves the ids.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06.</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>VeritaQC LJ chart vs Westgard rule mean-source mismatch (point near chart mean fires 1-3s)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Root cause confirmed in code AND in data (2026-10-07, read-only prod copy): lab 29 Gameday Plymouth, lot 27 "PSA (FREND B)" Level 1 (6361A26001), manufacturer mean 1.29 / SD 0.35; lab history n=30...</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>High. Customer-visible correctness and trust issue; the chart and the rule fl...</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>A QC point can fire the 1-3s rejection rule while the Levey-Jennings
 chart shows it near the mean. Root cause: the two use DIFFERENT baselines. The
@@ -1049,40 +1004,40 @@
 applied to both chart and rules).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Mike Hiltunen (MedStar), 2026-10-06 email "LJ Graph Question". Gameday Plymouth PSA Frend B Level 1, 9/28 point fired 1-3s but sits near the mean on the chart.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Milford (labs 4/5) house policy format for VeritaDC drafts</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>DESIGN written 2026-10-07: docs/VERITADC_HOUSE_FORMAT_DESIGN.md (per-lab docx_format setting, a format registry in veritapolicyDocx.ts rendering I. Purpose / II. Policy / III. Guidelines / IV. Pers...</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>M (multi-day)</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Medium. Lisa's lab.</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>"Update the UMASS Milford sites to this policy template." The house
 format (sections I-V, revision table, footer) was extracted from the sample DOCX
@@ -1090,40 +1045,40 @@
 4 and 5.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06 ~13:19 (.eml).</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>In-app Getting Started wizard (per-module checklists inside the system)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>DESIGN written 2026-10-07: docs/IN_APP_GETTING_STARTED_DESIGN.md (reuses gettingStartedContent.ts as the single source; GET /api/labs/:labId/getting-started derives every step's status from real ta...</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>M (multi-day)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>The public /resources/getting-started page shipped (PR #1480).
 Michael: "Love it being built into the system." The in-app per-module checklist
@@ -1131,41 +1086,41 @@
 started.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-06 13:15.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Env-gated Playwright specs never run in CI; two shipped unrunnable</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Open. Specs repaired and shipped; the CI token/QA-lab decision is Michael's (cost: one seeded demo lab on prod plus a repo secret).
 ---</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Medium. The Gate 3 step 8 receipts for authenticated UI are skipped in CI (no...</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>playwright-smoke runs 74 specs as "skip without PW_TOKEN". The
 2026-10-07 local pass over merged UI PRs found two that could never pass as
@@ -1178,41 +1133,41 @@
 system, never a client lab) would run these on every PR.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>overnight audit 2026-10-07 (local Playwright pass, see overnight log section 16).</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>VeritaComp assessment dialog: the Element 2 (and 3, 4) date picker is nearly unclickable</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Open. Root cause located; XS fix, build on request or fold into the next VeritaComp PR.
 ---</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Medium. Every technical competency assessment goes through these rows.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>In NewAssessmentDialog the per-element Date field is a native
 &lt;Input type="date"&gt; in a fixed 128 px column (w-32, text-xs h-7,
@@ -1226,41 +1181,41 @@
 the dialog's max-w-3xl width and in dark mode.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-07 morning screenshot (Element 2, Blood Bank Tube method program).</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>VeritaMap: Manual Diff cell lines never pair with the analyzer differential, so no correlation is triggered</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Open. Names on both sides confirmed in the library; build on request.
 ---</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>High. 42 CFR 493.1281 comparability: the same analyte on two methods (manual...</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Correlation grouping in the map intelligence matches instruments on
 the exact analyte string. The library's "Manual Differential" entry names the
@@ -1279,15 +1234,15 @@
 are unchanged.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Michael, 2026-10-07 morning ("Manual diff Lymph is the same as lymph% on the hematology analyzers, but they are showing as different tests and not triggering correlations. Same for the other cell lines").</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1298,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1356,24 +1311,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C74</t>
+          <t>C76</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed (was #67)</t>
+          <t>VeritaMap "Failed to delete map": half-cascade left shells, VeritaStaff FK blocked the rest (found and fixed 2026-10-07)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S / Importance: High. Michael could not delete four demo maps on lab 3; t...</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S / Importance: High. Michael could not delete four demo maps on lab 3; the same code path would have gutted any map whose instrument was ever assigned to a staff member.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1382,24 +1337,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C73</t>
+          <t>C75</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp legacy program modal shows no VeritaStaff employees (was #59)</t>
+          <t>VeritaMap test-menu accuracy audit: Siemens/Abbott duplicate cleanup (was #57)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was M / Importance: High</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was M / Importance: High</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1408,24 +1363,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C72</t>
+          <t>C74</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Nightly backup studyCount anomaly on every user-deleted study (was #73)</t>
+          <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed (was #67)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1434,12 +1389,12 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C71</t>
+          <t>C73</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody (was #70)</t>
+          <t>VeritaComp legacy program modal shows no VeritaStaff employees (was #59)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -1460,24 +1415,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C70</t>
+          <t>C72</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL (was #69)</t>
+          <t>Nightly backup studyCount anomaly on every user-deleted study (was #73)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1486,24 +1441,24 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C69</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte (was #68)</t>
+          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody (was #70)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium-High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1512,12 +1467,12 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C68</t>
+          <t>C70</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931 (was #66)</t>
+          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL (was #69)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -1538,24 +1493,24 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C67</t>
+          <t>C69</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat) (was #63)</t>
+          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte (was #68)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1564,24 +1519,24 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C66</t>
+          <t>C68</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
+          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931 (was #66)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>was S + S / Importance: High</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S + S / Importance: High</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1590,24 +1545,24 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C65</t>
+          <t>C67</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
+          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat) (was #63)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1616,24 +1571,24 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C64</t>
+          <t>C66</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VeritaPT CAP vendor program catalog (was #60)</t>
+          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was S + S / Importance: High</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was S + S / Importance: High</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1642,24 +1597,24 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C63</t>
+          <t>C65</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
+          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1668,24 +1623,24 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C62</t>
+          <t>C64</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
+          <t>VeritaPT CAP vendor program catalog (was #60)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1694,24 +1649,24 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C61</t>
+          <t>C63</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
+          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Low</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Low</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1720,24 +1675,24 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C60</t>
+          <t>C62</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
+          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Low</t>
+          <t>was M / Importance: Medium</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Low</t>
+          <t>Effort: was M / Importance: Medium</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1746,24 +1701,24 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C59</t>
+          <t>C61</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Confirm the finding-closure signer policy (was #43)</t>
+          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1772,24 +1727,24 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C58</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
+          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1798,24 +1753,24 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list (was #47)</t>
+          <t>Confirm the finding-closure signer policy (was #43)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1824,24 +1779,24 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
+          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Low-Medium</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Low-Medium</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1850,24 +1805,24 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -1876,24 +1831,24 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1902,24 +1857,24 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -1928,24 +1883,24 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1954,24 +1909,24 @@
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
@@ -1980,24 +1935,24 @@
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -2006,24 +1961,24 @@
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -2032,24 +1987,24 @@
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -2058,24 +2013,24 @@
     <row r="29" ht="90" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
@@ -2084,66 +2039,64 @@
     <row r="30" ht="90" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="90" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="3" t="inlineStr"/>
     </row>
     <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
@@ -2151,12 +2104,12 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -2165,12 +2118,12 @@
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
@@ -2178,12 +2131,12 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -2192,12 +2145,12 @@
     <row r="34" ht="90" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
@@ -2205,12 +2158,12 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -2219,12 +2172,12 @@
     <row r="35" ht="90" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
@@ -2232,12 +2185,12 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -2246,12 +2199,12 @@
     <row r="36" ht="90" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
@@ -2259,12 +2212,12 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -2273,12 +2226,12 @@
     <row r="37" ht="90" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
@@ -2286,12 +2239,12 @@
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -2300,12 +2253,12 @@
     <row r="38" ht="90" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
@@ -2313,12 +2266,12 @@
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -2327,12 +2280,12 @@
     <row r="39" ht="90" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
@@ -2340,12 +2293,12 @@
       <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -2354,12 +2307,12 @@
     <row r="40" ht="90" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
@@ -2367,12 +2320,12 @@
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -2381,18 +2334,72 @@
     <row r="41" ht="90" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="3" t="inlineStr"/>
       <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -2404,24 +2411,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -2431,24 +2438,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -2456,30 +2463,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -2490,30 +2497,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -2524,29 +2531,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -2557,57 +2564,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -2620,7 +2627,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -2628,75 +2635,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51" ht="90" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr"/>
@@ -2704,8 +2653,9 @@
       <c r="E51" s="3" t="inlineStr"/>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -2719,18 +2669,75 @@
     <row r="52" ht="90" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 5, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2739,29 +2746,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2772,30 +2779,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54" ht="90" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2805,59 +2812,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2872,29 +2879,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2902,29 +2909,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="90" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="90" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2939,56 +2946,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="90" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="90" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="90" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="90" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -3006,68 +3013,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61" ht="90" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
----</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62" ht="90" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
 ---</t>
         </is>
       </c>
@@ -3076,12 +3024,12 @@
     <row r="63" ht="90" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr"/>
@@ -3089,35 +3037,94 @@
       <c r="E63" s="3" t="inlineStr"/>
       <c r="F63" s="3" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the feature set ships today.
+---</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="90" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>PAL studies guided workflow (formerly #23)</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="90" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64" ht="90" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="90" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -3128,7 +3135,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -3136,23 +3143,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65" ht="90" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="90" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -3163,7 +3170,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -3171,23 +3178,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66" ht="90" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="90" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -3198,7 +3205,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -3207,23 +3214,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67" ht="90" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="90" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -3236,7 +3243,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -3245,30 +3252,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" ht="90" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="90" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -3277,262 +3284,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69" ht="90" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="90" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr"/>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70" ht="90" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72" ht="90" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71" ht="90" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="90" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72" ht="90" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74" ht="90" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73" ht="90" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75" ht="90" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr"/>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74" ht="90" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="90" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75" ht="90" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="90" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H75"/>
+  <autoFilter ref="A1:H77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Root cause confirmed in code AND in data (2026-10-07, read-only prod copy): lab 29 Gameday Plymouth, lot 27 "PSA (FREND B)" Level 1 (6361A26001), manufacturer mean 1.29 / SD 0.35; lab history n=30...</t>
+          <t>Data pulled 2026-10-07 from a read-only prod copy (Plymouth, lab 29, PSA FREND B Level 1, lot 6361A26001): the 9/28 result 1.39 is +3.2 SD against the lab's 30-point history (mean 1.067, SD 0.100)...</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1014,113 +1014,30 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Milford (labs 4/5) house policy format for VeritaDC drafts</t>
+          <t>Env-gated Playwright specs never run in CI; two shipped unrunnable</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DESIGN written 2026-10-07: docs/VERITADC_HOUSE_FORMAT_DESIGN.md (per-lab docx_format setting, a format registry in veritapolicyDocx.ts rendering I. Purpose / II. Policy / III. Guidelines / IV. Pers...</t>
+          <t>BUILT 2026-10-07 on Michael's option 1 (PR #1507): a BLOCKING "Sandbox receipts" step in playwright-smoke.yml runs tests/playwright/sandbox-receipts.txt (8 specs, 13 tests) with PW_* repo secrets,...</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>M (multi-day)</t>
+          <t>S (1-3 days)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Medium. Lisa's lab.</t>
+          <t>Medium. The Gate 3 step 8 receipts for authenticated UI are skipped in CI (no...</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>"Update the UMASS Milford sites to this policy template." The house
-format (sections I-V, revision table, footer) was extracted from the sample DOCX
-on 2026-10-06 13:21 but was never built into the VeritaDC DOCX generator for labs
-4 and 5.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-06 ~13:19 (.eml).</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>In-app Getting Started wizard (per-module checklists inside the system)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>DESIGN written 2026-10-07: docs/IN_APP_GETTING_STARTED_DESIGN.md (reuses gettingStartedContent.ts as the single source; GET /api/labs/:labId/getting-started derives every step's status from real ta...</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>M (multi-day)</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>The public /resources/getting-started page shipped (PR #1480).
-Michael: "Love it being built into the system." The in-app per-module checklist
-(progress read from the lab's actual state) was stated as a follow-up and not
-started.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Michael, 2026-10-06 13:15.</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Env-gated Playwright specs never run in CI; two shipped unrunnable</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Open. Specs repaired and shipped; the CI token/QA-lab decision is Michael's (cost: one seeded demo lab on prod plus a repo secret).
----</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>S (1-3 days)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Medium. The Gate 3 step 8 receipts for authenticated UI are skipped in CI (no...</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>playwright-smoke runs 74 specs as "skip without PW_TOKEN". The
 2026-10-07 local pass over merged UI PRs found two that could never pass as
@@ -1133,41 +1050,41 @@
 system, never a client lab) would run these on every PR.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>overnight audit 2026-10-07 (local Playwright pass, see overnight log section 16).</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>VeritaComp assessment dialog: the Element 2 (and 3, 4) date picker is nearly unclickable</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Open. Root cause located; XS fix, build on request or fold into the next VeritaComp PR.
 ---</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day)</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Medium. Every technical competency assessment goes through these rows.</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>In NewAssessmentDialog the per-element Date field is a native
 &lt;Input type="date"&gt; in a fixed 128 px column (w-32, text-xs h-7,
@@ -1181,41 +1098,41 @@
 the dialog's max-w-3xl width and in dark mode.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-07 morning screenshot (Element 2, Blood Bank Tube method program).</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>VeritaMap: Manual Diff cell lines never pair with the analyzer differential, so no correlation is triggered</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Open. Names on both sides confirmed in the library; build on request.
 ---</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>High. 42 CFR 493.1281 comparability: the same analyte on two methods (manual...</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Correlation grouping in the map intelligence matches instruments on
 the exact analyte string. The library's "Manual Differential" entry names the
@@ -1234,15 +1151,164 @@
 are unchanged.</t>
         </is>
       </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-07 morning ("Manual diff Lymph is the same as lymph% on the hematology analyzers, but they are showing as different tests and not triggering correlations. Same for the other cell lines").</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>VeritaMap: mark Calibration Verification "Not applicable" per test, with a reason, and honor the existing exemption flags on the map page</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Open. Build on request.
+---</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>High. Readiness and the surveyor-facing map currently show "missing" or "over...</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>On the map page the Cal Ver column treats only WAIVED complexity as
+exempt (VeritaMapMapPage.tsx ~1335 and ~1457: isWaived ? "Exempt" : DateCell);
+every other test gets a date cell, a 6-month clock and an overdue/missing
+border, and feeds the readiness counts. Qualitative methods (manual
+differential, urine microscopy, Gram stain, rapid kits), devices with no user
+calibration, and tests the lab has already flagged exempt on the instrument
+rows (the four linearity_exempt_* flags on veritamap_instrument_tests, set in
+the build wizard; see memory reference_veritamap_linearity_exemption_recovery)
+still show as needing a date on the map page because that page never reads the
+flags. Fix: (1) a per-test "Not applicable" control on the Cal Ver cell with a
+required reason (qualitative / no user calibration / manufacturer-calibrated
+single-use device / exempt per instrument flags / other with text), stored on
+veritamap_tests (cal_ver_na, cal_ver_na_reason, who and when) and shown as
+"N/A: reason" in the cell, the labwide page, the Excel export and the coverage
+intelligence; (2) the map page derives "Exempt" from the instrument-level flags
+as well as WAIVED, so the two stores agree (fix t...</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Michael, 2026-10-07 ~09:40 ("it would be nice to N/A the calibration verification from veritamap").</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>VeritaMap: manual date entry is clunky (native date control in a narrow cell; same class as #75)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Open. Build on request; bundle with #75.
+---</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Medium. Every map row carries at least two of these dates (Last Cal Ver, Last...</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>DateCell on the map page (VeritaMapMapPage.tsx ~374) renders a native
+Input type="date" in a text-xs cell; the browser's segmented control forces
+click-into-segment typing, hides its calendar icon at that width, rejects
+partial input, and offers no "today" or paste-a-date path, so entering a
+cal-ver date for 40 tests is 40 fiddly interactions. VeritaComp's element rows
+use the same native control. Fix the class once: one shared date-entry
+component (typed MM/DD/YYYY with masking and validation, calendar popover,
+"Today" shortcut, paste tolerant, keyboard-friendly, readable at cell size and
+in dark mode) used by the map page's two date columns, the labwide page, and
+the VeritaComp element dates; #75 closes with it. Receipt: Playwright entering
+a date by typing, by "Today" and by the picker on a map row and on a VeritaComp
+element, plus a dark mode screenshot.</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Michael, 2026-10-07 morning ("Manual diff Lymph is the same as lymph% on the hematology analyzers, but they are showing as different tests and not triggering correlations. Same for the other cell lines").</t>
+          <t>Michael, 2026-10-07 ~09:40 ("the manual date entry on veritamap is clunky").</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>In-app Getting Started phase B: live checkmarks on the module how-to cards</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Open. Build on request.
+---</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>XS (under 1 day)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Medium. The remaining half of Michael's #72 decision (option 1: dashboard car...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>ModuleHowToCard already renders on every module page; the
+getting-started endpoint already returns the 19 derived statuses. Phase B
+filters the three MODULE_GUIDES steps for the current module and shows them
+under the video with live done/todo marks from the same endpoint, so the
+public page, the dashboard card and the module card never drift. Receipt: the
+existing getting-started integration test plus a Playwright check that a
+module card flips a step to done after the lab adds the matching record.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>docs/IN_APP_GETTING_STARTED_DESIGN.md, Michael's option 1 (2026-10-07).</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1253,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1311,24 +1377,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C76</t>
+          <t>C78</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VeritaMap "Failed to delete map": half-cascade left shells, VeritaStaff FK blocked the rest (found and fixed 2026-10-07)</t>
+          <t>Milford (labs 4/5) house policy format for VeritaDC drafts (was #71)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High. Michael could not delete four demo maps on lab 3; t...</t>
+          <t>was M / Importance: Medium. Lisa's lab; first renderer-based instance of the...</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High. Michael could not delete four demo maps on lab 3; the same code path would have gutted any map whose instrument was ever assigned to a staff member.</t>
+          <t>Effort: was M / Importance: Medium. Lisa's lab; first renderer-based instance of the standing house-format courtesy (SCAHC was artifact-based).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1337,24 +1403,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C75</t>
+          <t>C77</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>VeritaMap test-menu accuracy audit: Siemens/Abbott duplicate cleanup (was #57)</t>
+          <t>In-app Getting Started, phase A: dashboard card scored from the lab's own tables (was #72)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: High</t>
+          <t>was M / Importance: Medium</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: High</t>
+          <t>Effort: was M / Importance: Medium</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1363,24 +1429,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C74</t>
+          <t>C76</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed (was #67)</t>
+          <t>VeritaMap "Failed to delete map": half-cascade left shells, VeritaStaff FK blocked the rest (found and fixed 2026-10-07)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S / Importance: High. Michael could not delete four demo maps on lab 3; t...</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S / Importance: High. Michael could not delete four demo maps on lab 3; the same code path would have gutted any map whose instrument was ever assigned to a staff member.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1389,24 +1455,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C73</t>
+          <t>C75</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp legacy program modal shows no VeritaStaff employees (was #59)</t>
+          <t>VeritaMap test-menu accuracy audit: Siemens/Abbott duplicate cleanup (was #57)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was M / Importance: High</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was M / Importance: High</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1415,24 +1481,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C72</t>
+          <t>C74</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Nightly backup studyCount anomaly on every user-deleted study (was #73)</t>
+          <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed (was #67)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1441,12 +1507,12 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C71</t>
+          <t>C73</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody (was #70)</t>
+          <t>VeritaComp legacy program modal shows no VeritaStaff employees (was #59)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -1467,24 +1533,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C70</t>
+          <t>C72</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL (was #69)</t>
+          <t>Nightly backup studyCount anomaly on every user-deleted study (was #73)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1493,24 +1559,24 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C69</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte (was #68)</t>
+          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody (was #70)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium-High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1519,12 +1585,12 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C68</t>
+          <t>C70</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931 (was #66)</t>
+          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL (was #69)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -1545,24 +1611,24 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C67</t>
+          <t>C69</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat) (was #63)</t>
+          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte (was #68)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1571,24 +1637,24 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C66</t>
+          <t>C68</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
+          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931 (was #66)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>was S + S / Importance: High</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S + S / Importance: High</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1597,24 +1663,24 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C65</t>
+          <t>C67</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
+          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat) (was #63)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1623,24 +1689,24 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C64</t>
+          <t>C66</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VeritaPT CAP vendor program catalog (was #60)</t>
+          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was S + S / Importance: High</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was S + S / Importance: High</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1649,24 +1715,24 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C63</t>
+          <t>C65</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
+          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1675,24 +1741,24 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C62</t>
+          <t>C64</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
+          <t>VeritaPT CAP vendor program catalog (was #60)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1701,24 +1767,24 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C61</t>
+          <t>C63</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
+          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Low</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Low</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1727,24 +1793,24 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C60</t>
+          <t>C62</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
+          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Low</t>
+          <t>was M / Importance: Medium</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Low</t>
+          <t>Effort: was M / Importance: Medium</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1753,24 +1819,24 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C59</t>
+          <t>C61</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Confirm the finding-closure signer policy (was #43)</t>
+          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1779,24 +1845,24 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C58</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
+          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1805,24 +1871,24 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list (was #47)</t>
+          <t>Confirm the finding-closure signer policy (was #43)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -1831,24 +1897,24 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
+          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Low-Medium</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Low-Medium</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1857,24 +1923,24 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -1883,24 +1949,24 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1909,24 +1975,24 @@
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
@@ -1935,24 +2001,24 @@
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1961,24 +2027,24 @@
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -1987,24 +2053,24 @@
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -2013,24 +2079,24 @@
     <row r="29" ht="90" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
@@ -2039,24 +2105,24 @@
     <row r="30" ht="90" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>was S (Phase 3) / Importance: Medium</t>
+          <t>was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+          <t>Effort: was S-M / Importance: Medium</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -2065,24 +2131,24 @@
     <row r="31" ht="90" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>VeritaResponse post-survey deficiency module (was #17)</t>
+          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>was XL / Importance: High</t>
+          <t>was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XL / Importance: High</t>
+          <t>Effort: was S-M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
@@ -2091,66 +2157,64 @@
     <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
+          <t>Unregulated-analyte / Alternative Assessment (AAA) coverage (was #18)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
----</t>
-        </is>
-      </c>
+          <t>Effort: was S (Phase 3) / Importance: Medium</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C48</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Verified-users product-update send path (wrong-list incident fix)</t>
+          <t>VeritaResponse post-survey deficiency module (was #17)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>was XL / Importance: High</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
----</t>
-        </is>
-      </c>
+          <t>Effort: was XL / Importance: High</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="inlineStr"/>
     </row>
     <row r="34" ht="90" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
+          <t>Unify coverage/competency recurrence helper (was #49) - closed as non-issue</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
@@ -2158,12 +2222,12 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
+          <t>Closure evidence: Investigated 2026-09-24 before building. The coverage recurrence math (+6-month interval, signed-resets-to-missing, nextDueOn/overdue, isFailVerdict) is ALREADY single-source in server/veritacheckCoverage.ts (computeCoverageFrom). server/coverageReport.ts and the routes.ts coverage export do not recompute it; they consume the computed nextDueOn/overdue/status fields and apply small surface-specific presentation labels (deliberately different vocabularies per surface, so they should not be merged). The only truly identical duplicate is a one-line date formatter. The competency "owed" derivation is NOT the same cadence: competency follows the CLIA milestone schedule (initial / semiannual year 1 / annual, 42 CFR 493.1451(b)(8) and 493.1235), which is a different regulatory interval from the coverage 6-month rule (493.1281 / 493.1255) and must stay separate. No worthwhile extraction; merging the two cadences would be wrong. Closed 2026-09-24. (The year-1 competency-window refinement remains tracked separately as #50.)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
+          <t>2026-09-24 session, "keep working" pass; scoped read-only, found no real duplication.
 ---</t>
         </is>
       </c>
@@ -2172,12 +2236,12 @@
     <row r="35" ht="90" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>VeritaStaff instrument-centric (dual) assignment view</t>
+          <t>Verified-users product-update send path (wrong-list incident fix)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
@@ -2185,12 +2249,12 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
+          <t>Closure evidence: Shipped PR #1324 (merged 4e05506a, deploy ACTIVE). New POST /api/admin/users/send targets registered VeritaAssure account holders (the users table), never the Lab Director's Briefing subscriber list. Separate explicitly-named endpoint (not a flag with a dangerous default), account-holder email framing, excludes suppressed emails and RFC-reserved test domains, CC owner, dryRun + testTo previews. Public unsubscribe now upserts a suppression row so opt-outs are honored across both audiences. Live dryRun: 49 verified-user recipients vs 673 on the Briefing list. Receipts: scripts/verify-product-update-send.mts 24/24, tsc clean, rendered sample inspected. Fixes the fallout from the 2026-09-23/24 wrong-list send (a product update went to the 675-person Briefing list). Nothing sends without Michael's explicit "send it."</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
+          <t>2026-09-24 session; Michael selected this as the next build after the #41 close.
 ---</t>
         </is>
       </c>
@@ -2199,12 +2263,12 @@
     <row r="36" ht="90" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
+          <t>Verify-script convention backfill (was #41) + audit matcher fix</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
@@ -2212,12 +2276,12 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
+          <t>Closure evidence: #41 was fully backfilled on 2026-06-13 (all 8 high-stakes scripts landed; see C30); it had only been mis-filed in OPEN. A 2026-09-24 re-audit initially reported 4 of 5 recent math/logic commits as missing a verify script, which was a FALSE POSITIVE: scripts/audit_verify_script_coverage.py matched only scripts/verify-*.js / .cjs, so it ignored the .mjs / .mts / .ts verify scripts the repo now ships (e.g. verify-ptcoag-multi.mts, verify-tea-criterion-format.mjs). Fixed the matcher to accept .js/.cjs/.mjs/.ts/.mts; re-run shows 5 of 5 covered, 0 debt. The convention is being followed. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
+          <t>2026-09-24 session, "keep working" pass; audit tooling bug found + fixed.
 ---</t>
         </is>
       </c>
@@ -2226,12 +2290,12 @@
     <row r="37" ht="90" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
+          <t>VeritaStaff instrument-centric (dual) assignment view</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
@@ -2239,12 +2303,12 @@
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1320. GET/PUT /staff/instruments/:id/employees (transpose of the per-employee endpoints); an "Assign by Instrument" dialog lets a director pick a test system or manual test and check off who runs it. Same staff_employee_instruments join, with the 42 CFR 493.1235(a) duty-change event emitted on newly-added pairs so both orientations trigger the same reassessment. GET verified live on SCAHC lab 2. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
+          <t>2026-09-24 session, Michael ("in staff we should also give the dual view when assigning coverage to test systems or manual tests").
 ---</t>
         </is>
       </c>
@@ -2253,12 +2317,12 @@
     <row r="38" ht="90" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
+          <t>VeritaComp coverage map (required-vs-assessed matrix, dual view)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
@@ -2266,12 +2330,12 @@
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1319 (+ status layer PR #1316). /competency/owed returns per-item assessed (locked passing assessment this cycle on a covering method group) + per-employee CLIA status; CompetencyCoverageMap renders a By-employee / By-instrument matrix (Assessed / Owed / Overdue / Gap). Verified live on SCAHC lab 2 (owed 116, assessed 2, gaps 0). Completes #48 as the VeritaCheck-parity coverage map. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
+          <t>2026-09-24 session, Michael ("are we building the competencies to have a coverage map, same as veritacheck?" then "build it").
 ---</t>
         </is>
       </c>
@@ -2280,12 +2344,12 @@
     <row r="39" ht="90" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan line items can attach or link evidence (was #46)</t>
+          <t>VeritaCheck coverage recurrence (method comparison + cal-ver/linearity + reports)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
@@ -2293,12 +2357,12 @@
       <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
+          <t>Closure evidence: PRs #1317 (method comparison), #1318 (cal-ver/linearity), #1321 (report Next-due columns). Periodic verification (correlation/method comparison 42 CFR 493.1281; cal-ver/linearity 42 CFR 493.1255; both 6-month) now recurs: a signed study banks the cycle and rolls to next-due = signed + 6 months instead of reading "done" forever. Status Missing/Failed/Completed-unsigned + a "Next due on" column on-screen and in both coverage exports; also credits the previously-ignored "correlation" study type. Root cause: computeCoverageFrom marked requirements done on mere existence, no date logic. Verified live on SCAHC lab 2 (101 correlations + 11 cal-ver rows now carry a next-due). Engine-level, all facilities. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
+          <t>2026-09-24 session, Michael ("Look at San Carlos... they finished their last set of correlations (all 103) but their menu never reset").
 ---</t>
         </is>
       </c>
@@ -2307,12 +2371,12 @@
     <row r="40" ht="90" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
+          <t>VeritaComp Competencies Owed derived from VeritaStaff, with gap detection (was #48)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
@@ -2320,12 +2384,12 @@
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1314 (squash 2bcb0db9). GET /api/labs/:labId/competency/owed derives each VeritaStaff testing employee's owed competencies from their assigned instruments (staff_employee_instruments -&gt; veritamap_instruments + tests), on the CLIA timeline, and flags instruments not covered by any competency program as gaps. CompetenciesOwedSection renders it on the VeritaComp landing page. Reuses the shipped bridge + suggested-method-groups match rules; no new tables. Verified live on prod with real assignment data: 2 instruments assigned to a demo staffer produced owed=2, gaps=2 (HIGH, Technical Supervisor), then reverted cleanly. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
+          <t>2026-09-23/24 session, Michael ("veritacomp bases what competencies they owe (currently untrue, but needs to be true)"). Option 1 (unify roster on VeritaStaff, match instruments by id).
 ---</t>
         </is>
       </c>
@@ -2334,12 +2398,12 @@
     <row r="41" ht="90" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
+          <t>VeritaScan line items can attach or link evidence (was #46)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
@@ -2347,12 +2411,12 @@
       <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+          <t>Closure evidence: PR #1312 (squash a1dda93d). VeritaScan scan checklist items now show linked evidence as chips (open link, remove) plus a writer "Link evidence" affordance whose picker links an existing VeritaDC/Library document; a shortcut deep-links to the Library for new (governed) documents. Reuses the already-shipped lab_documents + document_checklist_links + coverage endpoints (URL-pointer only, no file storage, no new tables). Browser-verified live on prod (scan 23): the affordance renders and the picker opens. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael. Recurring request. Companion: cross-module evidence display on the VeritaDC policy shipped in PR #1313 (by-target cross-links surfaced in the policy View modal, browser-verified live).
 ---</t>
         </is>
       </c>
@@ -2361,12 +2425,12 @@
     <row r="42" ht="90" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+          <t>VeritaTrack calendar month cells expand to reveal hidden tasks (was #45)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
@@ -2374,12 +2438,12 @@
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+          <t>Closure evidence: VeritaTrack CalendarView month cells with more than three tasks now expand in place (chevron, "+N more" toggling to "Show less", due dates), so no task is hidden with no path to it (client/src/pages/VeritaTrackAppPage.tsx CalendarView). Shipped 2026-09-23. Closed 2026-09-24.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+          <t>2026-09-23 session, Michael screenshot of the VeritaTrack calendar (lab 3, September cell).
 ---</t>
         </is>
       </c>
@@ -2388,18 +2452,72 @@
     <row r="43" ht="90" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Wire the two static-audit guards into CI (was #43)</t>
+          <t>Long Excel column headers no longer clip CFR citations (was #44)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. The VeritaMap export derives the header row height from the longest wrapped header via headerRowHeight(headers, colWidths) (server/routes.ts:15935) instead of a fixed 20, so "Reference Range Attestation (42 CFR 493.1253)" and the other long headers print in full. No new code this session. Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>License stamp no longer clobbers the §6 header/footer or names the wrong lab (was #43)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: Verified already fixed on main during the 2026-09-24 session. setHeaderFooter (shared/licenseExceljs.ts:155-209) now preserves an existing §6 header and appends (not overwrites) the footer left section, and customer-facing exports name the scoped lab: the VeritaScan library export reads req.scope.lab.name / clia_number (server/routes.ts:16572-16573), not the licensee. No new code this session (avoided regressing the existing fix). Closed 2026-09-24.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>parked 2026-07-16 (PR 4 Gate 3 render); found already-fixed 2026-09-24.
+---</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
 workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
@@ -2411,24 +2529,24 @@
 (same caveat as the existing guards already in that workflow).</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>C35</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: GET /api/studies now scopes its list to the active lab
 when one is resolved from the Referer (server/routes.ts), so every returned row
@@ -2438,24 +2556,24 @@
 mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
@@ -2463,30 +2581,30 @@
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -2497,30 +2615,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -2531,29 +2649,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -2564,57 +2682,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -2627,7 +2745,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -2635,75 +2753,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52" ht="90" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H52" s="2" t="inlineStr"/>
     </row>
     <row r="53" ht="90" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr"/>
@@ -2711,8 +2771,9 @@
       <c r="E53" s="3" t="inlineStr"/>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -2726,18 +2787,75 @@
     <row r="54" ht="90" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 5, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -2746,29 +2864,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -2779,30 +2897,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56" ht="90" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -2812,59 +2930,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58" ht="90" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60" ht="90" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -2879,29 +2997,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="90" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="90" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -2909,29 +3027,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60" ht="90" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62" ht="90" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -2946,56 +3064,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61" ht="90" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="90" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62" ht="90" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64" ht="90" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -3013,68 +3131,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63" ht="90" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr"/>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
----</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64" ht="90" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
 ---</t>
         </is>
       </c>
@@ -3083,12 +3142,12 @@
     <row r="65" ht="90" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr"/>
@@ -3096,35 +3155,94 @@
       <c r="E65" s="3" t="inlineStr"/>
       <c r="F65" s="3" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the feature set ships today.
+---</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="90" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>PAL studies guided workflow (formerly #23)</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="90" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66" ht="90" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68" ht="90" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -3135,7 +3253,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -3143,23 +3261,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67" ht="90" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="90" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -3170,7 +3288,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -3178,23 +3296,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" ht="90" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="90" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -3205,7 +3323,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -3214,23 +3332,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69" ht="90" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="90" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr"/>
-      <c r="D69" s="3" t="inlineStr"/>
-      <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -3243,7 +3361,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -3252,30 +3370,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70" ht="90" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72" ht="90" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -3284,262 +3402,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71" ht="90" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="90" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72" ht="90" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74" ht="90" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73" ht="90" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75" ht="90" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr"/>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74" ht="90" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="90" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75" ht="90" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="90" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76" ht="90" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78" ht="90" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr"/>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77" ht="90" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" ht="90" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr"/>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H77"/>
+  <autoFilter ref="A1:H79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Data pulled 2026-10-07 from a read-only prod copy (Plymouth, lab 29, PSA FREND B Level 1, lot 6361A26001): the 9/28 result 1.39 is +3.2 SD against the lab's 30-point history (mean 1.067, SD 0.100)...</t>
+          <t>FIX DEPLOYED 2026-10-07 (PR #1464, squash 03db1fe4, live 10:41 ET) on Michael's decision 2 relayed by Lisa: the Westgard rules, the chart and the monthly PDF all use the lot's programmed (manufactu...</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1307,8 +1307,62 @@
       </c>
       <c r="H17" s="3" t="inlineStr"/>
     </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPT: the CAP program catalog behind the enrollment picker is incomplete and partly stale (FH9 and RT4 missing, FH2P obsolete)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Open. Needs the current CAP Surveys catalog (or the program codes the Milford sites enroll in) as the verified source; build on request.
+---</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>S (1-3 days)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>High. The enrollment picker is how a lab records its PT coverage for 42 CFR 4...</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>The "Manage PT Program Enrollments" dialog lists CAP programs from the
+pt_vendor_programs table (GET /api/veritapt/programs), loaded through the admin
+vendor-programs endpoint from operator-verified data with provenance in the
+source column. Production holds 74 CAP programs, source "CAP Surveys catalog
+(estore.cap.org), compiled 2026-10-06", and only six of them are Hematology:
+FH2, FH2P, BCP, BP, BMD, ESR. Lisa (2026-10-07): FH9 is missing, RT4 is
+missing, FH2P is an obsolete event, "I'm sure there are more." The CAP Surveys
+catalog runs to several hundred programs, so a 74-row compile is a thin first
+pass, not a catalog. (The API vendor list, 225 programs loaded 2026-10-05, has
+not been checked the same way.) Fix: rebuild the CAP list from the current CAP
+Surveys catalog as the source document, code, name, category and analytes per
+program, verified by a CAP-enrolled director before load (Lisa is the natural
+verifier; the loader's never-fabricated rule stands); reload with replaceVendor
+CAP and the catalog edition recorded in source; mark retired programs such as
+FH2P inactive rather than deleting them so existing enrollments stay valid;
+then spot-check the API list against i...</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Lisa, 2026-10-07 ~10:20 (screenshot, lab 5 VeritaPT enrollments dialog).</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -965,79 +965,30 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaQC LJ chart vs Westgard rule mean-source mismatch (point near chart mean fires 1-3s)</t>
+          <t>Env-gated Playwright specs never run in CI; two shipped unrunnable</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FIX DEPLOYED 2026-10-07 (PR #1464, squash 03db1fe4, live 10:41 ET) on Michael's decision 2 relayed by Lisa: the Westgard rules, the chart and the monthly PDF all use the lot's programmed (manufactu...</t>
+          <t>BUILT 2026-10-07 on Michael's option 1 (PR #1507): a BLOCKING "Sandbox receipts" step in playwright-smoke.yml runs tests/playwright/sandbox-receipts.txt (8 specs, 13 tests) with PW_* repo secrets,...</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S (1-3 days)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>High. Customer-visible correctness and trust issue; the chart and the rule fl...</t>
+          <t>Medium. The Gate 3 step 8 receipts for authenticated UI are skipped in CI (no...</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>A QC point can fire the 1-3s rejection rule while the Levey-Jennings
-chart shows it near the mean. Root cause: the two use DIFFERENT baselines. The
-Westgard engine (evaluateWestgardForLot, server/routes.ts ~3717) computes mean/SD
-FRESH from the lab's accepted QC history and flags |value - historyMean| / historySD
-&gt; 3. The LJ chart draws its center line and SD bands from the lot's MANUFACTURER
-insert values (mfr_mean / mfr_sd, the columns the chart-data query pulls at
-server/routes.ts ~4250). When the lab's own running mean/SD differs from the
-manufacturer insert (common once a lab establishes its own stats), a point near the
-mfr mean on the chart can be &gt;3 lab-SD out. Per CLIA/CLSI C24, QC should be
-evaluated against the lab's established mean/SD; the fix is to make the chart plot
-the SAME established mean/SD the rules use (or a consistent mfr-vs-cumulative mode
-applied to both chart and rules).</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Mike Hiltunen (MedStar), 2026-10-06 email "LJ Graph Question". Gameday Plymouth PSA Frend B Level 1, 9/28 point fired 1-3s but sits near the mean on the chart.</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Env-gated Playwright specs never run in CI; two shipped unrunnable</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>BUILT 2026-10-07 on Michael's option 1 (PR #1507): a BLOCKING "Sandbox receipts" step in playwright-smoke.yml runs tests/playwright/sandbox-receipts.txt (8 specs, 13 tests) with PW_* repo secrets,...</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>S (1-3 days)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Medium. The Gate 3 step 8 receipts for authenticated UI are skipped in CI (no...</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>playwright-smoke runs 74 specs as "skip without PW_TOKEN". The
 2026-10-07 local pass over merged UI PRs found two that could never pass as
@@ -1050,41 +1001,41 @@
 system, never a client lab) would run these on every PR.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>overnight audit 2026-10-07 (local Playwright pass, see overnight log section 16).</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>VeritaComp assessment dialog: the Element 2 (and 3, 4) date picker is nearly unclickable</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Open. Root cause located; XS fix, build on request or fold into the next VeritaComp PR.
 ---</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day)</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Medium. Every technical competency assessment goes through these rows.</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>In NewAssessmentDialog the per-element Date field is a native
 &lt;Input type="date"&gt; in a fixed 128 px column (w-32, text-xs h-7,
@@ -1098,41 +1049,41 @@
 the dialog's max-w-3xl width and in dark mode.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Michael, 2026-10-07 morning screenshot (Element 2, Blood Bank Tube method program).</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>VeritaMap: Manual Diff cell lines never pair with the analyzer differential, so no correlation is triggered</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Open. Names on both sides confirmed in the library; build on request.
 ---</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>High. 42 CFR 493.1281 comparability: the same analyte on two methods (manual...</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Correlation grouping in the map intelligence matches instruments on
 the exact analyte string. The library's "Manual Differential" entry names the
@@ -1151,41 +1102,41 @@
 are unchanged.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-07 morning ("Manual diff Lymph is the same as lymph% on the hematology analyzers, but they are showing as different tests and not triggering correlations. Same for the other cell lines").</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>VeritaMap: mark Calibration Verification "Not applicable" per test, with a reason, and honor the existing exemption flags on the map page</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Open. Build on request.
 ---</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>High. Readiness and the surveyor-facing map currently show "missing" or "over...</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>On the map page the Cal Ver column treats only WAIVED complexity as
 exempt (VeritaMapMapPage.tsx ~1335 and ~1457: isWaived ? "Exempt" : DateCell);
@@ -1205,41 +1156,41 @@
 as well as WAIVED, so the two stores agree (fix t...</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Michael, 2026-10-07 ~09:40 ("it would be nice to N/A the calibration verification from veritamap").</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>VeritaMap: manual date entry is clunky (native date control in a narrow cell; same class as #75)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Open. Build on request; bundle with #75.
 ---</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Medium. Every map row carries at least two of these dates (Last Cal Ver, Last...</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>DateCell on the map page (VeritaMapMapPage.tsx ~374) renders a native
 Input type="date" in a text-xs cell; the browser's segmented control forces
@@ -1255,41 +1206,41 @@
 element, plus a dark mode screenshot.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Michael, 2026-10-07 ~09:40 ("the manual date entry on veritamap is clunky").</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>In-app Getting Started phase B: live checkmarks on the module how-to cards</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Open. Build on request.
 ---</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Medium. The remaining half of Michael's #72 decision (option 1: dashboard car...</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>ModuleHowToCard already renders on every module page; the
 getting-started endpoint already returns the 19 derived statuses. Phase B
@@ -1300,41 +1251,41 @@
 module card flips a step to done after the lab adds the matching record.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>docs/IN_APP_GETTING_STARTED_DESIGN.md, Michael's option 1 (2026-10-07).</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>VeritaPT: the CAP program catalog behind the enrollment picker is incomplete and partly stale (FH9 and RT4 missing, FH2P obsolete)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Open. Needs the current CAP Surveys catalog (or the program codes the Milford sites enroll in) as the verified source; build on request.
 ---</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>S (1-3 days)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>High. The enrollment picker is how a lab records its PT coverage for 42 CFR 4...</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>The "Manage PT Program Enrollments" dialog lists CAP programs from the
 pt_vendor_programs table (GET /api/veritapt/programs), loaded through the admin
@@ -1354,15 +1305,15 @@
 then spot-check the API list against i...</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Lisa, 2026-10-07 ~10:20 (screenshot, lab 5 VeritaPT enrollments dialog).</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1373,7 +1324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1431,24 +1382,24 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C78</t>
+          <t>C79</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Milford (labs 4/5) house policy format for VeritaDC drafts (was #71)</t>
+          <t>VeritaQC: Levey-Jennings chart and Westgard rules used two different mean/SD bases (was #65)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium. Lisa's lab; first renderer-based instance of the...</t>
+          <t>was S / Importance: High. Live on a paying account (MedStar, Gameday Plymouth...</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium. Lisa's lab; first renderer-based instance of the standing house-format courtesy (SCAHC was artifact-based).</t>
+          <t>Effort: was S / Importance: High. Live on a paying account (MedStar, Gameday Plymouth): a 1-3s rejection drawn near the chart mean.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -1457,24 +1408,24 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C77</t>
+          <t>C78</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>In-app Getting Started, phase A: dashboard card scored from the lab's own tables (was #72)</t>
+          <t>Milford (labs 4/5) house policy format for VeritaDC drafts (was #71)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium</t>
+          <t>was M / Importance: Medium. Lisa's lab; first renderer-based instance of the...</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium</t>
+          <t>Effort: was M / Importance: Medium. Lisa's lab; first renderer-based instance of the standing house-format courtesy (SCAHC was artifact-based).</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1483,24 +1434,24 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C76</t>
+          <t>C77</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VeritaMap "Failed to delete map": half-cascade left shells, VeritaStaff FK blocked the rest (found and fixed 2026-10-07)</t>
+          <t>In-app Getting Started, phase A: dashboard card scored from the lab's own tables (was #72)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High. Michael could not delete four demo maps on lab 3; t...</t>
+          <t>was M / Importance: Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High. Michael could not delete four demo maps on lab 3; the same code path would have gutted any map whose instrument was ever assigned to a staff member.</t>
+          <t>Effort: was M / Importance: Medium</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1509,24 +1460,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C75</t>
+          <t>C76</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaMap test-menu accuracy audit: Siemens/Abbott duplicate cleanup (was #57)</t>
+          <t>VeritaMap "Failed to delete map": half-cascade left shells, VeritaStaff FK blocked the rest (found and fixed 2026-10-07)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: High</t>
+          <t>was S / Importance: High. Michael could not delete four demo maps on lab 3; t...</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: High</t>
+          <t>Effort: was S / Importance: High. Michael could not delete four demo maps on lab 3; the same code path would have gutted any map whose instrument was ever assigned to a staff member.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1535,24 +1486,24 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C74</t>
+          <t>C75</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed (was #67)</t>
+          <t>VeritaMap test-menu accuracy audit: Siemens/Abbott duplicate cleanup (was #57)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was M / Importance: High</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was M / Importance: High</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1561,12 +1512,12 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>C73</t>
+          <t>C74</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VeritaComp legacy program modal shows no VeritaStaff employees (was #59)</t>
+          <t>VeritaCheck D1 method-comparison verdict: the mean-|bias| override is disputed (was #67)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -1587,24 +1538,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C72</t>
+          <t>C73</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Nightly backup studyCount anomaly on every user-deleted study (was #73)</t>
+          <t>VeritaComp legacy program modal shows no VeritaStaff employees (was #59)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1613,24 +1564,24 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>C71</t>
+          <t>C72</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody (was #70)</t>
+          <t>Nightly backup studyCount anomaly on every user-deleted study (was #73)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1639,24 +1590,24 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C70</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL (was #69)</t>
+          <t>Nightly backup "integrity ANOMALY" email on every real-user decrease, naming nobody (was #70)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1665,24 +1616,24 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C69</t>
+          <t>C70</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte (was #68)</t>
+          <t>computeStudyStatus throws at every boot for 4 studies and fail-safes them to FAIL (was #69)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium-High</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1691,24 +1642,24 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C68</t>
+          <t>C69</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931 (was #66)</t>
+          <t>VeritaMap: director attestation, MEC review and unlock stamp EVERY age/sex band of an analyte (was #68)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was S / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1717,24 +1668,24 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C67</t>
+          <t>C68</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat) (was #63)</t>
+          <t>VeritaCheck: Hemoglobin studies render as "Lab-Set Internal Goal", and every narrative cites 42 CFR 493.931 (was #66)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1743,24 +1694,24 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C66</t>
+          <t>C67</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
+          <t>about:blank on PDF opens (window.open token pattern + Adobe Acrobat) (was #63)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>was S + S / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S + S / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1769,24 +1720,24 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C65</t>
+          <t>C66</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
+          <t>Milford VeritaMap: every value/date save failed, then the AMR autosave loop (was #64)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was S + S / Importance: High</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was S + S / Importance: High</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1795,24 +1746,24 @@
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C64</t>
+          <t>C65</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VeritaPT CAP vendor program catalog (was #60)</t>
+          <t>Vendor instrument expansion PR #1474, 25 platforms (was #62)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1821,12 +1772,12 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C63</t>
+          <t>C64</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
+          <t>VeritaPT CAP vendor program catalog (was #60)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -1847,24 +1798,24 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C62</t>
+          <t>C63</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
+          <t>VeritaCheck instrument-verification multi-select analyte menu (was #58)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium</t>
+          <t>was S / Importance: High</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium</t>
+          <t>Effort: was S / Importance: High</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1873,24 +1824,24 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>C61</t>
+          <t>C62</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
+          <t>Plain-language summary layer: CFR Reference tab (was #30)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Low</t>
+          <t>was M / Importance: Medium</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Low</t>
+          <t>Effort: was M / Importance: Medium</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1899,12 +1850,12 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C60</t>
+          <t>C61</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
+          <t>Regenerate the access-inventory Excel with the corrected MD persona (was #44)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -1925,24 +1876,24 @@
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>C59</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Confirm the finding-closure signer policy (was #43)</t>
+          <t>VeritaQC Import Phase A browser click-through (was #40)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>was XS / Importance: Medium</t>
+          <t>was XS / Importance: Low</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Effort: was XS / Importance: Medium</t>
+          <t>Effort: was XS / Importance: Low</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -1951,24 +1902,24 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C58</t>
+          <t>C59</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
+          <t>Confirm the finding-closure signer policy (was #43)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was XS / Importance: Medium</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1977,24 +1928,24 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C57</t>
+          <t>C58</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Hide sections a lab does not use from a master list (was #47)</t>
+          <t>VeritaDC per-document attestation tracker + "My Documents" rename (built as #45)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -2003,24 +1954,24 @@
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C56</t>
+          <t>C57</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
+          <t>Hide sections a lab does not use from a master list (was #47)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>was S / Importance: Low-Medium</t>
+          <t>was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Low-Medium</t>
+          <t>Effort: was S-M / Importance: Medium-High (prospect-requested)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -2029,24 +1980,24 @@
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C55</t>
+          <t>C56</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
+          <t>VeritaCEU: curated free continuing-education provider list (was #53)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>was M / Importance: Medium-High</t>
+          <t>was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Effort: was M / Importance: Medium-High</t>
+          <t>Effort: was S / Importance: Low-Medium</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
@@ -2055,24 +2006,24 @@
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C54</t>
+          <t>C55</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
+          <t>VeritaScan: let sites add their own custom questions (was #55)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>was S-M (shipped S) / Importance: High</t>
+          <t>was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Effort: was S-M (shipped S) / Importance: High</t>
+          <t>Effort: was M / Importance: Medium-High</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -2081,24 +2032,24 @@
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C53</t>
+          <t>C54</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
+          <t>VeritaQC: at-entry warning when a QC point is outside 2 SD (was #56)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>was S / Importance: Medium</t>
+          <t>was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S / Importance: Medium</t>
+          <t>Effort: was S-M (shipped S) / Importance: High</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -2107,24 +2058,24 @@
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>C52</t>
+          <t>C53</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
+          <t>VeritaTrack: quarterly task loaded as monthly until re-saved (was #54)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>was L (shipped as MEDIUM) / Importance: High</t>
+          <t>was S / Importance: Medium</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
+          <t>Effort: was S / Importance: Medium</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -2133,24 +2084,24 @@
     <row r="29" ht="90" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C52</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
+          <t>VeritaResponse internal NCE / non-conforming event (was #36)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>was S-M / Importance: Medium</t>
+          <t>was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Effort: was S-M / Importance: Medium</t>
+          <t>Effort: was L (shipped as MEDIUM) / Importance: High</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
@@ -2159,12 +2110,12 @@
     <row r="30" ht="90" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>C49</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>VeritaTrack task owner + owner-only reminder routing (was #51)</t>
+          <t>Competency "assessed this cycle" cadence-aware window (was #50)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
@@ -2185,24 +2136,24 @@
     <row r="31" ht="90" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C50</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Designate Medical Director by picking a lab member (was #52, core)</t>
+          <t>VeritaTrack task owner + owner-only reminder routing (was #51